--- a/input/budget.xlsx
+++ b/input/budget.xlsx
@@ -12,11 +12,11 @@
     <externalReference r:id="rId1"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$775</definedName>
     <definedName name="Print_Titles" localSheetId="0">Sheet1!$1:$1</definedName>
     <definedName name="_xlcn.WorksheetConnection_budget_2024.xlsxTable21" hidden="1">'[1]budget 11-01-23'!$A$1:$M$198</definedName>
     <definedName name="_xlcn.WorksheetConnection_budget_2024.xlsxTable31" hidden="1">Table1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$775</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="309">
   <si>
     <t>Year</t>
   </si>
@@ -914,17 +914,125 @@
   </si>
   <si>
     <t xml:space="preserve">9116 Supplies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 Classis Assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4026 Beguest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1234 Designated Fund Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5020 Pastoral Search Expense</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6082 Candle,Oil,Wreth Exp.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>6084</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Chancel Guild expenses/Cook Trust</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">08 M&amp;B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6306 Little Pantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 Covenant Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COVENANT FUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Adult Ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Care &amp; Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Creation Care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Archives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9001 Personnel Committee expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9002 Business ans auto expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Communications</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">9116 Supplies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="2"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="\$#,##0_);[Red](\$#,##0)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -941,8 +1049,33 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -961,8 +1094,48 @@
         <bgColor theme="0" tint="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.099978637043366805"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -983,12 +1156,51 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="50">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1017,6 +1229,118 @@
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="3" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="5" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="6" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="0" borderId="3" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="8" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="6" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="1" fillId="4" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="1" fillId="4" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf fontId="6" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf fontId="1" fillId="8" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="2" fillId="9" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="3" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="10" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="2" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="2" fillId="4" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1549,9 +1873,10 @@
     <col min="1" max="1" style="1" width="9.140625"/>
     <col bestFit="1" customWidth="1" min="2" max="2" style="1" width="17.28515625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" style="1" width="29.140625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="24"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="46.7109375"/>
     <col customWidth="1" min="5" max="5" style="2" width="24"/>
-    <col min="6" max="16384" style="1" width="9.140625"/>
+    <col bestFit="1" min="6" max="6" style="1" width="9.421875"/>
+    <col min="7" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="14.25">
@@ -10278,8 +10603,6023 @@
         <v>47</v>
       </c>
     </row>
+    <row r="415" ht="12.75">
+      <c r="A415" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C415" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D415" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E415" s="13">
+        <v>14000</v>
+      </c>
+      <c r="F415" s="1"/>
+      <c r="G415" s="1"/>
+      <c r="H415" s="1"/>
+      <c r="I415" s="1"/>
+    </row>
+    <row r="416" ht="12.75">
+      <c r="A416" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C416" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D416" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E416" s="14">
+        <v>300000</v>
+      </c>
+      <c r="F416" s="15"/>
+      <c r="G416" s="15"/>
+      <c r="H416" s="15"/>
+      <c r="I416" s="1"/>
+    </row>
+    <row r="417" ht="12.75">
+      <c r="A417" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C417" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D417" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E417" s="16">
+        <v>8000</v>
+      </c>
+      <c r="F417" s="15"/>
+      <c r="G417" s="15"/>
+      <c r="H417" s="1"/>
+      <c r="I417" s="1"/>
+    </row>
+    <row r="418" ht="12.75">
+      <c r="A418" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D418" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E418" s="16">
+        <v>7000</v>
+      </c>
+      <c r="F418" s="15"/>
+      <c r="G418" s="15"/>
+      <c r="H418" s="1"/>
+      <c r="I418" s="1"/>
+    </row>
+    <row r="419" ht="12.75">
+      <c r="A419" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D419" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E419" s="16">
+        <v>3000</v>
+      </c>
+      <c r="F419" s="15"/>
+      <c r="G419" s="15"/>
+      <c r="H419" s="1"/>
+      <c r="I419" s="1"/>
+    </row>
+    <row r="420" ht="12.75">
+      <c r="A420" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D420" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="E420" s="16">
+        <v>3000</v>
+      </c>
+      <c r="F420" s="15"/>
+      <c r="G420" s="15"/>
+      <c r="H420" s="1"/>
+      <c r="I420" s="1"/>
+    </row>
+    <row r="421" ht="12.75">
+      <c r="A421" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D421" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="E421" s="16">
+        <v>3000</v>
+      </c>
+      <c r="F421" s="15"/>
+      <c r="G421" s="15"/>
+      <c r="H421" s="1"/>
+      <c r="I421" s="1"/>
+    </row>
+    <row r="422" ht="12.75">
+      <c r="A422" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D422" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E422" s="16">
+        <v>1000</v>
+      </c>
+      <c r="F422" s="15"/>
+      <c r="G422" s="15"/>
+      <c r="H422" s="1"/>
+      <c r="I422" s="1"/>
+    </row>
+    <row r="423" ht="12.75">
+      <c r="A423" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D423" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E423" s="19">
+        <v>30000</v>
+      </c>
+      <c r="F423" s="15"/>
+      <c r="G423" s="15"/>
+      <c r="H423" s="1"/>
+      <c r="I423" s="1"/>
+    </row>
+    <row r="424" ht="12.75">
+      <c r="A424" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D424" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E424" s="16">
+        <v>8000</v>
+      </c>
+      <c r="F424" s="15"/>
+      <c r="G424" s="15"/>
+      <c r="H424" s="1"/>
+      <c r="I424" s="1"/>
+    </row>
+    <row r="425" ht="12.75">
+      <c r="A425" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D425" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E425" s="16">
+        <v>200</v>
+      </c>
+      <c r="F425" s="15"/>
+      <c r="G425" s="15"/>
+      <c r="H425" s="1"/>
+      <c r="I425" s="1"/>
+    </row>
+    <row r="426" ht="12.75">
+      <c r="A426" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D426" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E426" s="20">
+        <v>2000</v>
+      </c>
+      <c r="F426" s="15"/>
+      <c r="G426" s="15"/>
+      <c r="H426" s="1"/>
+      <c r="I426" s="1"/>
+    </row>
+    <row r="427" ht="12.75">
+      <c r="A427" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D427" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E427" s="16">
+        <v>0</v>
+      </c>
+      <c r="F427" s="15"/>
+      <c r="G427" s="15"/>
+      <c r="H427" s="1"/>
+      <c r="I427" s="1"/>
+    </row>
+    <row r="428" ht="12.75">
+      <c r="A428" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D428" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E428" s="16">
+        <v>0</v>
+      </c>
+      <c r="F428" s="15"/>
+      <c r="G428" s="15"/>
+      <c r="H428" s="1"/>
+      <c r="I428" s="1"/>
+    </row>
+    <row r="429" ht="12.75">
+      <c r="A429" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D429" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="E429" s="22">
+        <v>40000</v>
+      </c>
+      <c r="F429" s="15"/>
+      <c r="G429" s="15"/>
+      <c r="H429" s="1"/>
+      <c r="I429" s="1"/>
+    </row>
+    <row r="430" ht="12.75">
+      <c r="A430" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D430" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="E430" s="16">
+        <v>0</v>
+      </c>
+      <c r="F430" s="15"/>
+      <c r="G430" s="15"/>
+      <c r="H430" s="1"/>
+      <c r="I430" s="1"/>
+    </row>
+    <row r="431" ht="12.75">
+      <c r="A431" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D431" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E431" s="24">
+        <f>195500*0.055/0.05</f>
+        <v>215050</v>
+      </c>
+      <c r="F431" s="15"/>
+      <c r="G431" s="15"/>
+      <c r="H431" s="1"/>
+      <c r="I431" s="1"/>
+    </row>
+    <row r="432" ht="12.75">
+      <c r="A432" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D432" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E432" s="16">
+        <v>140000</v>
+      </c>
+      <c r="F432" s="15"/>
+      <c r="G432" s="15"/>
+      <c r="H432" s="1"/>
+      <c r="I432" s="1"/>
+    </row>
+    <row r="433" ht="12.75">
+      <c r="A433" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D433" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E433" s="25">
+        <v>17000</v>
+      </c>
+      <c r="F433" s="26"/>
+      <c r="G433" s="27"/>
+      <c r="H433" s="1"/>
+      <c r="I433" s="1"/>
+    </row>
+    <row r="434" ht="12.75">
+      <c r="A434" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D434" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E434" s="28">
+        <v>36900</v>
+      </c>
+      <c r="F434" s="15"/>
+      <c r="G434" s="15"/>
+      <c r="H434" s="1"/>
+      <c r="I434" s="1"/>
+    </row>
+    <row r="435" ht="12.75">
+      <c r="A435" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C435" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D435" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E435" s="28">
+        <v>25100</v>
+      </c>
+      <c r="F435" s="15"/>
+      <c r="G435" s="15"/>
+      <c r="H435" s="1"/>
+      <c r="I435" s="1"/>
+    </row>
+    <row r="436" ht="12.75">
+      <c r="A436" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C436" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D436" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E436" s="16">
+        <v>70000</v>
+      </c>
+      <c r="F436" s="15"/>
+      <c r="G436" s="15"/>
+      <c r="H436" s="1"/>
+      <c r="I436" s="1"/>
+    </row>
+    <row r="437" ht="12.75">
+      <c r="A437" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D437" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E437" s="16">
+        <f>246500-E438-E436</f>
+        <v>76500</v>
+      </c>
+      <c r="F437" s="15"/>
+      <c r="G437" s="15"/>
+      <c r="H437" s="1"/>
+      <c r="I437" s="1"/>
+    </row>
+    <row r="438" ht="12.75">
+      <c r="A438" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D438" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E438" s="16">
+        <v>100000</v>
+      </c>
+      <c r="F438" s="15"/>
+      <c r="G438" s="15"/>
+      <c r="H438" s="1"/>
+      <c r="I438" s="1"/>
+    </row>
+    <row r="439" ht="12.75">
+      <c r="A439" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D439" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E439" s="14">
+        <v>10000</v>
+      </c>
+      <c r="F439" s="15"/>
+      <c r="G439" s="15"/>
+      <c r="H439" s="1"/>
+      <c r="I439" s="1"/>
+    </row>
+    <row r="440" ht="12.75">
+      <c r="A440" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D440" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E440" s="14">
+        <v>3000</v>
+      </c>
+      <c r="F440" s="15"/>
+      <c r="G440" s="15"/>
+      <c r="H440" s="1"/>
+      <c r="I440" s="1"/>
+    </row>
+    <row r="441" ht="12.75">
+      <c r="A441" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D441" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E441" s="14">
+        <v>18000</v>
+      </c>
+      <c r="F441" s="15"/>
+      <c r="G441" s="15"/>
+      <c r="H441" s="1"/>
+      <c r="I441" s="1"/>
+    </row>
+    <row r="442" ht="12.75">
+      <c r="A442" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D442" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E442" s="14">
+        <v>1100</v>
+      </c>
+      <c r="F442" s="15"/>
+      <c r="G442" s="15"/>
+      <c r="H442" s="1"/>
+      <c r="I442" s="1"/>
+    </row>
+    <row r="443" ht="12.75">
+      <c r="A443" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D443" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E443" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F443" s="15"/>
+      <c r="G443" s="15"/>
+      <c r="H443" s="1"/>
+      <c r="I443" s="1"/>
+    </row>
+    <row r="444" ht="12.75">
+      <c r="A444" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D444" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E444" s="14">
+        <v>5000</v>
+      </c>
+      <c r="F444" s="15"/>
+      <c r="G444" s="15"/>
+      <c r="H444" s="1"/>
+      <c r="I444" s="1"/>
+    </row>
+    <row r="445" ht="12.75">
+      <c r="A445" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D445" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E445" s="29">
+        <v>-2200</v>
+      </c>
+      <c r="F445" s="30"/>
+      <c r="G445" s="15"/>
+      <c r="H445" s="1"/>
+      <c r="I445" s="1"/>
+    </row>
+    <row r="446" ht="12.75">
+      <c r="A446" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D446" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E446" s="31">
+        <v>-57500</v>
+      </c>
+      <c r="F446" s="30"/>
+      <c r="G446" s="15"/>
+      <c r="H446" s="1"/>
+      <c r="I446" s="1"/>
+    </row>
+    <row r="447" ht="12.75">
+      <c r="A447" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D447" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E447" s="31">
+        <v>-10000</v>
+      </c>
+      <c r="F447" s="30"/>
+      <c r="G447" s="15"/>
+      <c r="H447" s="1"/>
+      <c r="I447" s="1"/>
+    </row>
+    <row r="448" ht="12.75">
+      <c r="A448" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D448" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E448" s="31">
+        <v>-13300</v>
+      </c>
+      <c r="F448" s="30"/>
+      <c r="G448" s="15"/>
+      <c r="H448" s="1"/>
+      <c r="I448" s="1"/>
+    </row>
+    <row r="449" ht="12.75">
+      <c r="A449" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D449" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E449" s="31">
+        <v>-7268</v>
+      </c>
+      <c r="F449" s="30"/>
+      <c r="G449" s="15"/>
+      <c r="H449" s="1"/>
+      <c r="I449" s="1"/>
+    </row>
+    <row r="450" ht="12.75">
+      <c r="A450" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D450" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E450" s="31">
+        <v>-5000</v>
+      </c>
+      <c r="F450" s="30"/>
+      <c r="G450" s="15"/>
+      <c r="H450" s="1"/>
+      <c r="I450" s="1"/>
+    </row>
+    <row r="451" ht="12.75">
+      <c r="A451" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D451" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E451" s="31">
+        <v>-37500</v>
+      </c>
+      <c r="F451" s="30"/>
+      <c r="G451" s="15"/>
+      <c r="H451" s="1"/>
+      <c r="I451" s="1"/>
+    </row>
+    <row r="452" ht="12.75">
+      <c r="A452" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D452" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E452" s="31">
+        <v>-1425</v>
+      </c>
+      <c r="F452" s="30"/>
+      <c r="G452" s="15"/>
+      <c r="H452" s="1"/>
+      <c r="I452" s="1"/>
+    </row>
+    <row r="453" ht="12.75">
+      <c r="A453" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D453" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="E453" s="32">
+        <v>-10000</v>
+      </c>
+      <c r="F453" s="30"/>
+      <c r="G453" s="15"/>
+      <c r="H453" s="1"/>
+      <c r="I453" s="1"/>
+    </row>
+    <row r="454" ht="12.75">
+      <c r="A454" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D454" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E454" s="29">
+        <v>-1524</v>
+      </c>
+      <c r="F454" s="30"/>
+      <c r="G454" s="15"/>
+      <c r="H454" s="1"/>
+      <c r="I454" s="1"/>
+    </row>
+    <row r="455" ht="12.75">
+      <c r="A455" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D455" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E455" s="29">
+        <v>-44623</v>
+      </c>
+      <c r="F455" s="30"/>
+      <c r="G455" s="15"/>
+      <c r="H455" s="1"/>
+      <c r="I455" s="1"/>
+    </row>
+    <row r="456" ht="12.75">
+      <c r="A456" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D456" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E456" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F456" s="30"/>
+      <c r="G456" s="15"/>
+      <c r="H456" s="1"/>
+      <c r="I456" s="1"/>
+    </row>
+    <row r="457" ht="12.75">
+      <c r="A457" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D457" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="E457" s="29">
+        <v>-18000</v>
+      </c>
+      <c r="F457" s="30"/>
+      <c r="G457" s="15"/>
+      <c r="H457" s="1"/>
+      <c r="I457" s="1"/>
+    </row>
+    <row r="458" ht="12.75">
+      <c r="A458" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D458" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E458" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F458" s="30"/>
+      <c r="G458" s="15"/>
+      <c r="H458" s="1"/>
+      <c r="I458" s="1"/>
+    </row>
+    <row r="459" ht="12.75">
+      <c r="A459" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D459" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E459" s="33">
+        <v>-700</v>
+      </c>
+      <c r="F459" s="30"/>
+      <c r="G459" s="15"/>
+      <c r="H459" s="1"/>
+      <c r="I459" s="1"/>
+    </row>
+    <row r="460" ht="12.75">
+      <c r="A460" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D460" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E460" s="33">
+        <v>-12950</v>
+      </c>
+      <c r="F460" s="30"/>
+      <c r="G460" s="15"/>
+      <c r="H460" s="1"/>
+      <c r="I460" s="1"/>
+    </row>
+    <row r="461" ht="12.75">
+      <c r="A461" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D461" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E461" s="33">
+        <v>-1200</v>
+      </c>
+      <c r="F461" s="30"/>
+      <c r="G461" s="15"/>
+      <c r="H461" s="1"/>
+      <c r="I461" s="1"/>
+    </row>
+    <row r="462" ht="12.75">
+      <c r="A462" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D462" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E462" s="33">
+        <v>-250</v>
+      </c>
+      <c r="F462" s="30"/>
+      <c r="G462" s="15"/>
+      <c r="H462" s="1"/>
+      <c r="I462" s="1"/>
+    </row>
+    <row r="463" ht="12.75">
+      <c r="A463" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D463" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E463" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F463" s="30"/>
+      <c r="G463" s="15"/>
+      <c r="H463" s="1"/>
+      <c r="I463" s="1"/>
+    </row>
+    <row r="464" ht="12.75">
+      <c r="A464" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D464" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E464" s="33">
+        <v>-1200</v>
+      </c>
+      <c r="F464" s="30"/>
+      <c r="G464" s="15"/>
+      <c r="H464" s="1"/>
+      <c r="I464" s="1"/>
+    </row>
+    <row r="465" ht="12.75">
+      <c r="A465" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D465" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E465" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F465" s="30"/>
+      <c r="G465" s="15"/>
+      <c r="H465" s="1"/>
+      <c r="I465" s="1"/>
+    </row>
+    <row r="466" ht="12.75">
+      <c r="A466" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D466" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E466" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F466" s="30"/>
+      <c r="G466" s="15"/>
+      <c r="H466" s="1"/>
+      <c r="I466" s="1"/>
+    </row>
+    <row r="467" ht="12.75">
+      <c r="A467" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D467" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E467" s="34">
+        <v>0</v>
+      </c>
+      <c r="F467" s="30"/>
+      <c r="G467" s="15"/>
+      <c r="H467" s="1"/>
+      <c r="I467" s="1"/>
+    </row>
+    <row r="468" ht="12.75">
+      <c r="A468" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D468" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E468" s="33">
+        <v>-3200</v>
+      </c>
+      <c r="F468" s="30"/>
+      <c r="G468" s="15"/>
+      <c r="H468" s="1"/>
+      <c r="I468" s="1"/>
+    </row>
+    <row r="469" ht="12.75">
+      <c r="A469" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C469" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D469" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E469" s="33">
+        <v>0</v>
+      </c>
+      <c r="F469" s="30"/>
+      <c r="G469" s="15"/>
+      <c r="H469" s="1"/>
+      <c r="I469" s="1"/>
+    </row>
+    <row r="470" ht="12.75">
+      <c r="A470" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C470" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D470" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E470" s="33">
+        <v>0</v>
+      </c>
+      <c r="F470" s="30"/>
+      <c r="G470" s="15"/>
+      <c r="H470" s="1"/>
+      <c r="I470" s="1"/>
+    </row>
+    <row r="471" ht="12.75">
+      <c r="A471" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C471" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D471" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E471" s="33">
+        <v>-100</v>
+      </c>
+      <c r="F471" s="30"/>
+      <c r="G471" s="15"/>
+      <c r="H471" s="1"/>
+      <c r="I471" s="1"/>
+    </row>
+    <row r="472" ht="12.75">
+      <c r="A472" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C472" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D472" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E472" s="33">
+        <v>-12000</v>
+      </c>
+      <c r="F472" s="30"/>
+      <c r="G472" s="15"/>
+      <c r="H472" s="1"/>
+      <c r="I472" s="1"/>
+    </row>
+    <row r="473" ht="12.75">
+      <c r="A473" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C473" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D473" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="E473" s="29">
+        <v>-2000</v>
+      </c>
+      <c r="F473" s="30"/>
+      <c r="G473" s="15"/>
+      <c r="H473" s="1"/>
+      <c r="I473" s="1"/>
+    </row>
+    <row r="474" ht="12.75">
+      <c r="A474" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C474" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D474" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E474" s="35">
+        <v>0</v>
+      </c>
+      <c r="F474" s="30"/>
+      <c r="G474" s="15"/>
+      <c r="H474" s="1"/>
+      <c r="I474" s="1"/>
+    </row>
+    <row r="475" ht="12.75">
+      <c r="A475" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C475" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D475" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E475" s="35">
+        <v>-1000</v>
+      </c>
+      <c r="F475" s="30"/>
+      <c r="G475" s="15"/>
+      <c r="H475" s="1"/>
+      <c r="I475" s="1"/>
+    </row>
+    <row r="476" ht="12.75">
+      <c r="A476" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C476" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D476" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="E476" s="35">
+        <v>0</v>
+      </c>
+      <c r="F476" s="30"/>
+      <c r="G476" s="15"/>
+      <c r="H476" s="1"/>
+      <c r="I476" s="1"/>
+    </row>
+    <row r="477" ht="12.75">
+      <c r="A477" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C477" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D477" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E477" s="37">
+        <v>0</v>
+      </c>
+      <c r="F477" s="30"/>
+      <c r="G477" s="15"/>
+      <c r="H477" s="1"/>
+      <c r="I477" s="1"/>
+    </row>
+    <row r="478" ht="12.75">
+      <c r="A478" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C478" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D478" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E478" s="37">
+        <v>-400</v>
+      </c>
+      <c r="F478" s="30"/>
+      <c r="G478" s="15"/>
+      <c r="H478" s="1"/>
+      <c r="I478" s="1"/>
+    </row>
+    <row r="479" ht="12.75">
+      <c r="A479" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C479" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D479" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E479" s="37">
+        <v>-1300</v>
+      </c>
+      <c r="F479" s="30"/>
+      <c r="G479" s="15"/>
+      <c r="H479" s="1"/>
+      <c r="I479" s="1"/>
+    </row>
+    <row r="480" ht="12.75">
+      <c r="A480" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C480" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D480" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="E480" s="37">
+        <v>-1000</v>
+      </c>
+      <c r="F480" s="30"/>
+      <c r="G480" s="15"/>
+      <c r="H480" s="1"/>
+      <c r="I480" s="1"/>
+    </row>
+    <row r="481" ht="12.75">
+      <c r="A481" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C481" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D481" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="E481" s="37">
+        <v>-1000</v>
+      </c>
+      <c r="F481" s="30"/>
+      <c r="G481" s="15"/>
+      <c r="H481" s="1"/>
+      <c r="I481" s="1"/>
+    </row>
+    <row r="482" ht="12.75">
+      <c r="A482" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C482" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D482" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E482" s="29">
+        <v>-10000</v>
+      </c>
+      <c r="F482" s="30"/>
+      <c r="G482" s="15"/>
+      <c r="H482" s="1"/>
+      <c r="I482" s="1"/>
+    </row>
+    <row r="483" ht="12.75">
+      <c r="A483" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C483" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D483" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E483" s="29">
+        <v>-14400</v>
+      </c>
+      <c r="F483" s="30"/>
+      <c r="G483" s="15"/>
+      <c r="H483" s="1"/>
+      <c r="I483" s="1"/>
+    </row>
+    <row r="484" ht="12.75">
+      <c r="A484" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C484" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D484" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="E484" s="39">
+        <v>-2000</v>
+      </c>
+      <c r="F484" s="30"/>
+      <c r="G484" s="15"/>
+      <c r="H484" s="1"/>
+      <c r="I484" s="1"/>
+    </row>
+    <row r="485" ht="12.75">
+      <c r="A485" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C485" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D485" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E485" s="29">
+        <v>-42800</v>
+      </c>
+      <c r="F485" s="30"/>
+      <c r="G485" s="15"/>
+      <c r="H485" s="1"/>
+      <c r="I485" s="1"/>
+    </row>
+    <row r="486" ht="12.75">
+      <c r="A486" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C486" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D486" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E486" s="29">
+        <v>-20000</v>
+      </c>
+      <c r="F486" s="30"/>
+      <c r="G486" s="15"/>
+      <c r="H486" s="1"/>
+      <c r="I486" s="1"/>
+    </row>
+    <row r="487" ht="12.75">
+      <c r="A487" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C487" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D487" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E487" s="29">
+        <v>-1600</v>
+      </c>
+      <c r="F487" s="30"/>
+      <c r="G487" s="15"/>
+      <c r="H487" s="1"/>
+      <c r="I487" s="1"/>
+    </row>
+    <row r="488" ht="12.75">
+      <c r="A488" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C488" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D488" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E488" s="32">
+        <v>0</v>
+      </c>
+      <c r="F488" s="30"/>
+      <c r="G488" s="15"/>
+      <c r="H488" s="1"/>
+      <c r="I488" s="1"/>
+    </row>
+    <row r="489" ht="12.75">
+      <c r="A489" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C489" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D489" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E489" s="29">
+        <v>-7200</v>
+      </c>
+      <c r="F489" s="30"/>
+      <c r="G489" s="15"/>
+      <c r="H489" s="1"/>
+      <c r="I489" s="1"/>
+    </row>
+    <row r="490" ht="12.75">
+      <c r="A490" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C490" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D490" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E490" s="29">
+        <v>-7200</v>
+      </c>
+      <c r="F490" s="30"/>
+      <c r="G490" s="15"/>
+      <c r="H490" s="1"/>
+      <c r="I490" s="1"/>
+    </row>
+    <row r="491" ht="12.75">
+      <c r="A491" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C491" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D491" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E491" s="29">
+        <v>-10000</v>
+      </c>
+      <c r="F491" s="30"/>
+      <c r="G491" s="15"/>
+      <c r="H491" s="1"/>
+      <c r="I491" s="1"/>
+    </row>
+    <row r="492" ht="12.75">
+      <c r="A492" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C492" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D492" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E492" s="40">
+        <v>-36900</v>
+      </c>
+      <c r="F492" s="30"/>
+      <c r="G492" s="15"/>
+      <c r="H492" s="1"/>
+      <c r="I492" s="1"/>
+    </row>
+    <row r="493" ht="12.75">
+      <c r="A493" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C493" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D493" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E493" s="29">
+        <v>-1591</v>
+      </c>
+      <c r="F493" s="30"/>
+      <c r="G493" s="15"/>
+      <c r="H493" s="1"/>
+      <c r="I493" s="1"/>
+    </row>
+    <row r="494" ht="12.75">
+      <c r="A494" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C494" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D494" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E494" s="29">
+        <v>-20800</v>
+      </c>
+      <c r="F494" s="30"/>
+      <c r="G494" s="15"/>
+      <c r="H494" s="1"/>
+      <c r="I494" s="1"/>
+    </row>
+    <row r="495" ht="12.75">
+      <c r="A495" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C495" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D495" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E495" s="33">
+        <v>0</v>
+      </c>
+      <c r="F495" s="30"/>
+      <c r="G495" s="15"/>
+      <c r="H495" s="1"/>
+      <c r="I495" s="1"/>
+    </row>
+    <row r="496" ht="12.75">
+      <c r="A496" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C496" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D496" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="E496" s="29">
+        <v>0</v>
+      </c>
+      <c r="F496" s="30"/>
+      <c r="G496" s="15"/>
+      <c r="H496" s="1"/>
+      <c r="I496" s="1"/>
+    </row>
+    <row r="497" ht="12.75">
+      <c r="A497" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C497" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D497" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E497" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F497" s="30"/>
+      <c r="G497" s="15"/>
+      <c r="H497" s="1"/>
+      <c r="I497" s="1"/>
+    </row>
+    <row r="498" ht="12.75">
+      <c r="A498" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C498" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D498" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E498" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F498" s="30"/>
+      <c r="G498" s="15"/>
+      <c r="H498" s="1"/>
+      <c r="I498" s="1"/>
+    </row>
+    <row r="499" ht="12.75">
+      <c r="A499" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C499" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D499" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E499" s="33">
+        <v>-250</v>
+      </c>
+      <c r="F499" s="30"/>
+      <c r="G499" s="15"/>
+      <c r="H499" s="1"/>
+      <c r="I499" s="1"/>
+    </row>
+    <row r="500" ht="12.75">
+      <c r="A500" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C500" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D500" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E500" s="33">
+        <v>-1500</v>
+      </c>
+      <c r="F500" s="30"/>
+      <c r="G500" s="15"/>
+      <c r="H500" s="1"/>
+      <c r="I500" s="1"/>
+    </row>
+    <row r="501" ht="12.75">
+      <c r="A501" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C501" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D501" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E501" s="34">
+        <v>-3000</v>
+      </c>
+      <c r="F501" s="30"/>
+      <c r="G501" s="15"/>
+      <c r="H501" s="1"/>
+      <c r="I501" s="1"/>
+    </row>
+    <row r="502" ht="12.75">
+      <c r="A502" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C502" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D502" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E502" s="33">
+        <v>-1400</v>
+      </c>
+      <c r="F502" s="30"/>
+      <c r="G502" s="15"/>
+      <c r="H502" s="1"/>
+      <c r="I502" s="1"/>
+    </row>
+    <row r="503" ht="12.75">
+      <c r="A503" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C503" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D503" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E503" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F503" s="30"/>
+      <c r="G503" s="15"/>
+      <c r="H503" s="1"/>
+      <c r="I503" s="1"/>
+    </row>
+    <row r="504" ht="12.75">
+      <c r="A504" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C504" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D504" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E504" s="33">
+        <v>-300</v>
+      </c>
+      <c r="F504" s="30"/>
+      <c r="G504" s="15"/>
+      <c r="H504" s="1"/>
+      <c r="I504" s="1"/>
+    </row>
+    <row r="505" ht="12.75">
+      <c r="A505" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C505" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D505" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E505" s="33">
+        <v>-20000</v>
+      </c>
+      <c r="F505" s="30"/>
+      <c r="G505" s="15"/>
+      <c r="H505" s="1"/>
+      <c r="I505" s="1"/>
+    </row>
+    <row r="506" ht="12.75">
+      <c r="A506" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C506" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D506" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E506" s="33">
+        <v>-150</v>
+      </c>
+      <c r="F506" s="30"/>
+      <c r="G506" s="15"/>
+      <c r="H506" s="1"/>
+      <c r="I506" s="1"/>
+    </row>
+    <row r="507" ht="12.75">
+      <c r="A507" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C507" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D507" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E507" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F507" s="30"/>
+      <c r="G507" s="15"/>
+      <c r="H507" s="1"/>
+      <c r="I507" s="1"/>
+    </row>
+    <row r="508" ht="12.75">
+      <c r="A508" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C508" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D508" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E508" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F508" s="30"/>
+      <c r="G508" s="15"/>
+      <c r="H508" s="1"/>
+      <c r="I508" s="1"/>
+    </row>
+    <row r="509" ht="12.75">
+      <c r="A509" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C509" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D509" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E509" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F509" s="30"/>
+      <c r="G509" s="15"/>
+      <c r="H509" s="1"/>
+      <c r="I509" s="1"/>
+    </row>
+    <row r="510" ht="12.75">
+      <c r="A510" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C510" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D510" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E510" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F510" s="30"/>
+      <c r="G510" s="15"/>
+      <c r="H510" s="1"/>
+      <c r="I510" s="1"/>
+    </row>
+    <row r="511" ht="12.75">
+      <c r="A511" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C511" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D511" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E511" s="32">
+        <v>-13337</v>
+      </c>
+      <c r="F511" s="30"/>
+      <c r="G511" s="15"/>
+      <c r="H511" s="1"/>
+      <c r="I511" s="1"/>
+    </row>
+    <row r="512" ht="12.75">
+      <c r="A512" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C512" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D512" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E512" s="29">
+        <v>-200</v>
+      </c>
+      <c r="F512" s="30"/>
+      <c r="G512" s="15"/>
+      <c r="H512" s="1"/>
+      <c r="I512" s="1"/>
+    </row>
+    <row r="513" ht="12.75">
+      <c r="A513" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C513" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D513" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E513" s="29">
+        <v>-10500</v>
+      </c>
+      <c r="F513" s="30"/>
+      <c r="G513" s="15"/>
+      <c r="H513" s="1"/>
+      <c r="I513" s="1"/>
+    </row>
+    <row r="514" ht="12.75">
+      <c r="A514" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C514" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D514" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E514" s="29">
+        <v>-200</v>
+      </c>
+      <c r="F514" s="30"/>
+      <c r="G514" s="15"/>
+      <c r="H514" s="1"/>
+      <c r="I514" s="1"/>
+    </row>
+    <row r="515" ht="12.75">
+      <c r="A515" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C515" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D515" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E515" s="29">
+        <v>-2000</v>
+      </c>
+      <c r="F515" s="30"/>
+      <c r="G515" s="15"/>
+      <c r="H515" s="1"/>
+      <c r="I515" s="1"/>
+    </row>
+    <row r="516" ht="12.75">
+      <c r="A516" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C516" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D516" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="E516" s="29">
+        <v>-1000</v>
+      </c>
+      <c r="F516" s="30"/>
+      <c r="G516" s="15"/>
+      <c r="H516" s="1"/>
+      <c r="I516" s="1"/>
+    </row>
+    <row r="517" ht="12.75">
+      <c r="A517" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C517" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D517" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E517" s="33">
+        <v>-6000</v>
+      </c>
+      <c r="F517" s="30"/>
+      <c r="G517" s="15"/>
+      <c r="H517" s="1"/>
+      <c r="I517" s="1"/>
+    </row>
+    <row r="518" ht="12.75">
+      <c r="A518" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C518" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D518" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E518" s="33">
+        <v>0</v>
+      </c>
+      <c r="F518" s="30"/>
+      <c r="G518" s="15"/>
+      <c r="H518" s="1"/>
+      <c r="I518" s="1"/>
+    </row>
+    <row r="519" ht="12.75">
+      <c r="A519" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C519" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D519" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E519" s="29">
+        <v>0</v>
+      </c>
+      <c r="F519" s="30"/>
+      <c r="G519" s="15"/>
+      <c r="H519" s="1"/>
+      <c r="I519" s="1"/>
+    </row>
+    <row r="520" ht="12.75">
+      <c r="A520" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C520" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D520" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="E520" s="42">
+        <v>0</v>
+      </c>
+      <c r="F520" s="30"/>
+      <c r="G520" s="15"/>
+      <c r="H520" s="1"/>
+      <c r="I520" s="1"/>
+    </row>
+    <row r="521" ht="12.75">
+      <c r="A521" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C521" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D521" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E521" s="33">
+        <v>0</v>
+      </c>
+      <c r="F521" s="30"/>
+      <c r="G521" s="15"/>
+      <c r="H521" s="1"/>
+      <c r="I521" s="1"/>
+    </row>
+    <row r="522" ht="12.75">
+      <c r="A522" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C522" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D522" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E522" s="33">
+        <v>-500</v>
+      </c>
+      <c r="F522" s="30"/>
+      <c r="G522" s="15"/>
+      <c r="H522" s="1"/>
+      <c r="I522" s="1"/>
+    </row>
+    <row r="523" ht="12.75">
+      <c r="A523" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C523" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D523" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="E523" s="44">
+        <v>-5000</v>
+      </c>
+      <c r="F523" s="30"/>
+      <c r="G523" s="15"/>
+      <c r="H523" s="1"/>
+      <c r="I523" s="1"/>
+    </row>
+    <row r="524" ht="12.75">
+      <c r="A524" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C524" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D524" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E524" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F524" s="30"/>
+      <c r="G524" s="15"/>
+      <c r="H524" s="1"/>
+      <c r="I524" s="1"/>
+    </row>
+    <row r="525" ht="12.75">
+      <c r="A525" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C525" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D525" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E525" s="33">
+        <v>-150</v>
+      </c>
+      <c r="F525" s="30"/>
+      <c r="G525" s="15"/>
+      <c r="H525" s="1"/>
+      <c r="I525" s="1"/>
+    </row>
+    <row r="526" ht="12.75">
+      <c r="A526" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C526" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D526" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E526" s="33">
+        <v>-450</v>
+      </c>
+      <c r="F526" s="30"/>
+      <c r="G526" s="15"/>
+      <c r="H526" s="1"/>
+      <c r="I526" s="1"/>
+    </row>
+    <row r="527" ht="12.75">
+      <c r="A527" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C527" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D527" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E527" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F527" s="30"/>
+      <c r="G527" s="15"/>
+      <c r="H527" s="1"/>
+      <c r="I527" s="1"/>
+    </row>
+    <row r="528" ht="12.75">
+      <c r="A528" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C528" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D528" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E528" s="33">
+        <v>-150</v>
+      </c>
+      <c r="F528" s="30"/>
+      <c r="G528" s="15"/>
+      <c r="H528" s="1"/>
+      <c r="I528" s="1"/>
+    </row>
+    <row r="529" ht="12.75">
+      <c r="A529" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C529" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D529" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E529" s="33">
+        <v>-800</v>
+      </c>
+      <c r="F529" s="30"/>
+      <c r="G529" s="15"/>
+      <c r="H529" s="1"/>
+      <c r="I529" s="1"/>
+    </row>
+    <row r="530" ht="12.75">
+      <c r="A530" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C530" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D530" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E530" s="33">
+        <v>-150</v>
+      </c>
+      <c r="F530" s="30"/>
+      <c r="G530" s="15"/>
+      <c r="H530" s="1"/>
+      <c r="I530" s="1"/>
+    </row>
+    <row r="531" ht="12.75">
+      <c r="A531" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C531" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D531" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E531" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F531" s="30"/>
+      <c r="G531" s="15"/>
+      <c r="H531" s="1"/>
+      <c r="I531" s="1"/>
+    </row>
+    <row r="532" ht="12.75">
+      <c r="A532" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C532" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D532" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E532" s="31">
+        <v>0</v>
+      </c>
+      <c r="F532" s="30"/>
+      <c r="G532" s="15"/>
+      <c r="H532" s="1"/>
+      <c r="I532" s="1"/>
+    </row>
+    <row r="533" ht="12.75">
+      <c r="A533" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C533" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D533" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E533" s="31">
+        <v>0</v>
+      </c>
+      <c r="F533" s="30"/>
+      <c r="G533" s="15"/>
+      <c r="H533" s="1"/>
+      <c r="I533" s="1"/>
+    </row>
+    <row r="534" ht="12.75">
+      <c r="A534" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C534" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D534" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E534" s="31">
+        <v>0</v>
+      </c>
+      <c r="F534" s="30"/>
+      <c r="G534" s="15"/>
+      <c r="H534" s="1"/>
+      <c r="I534" s="1"/>
+    </row>
+    <row r="535" ht="12.75">
+      <c r="A535" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C535" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D535" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E535" s="31">
+        <v>0</v>
+      </c>
+      <c r="F535" s="30"/>
+      <c r="G535" s="15"/>
+      <c r="H535" s="1"/>
+      <c r="I535" s="1"/>
+    </row>
+    <row r="536" ht="12.75">
+      <c r="A536" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C536" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D536" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E536" s="31">
+        <v>0</v>
+      </c>
+      <c r="F536" s="30"/>
+      <c r="G536" s="15"/>
+      <c r="H536" s="1"/>
+      <c r="I536" s="1"/>
+    </row>
+    <row r="537" ht="12.75">
+      <c r="A537" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C537" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D537" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E537" s="31">
+        <v>0</v>
+      </c>
+      <c r="F537" s="30"/>
+      <c r="G537" s="15"/>
+      <c r="H537" s="1"/>
+      <c r="I537" s="1"/>
+    </row>
+    <row r="538" ht="12.75">
+      <c r="A538" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C538" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D538" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E538" s="31">
+        <v>0</v>
+      </c>
+      <c r="F538" s="30"/>
+      <c r="G538" s="15"/>
+      <c r="H538" s="1"/>
+      <c r="I538" s="1"/>
+    </row>
+    <row r="539" ht="12.75">
+      <c r="A539" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C539" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D539" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E539" s="31">
+        <v>0</v>
+      </c>
+      <c r="F539" s="30"/>
+      <c r="G539" s="15"/>
+      <c r="H539" s="1"/>
+      <c r="I539" s="1"/>
+    </row>
+    <row r="540" ht="12.75">
+      <c r="A540" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C540" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D540" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E540" s="33">
+        <v>-300</v>
+      </c>
+      <c r="F540" s="30"/>
+      <c r="G540" s="15"/>
+      <c r="H540" s="1"/>
+      <c r="I540" s="1"/>
+    </row>
+    <row r="541" ht="12.75">
+      <c r="A541" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C541" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D541" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E541" s="33">
+        <v>-200</v>
+      </c>
+      <c r="F541" s="30"/>
+      <c r="G541" s="15"/>
+      <c r="H541" s="1"/>
+      <c r="I541" s="1"/>
+    </row>
+    <row r="542" ht="12.75">
+      <c r="A542" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C542" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D542" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E542" s="33">
+        <v>-500</v>
+      </c>
+      <c r="F542" s="30"/>
+      <c r="G542" s="15"/>
+      <c r="H542" s="1"/>
+      <c r="I542" s="1"/>
+    </row>
+    <row r="543" ht="12.75">
+      <c r="A543" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C543" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D543" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E543" s="33">
+        <v>-100</v>
+      </c>
+      <c r="F543" s="30"/>
+      <c r="G543" s="15"/>
+      <c r="H543" s="1"/>
+      <c r="I543" s="1"/>
+    </row>
+    <row r="544" ht="12.75">
+      <c r="A544" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C544" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D544" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E544" s="33">
+        <v>-300</v>
+      </c>
+      <c r="F544" s="30"/>
+      <c r="G544" s="15"/>
+      <c r="H544" s="1"/>
+      <c r="I544" s="1"/>
+    </row>
+    <row r="545" ht="12.75">
+      <c r="A545" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C545" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D545" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E545" s="33">
+        <v>-1500</v>
+      </c>
+      <c r="F545" s="30"/>
+      <c r="G545" s="15"/>
+      <c r="H545" s="1"/>
+      <c r="I545" s="1"/>
+    </row>
+    <row r="546" ht="12.75">
+      <c r="A546" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C546" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D546" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E546" s="33">
+        <v>-500</v>
+      </c>
+      <c r="F546" s="30"/>
+      <c r="G546" s="15"/>
+      <c r="H546" s="1"/>
+      <c r="I546" s="1"/>
+    </row>
+    <row r="547" ht="12.75">
+      <c r="A547" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C547" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D547" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E547" s="33">
+        <v>-300</v>
+      </c>
+      <c r="F547" s="30"/>
+      <c r="G547" s="15"/>
+      <c r="H547" s="1"/>
+      <c r="I547" s="1"/>
+    </row>
+    <row r="548" ht="12.75">
+      <c r="A548" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C548" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D548" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E548" s="33">
+        <v>-300</v>
+      </c>
+      <c r="F548" s="30"/>
+      <c r="G548" s="15"/>
+      <c r="H548" s="1"/>
+      <c r="I548" s="1"/>
+    </row>
+    <row r="549" ht="12.75">
+      <c r="A549" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C549" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D549" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E549" s="33">
+        <v>-500</v>
+      </c>
+      <c r="F549" s="30"/>
+      <c r="G549" s="15"/>
+      <c r="H549" s="1"/>
+      <c r="I549" s="1"/>
+    </row>
+    <row r="550" ht="12.75">
+      <c r="A550" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C550" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D550" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E550" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F550" s="30"/>
+      <c r="G550" s="15"/>
+      <c r="H550" s="1"/>
+      <c r="I550" s="1"/>
+    </row>
+    <row r="551" ht="12.75">
+      <c r="A551" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C551" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D551" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E551" s="29">
+        <v>0</v>
+      </c>
+      <c r="F551" s="30"/>
+      <c r="G551" s="15"/>
+      <c r="H551" s="1"/>
+      <c r="I551" s="1"/>
+    </row>
+    <row r="552" ht="12.75">
+      <c r="A552" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C552" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D552" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E552" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F552" s="30"/>
+      <c r="G552" s="15"/>
+      <c r="H552" s="1"/>
+      <c r="I552" s="1"/>
+    </row>
+    <row r="553" ht="12.75">
+      <c r="A553" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C553" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D553" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E553" s="33">
+        <v>-7571</v>
+      </c>
+      <c r="F553" s="30"/>
+      <c r="G553" s="15"/>
+      <c r="H553" s="1"/>
+      <c r="I553" s="1"/>
+    </row>
+    <row r="554" ht="12.75">
+      <c r="A554" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C554" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D554" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E554" s="29">
+        <v>-98959</v>
+      </c>
+      <c r="F554" s="30"/>
+      <c r="G554" s="15"/>
+      <c r="H554" s="1"/>
+      <c r="I554" s="1"/>
+    </row>
+    <row r="555" ht="12.75">
+      <c r="A555" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C555" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D555" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E555" s="33">
+        <v>-15000</v>
+      </c>
+      <c r="F555" s="30"/>
+      <c r="G555" s="15"/>
+      <c r="H555" s="1"/>
+      <c r="I555" s="1"/>
+    </row>
+    <row r="556" ht="12.75">
+      <c r="A556" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C556" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D556" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E556" s="33">
+        <v>-2699</v>
+      </c>
+      <c r="F556" s="30"/>
+      <c r="G556" s="15"/>
+      <c r="H556" s="1"/>
+      <c r="I556" s="1"/>
+    </row>
+    <row r="557" ht="12.75">
+      <c r="A557" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C557" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D557" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E557" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F557" s="30"/>
+      <c r="G557" s="15"/>
+      <c r="H557" s="1"/>
+      <c r="I557" s="1"/>
+    </row>
+    <row r="558" ht="12.75">
+      <c r="A558" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C558" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D558" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E558" s="33">
+        <v>-3000</v>
+      </c>
+      <c r="F558" s="30"/>
+      <c r="G558" s="15"/>
+      <c r="H558" s="1"/>
+      <c r="I558" s="1"/>
+    </row>
+    <row r="559" ht="12.75">
+      <c r="A559" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C559" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D559" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E559" s="33">
+        <v>-750</v>
+      </c>
+      <c r="F559" s="30"/>
+      <c r="G559" s="15"/>
+      <c r="H559" s="1"/>
+      <c r="I559" s="1"/>
+    </row>
+    <row r="560" ht="12.75">
+      <c r="A560" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C560" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D560" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E560" s="33">
+        <v>-8850</v>
+      </c>
+      <c r="F560" s="30"/>
+      <c r="G560" s="15"/>
+      <c r="H560" s="1"/>
+      <c r="I560" s="1"/>
+    </row>
+    <row r="561" ht="12.75">
+      <c r="A561" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C561" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D561" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E561" s="33">
+        <v>-9500</v>
+      </c>
+      <c r="F561" s="30"/>
+      <c r="G561" s="15"/>
+      <c r="H561" s="1"/>
+      <c r="I561" s="1"/>
+    </row>
+    <row r="562" ht="12.75">
+      <c r="A562" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C562" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D562" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E562" s="33">
+        <v>-950</v>
+      </c>
+      <c r="F562" s="30"/>
+      <c r="G562" s="15"/>
+      <c r="H562" s="1"/>
+      <c r="I562" s="1"/>
+    </row>
+    <row r="563" ht="12.75">
+      <c r="A563" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C563" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D563" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E563" s="33">
+        <v>-1500</v>
+      </c>
+      <c r="F563" s="30"/>
+      <c r="G563" s="15"/>
+      <c r="H563" s="1"/>
+      <c r="I563" s="1"/>
+    </row>
+    <row r="564" ht="12.75">
+      <c r="A564" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C564" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D564" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E564" s="33">
+        <v>-5000</v>
+      </c>
+      <c r="F564" s="30"/>
+      <c r="G564" s="15"/>
+      <c r="H564" s="1"/>
+      <c r="I564" s="1"/>
+    </row>
+    <row r="565" ht="12.75">
+      <c r="A565" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C565" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D565" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E565" s="33">
+        <v>-2300</v>
+      </c>
+      <c r="F565" s="30"/>
+      <c r="G565" s="15"/>
+      <c r="H565" s="1"/>
+      <c r="I565" s="1"/>
+    </row>
+    <row r="566" ht="12.75">
+      <c r="A566" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C566" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D566" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E566" s="33">
+        <v>-4300</v>
+      </c>
+      <c r="F566" s="30"/>
+      <c r="G566" s="15"/>
+      <c r="H566" s="1"/>
+      <c r="I566" s="1"/>
+    </row>
+    <row r="567" ht="12.75">
+      <c r="A567" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C567" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D567" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E567" s="33">
+        <v>-10950</v>
+      </c>
+      <c r="F567" s="30"/>
+      <c r="G567" s="15"/>
+      <c r="H567" s="1"/>
+      <c r="I567" s="1"/>
+    </row>
+    <row r="568" ht="12.75">
+      <c r="A568" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C568" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D568" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E568" s="33">
+        <v>0</v>
+      </c>
+      <c r="F568" s="30"/>
+      <c r="G568" s="15"/>
+      <c r="H568" s="1"/>
+      <c r="I568" s="1"/>
+    </row>
+    <row r="569" ht="12.75">
+      <c r="A569" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C569" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D569" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E569" s="33">
+        <v>0</v>
+      </c>
+      <c r="F569" s="30"/>
+      <c r="G569" s="15"/>
+      <c r="H569" s="1"/>
+      <c r="I569" s="1"/>
+    </row>
+    <row r="570" ht="12.75">
+      <c r="A570" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C570" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D570" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E570" s="33">
+        <v>0</v>
+      </c>
+      <c r="F570" s="30"/>
+      <c r="G570" s="15"/>
+      <c r="H570" s="1"/>
+      <c r="I570" s="1"/>
+    </row>
+    <row r="571" ht="12.75">
+      <c r="A571" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C571" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D571" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E571" s="33">
+        <v>0</v>
+      </c>
+      <c r="F571" s="30"/>
+      <c r="G571" s="15"/>
+      <c r="H571" s="1"/>
+      <c r="I571" s="1"/>
+    </row>
+    <row r="572" ht="12.75">
+      <c r="A572" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C572" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D572" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E572" s="33">
+        <v>-1500</v>
+      </c>
+      <c r="F572" s="30"/>
+      <c r="G572" s="15"/>
+      <c r="H572" s="1"/>
+      <c r="I572" s="1"/>
+    </row>
+    <row r="573" ht="12.75">
+      <c r="A573" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C573" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D573" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E573" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F573" s="30"/>
+      <c r="G573" s="15"/>
+      <c r="H573" s="1"/>
+      <c r="I573" s="1"/>
+    </row>
+    <row r="574" ht="12.75">
+      <c r="A574" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C574" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D574" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E574" s="33">
+        <v>-13500</v>
+      </c>
+      <c r="F574" s="30"/>
+      <c r="G574" s="15"/>
+      <c r="H574" s="1"/>
+      <c r="I574" s="1"/>
+    </row>
+    <row r="575" ht="12.75">
+      <c r="A575" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C575" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D575" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E575" s="33">
+        <v>-5000</v>
+      </c>
+      <c r="F575" s="30"/>
+      <c r="G575" s="15"/>
+      <c r="H575" s="1"/>
+      <c r="I575" s="1"/>
+    </row>
+    <row r="576" ht="12.75">
+      <c r="A576" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C576" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D576" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E576" s="33">
+        <v>-14700</v>
+      </c>
+      <c r="F576" s="30"/>
+      <c r="G576" s="15"/>
+      <c r="H576" s="1"/>
+      <c r="I576" s="1"/>
+    </row>
+    <row r="577" ht="12.75">
+      <c r="A577" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C577" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D577" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E577" s="33">
+        <v>-39900</v>
+      </c>
+      <c r="F577" s="30"/>
+      <c r="G577" s="15"/>
+      <c r="H577" s="1"/>
+      <c r="I577" s="1"/>
+    </row>
+    <row r="578" ht="12.75">
+      <c r="A578" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C578" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D578" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E578" s="33">
+        <v>-2200</v>
+      </c>
+      <c r="F578" s="30"/>
+      <c r="G578" s="15"/>
+      <c r="H578" s="1"/>
+      <c r="I578" s="1"/>
+    </row>
+    <row r="579" ht="12.75">
+      <c r="A579" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C579" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D579" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E579" s="33">
+        <v>-4000</v>
+      </c>
+      <c r="F579" s="30"/>
+      <c r="G579" s="15"/>
+      <c r="H579" s="1"/>
+      <c r="I579" s="1"/>
+    </row>
+    <row r="580" ht="12.75">
+      <c r="A580" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C580" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D580" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E580" s="33">
+        <v>-3000</v>
+      </c>
+      <c r="F580" s="30"/>
+      <c r="G580" s="15"/>
+      <c r="H580" s="1"/>
+      <c r="I580" s="1"/>
+    </row>
+    <row r="581" ht="12.75">
+      <c r="A581" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C581" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D581" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E581" s="33">
+        <v>-3000</v>
+      </c>
+      <c r="F581" s="30"/>
+      <c r="G581" s="15"/>
+      <c r="H581" s="1"/>
+      <c r="I581" s="1"/>
+    </row>
+    <row r="582" ht="12.75">
+      <c r="A582" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C582" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D582" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E582" s="33">
+        <v>-4000</v>
+      </c>
+      <c r="F582" s="30"/>
+      <c r="G582" s="15"/>
+      <c r="H582" s="1"/>
+      <c r="I582" s="1"/>
+    </row>
+    <row r="583" ht="12.75">
+      <c r="A583" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C583" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D583" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E583" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F583" s="30"/>
+      <c r="G583" s="15"/>
+      <c r="H583" s="1"/>
+      <c r="I583" s="1"/>
+    </row>
+    <row r="584" ht="12.75">
+      <c r="A584" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C584" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D584" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E584" s="32">
+        <v>-60000</v>
+      </c>
+      <c r="F584" s="30"/>
+      <c r="G584" s="15"/>
+      <c r="H584" s="1"/>
+      <c r="I584" s="1"/>
+    </row>
+    <row r="585" ht="12.75">
+      <c r="A585" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C585" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D585" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="E585" s="33">
+        <v>-500</v>
+      </c>
+      <c r="F585" s="30"/>
+      <c r="G585" s="15"/>
+      <c r="H585" s="1"/>
+      <c r="I585" s="1"/>
+    </row>
+    <row r="586" ht="12.75">
+      <c r="A586" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C586" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D586" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E586" s="29">
+        <v>0</v>
+      </c>
+      <c r="F586" s="30"/>
+      <c r="G586" s="15"/>
+      <c r="H586" s="1"/>
+      <c r="I586" s="1"/>
+    </row>
+    <row r="587" ht="12.75">
+      <c r="A587" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C587" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D587" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E587" s="29">
+        <v>-40000</v>
+      </c>
+      <c r="F587" s="30"/>
+      <c r="G587" s="15"/>
+      <c r="H587" s="1"/>
+      <c r="I587" s="1"/>
+    </row>
+    <row r="588" ht="12.75">
+      <c r="A588" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C588" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D588" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E588" s="29">
+        <v>-37000</v>
+      </c>
+      <c r="F588" s="30"/>
+      <c r="G588" s="15"/>
+      <c r="H588" s="1"/>
+      <c r="I588" s="1"/>
+    </row>
+    <row r="589" ht="12.75">
+      <c r="A589" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C589" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D589" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E589" s="29">
+        <v>-2000</v>
+      </c>
+      <c r="F589" s="30"/>
+      <c r="G589" s="15"/>
+      <c r="H589" s="1"/>
+      <c r="I589" s="1"/>
+    </row>
+    <row r="590" ht="12.75">
+      <c r="A590" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C590" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D590" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E590" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F590" s="30"/>
+      <c r="G590" s="15"/>
+      <c r="H590" s="1"/>
+      <c r="I590" s="1"/>
+    </row>
+    <row r="591" ht="12.75">
+      <c r="A591" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C591" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D591" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E591" s="33">
+        <v>-6000</v>
+      </c>
+      <c r="F591" s="30"/>
+      <c r="G591" s="15"/>
+      <c r="H591" s="1"/>
+      <c r="I591" s="1"/>
+    </row>
+    <row r="592" ht="12.75">
+      <c r="A592" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C592" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D592" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E592" s="33">
+        <v>-250</v>
+      </c>
+      <c r="F592" s="30"/>
+      <c r="G592" s="15"/>
+      <c r="H592" s="1"/>
+      <c r="I592" s="1"/>
+    </row>
+    <row r="593" ht="12.75">
+      <c r="A593" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C593" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D593" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E593" s="33">
+        <v>-5000</v>
+      </c>
+      <c r="F593" s="30"/>
+      <c r="G593" s="15"/>
+      <c r="H593" s="1"/>
+      <c r="I593" s="1"/>
+    </row>
+    <row r="594" ht="12.75">
+      <c r="A594" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C594" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D594" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E594" s="33">
+        <v>-500</v>
+      </c>
+      <c r="F594" s="30"/>
+      <c r="G594" s="15"/>
+      <c r="H594" s="1"/>
+      <c r="I594" s="1"/>
+    </row>
+    <row r="595" ht="12.75">
+      <c r="A595" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C595" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D595" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E595" s="29">
+        <v>-3525</v>
+      </c>
+      <c r="F595" s="30"/>
+      <c r="G595" s="15"/>
+      <c r="H595" s="1"/>
+      <c r="I595" s="1"/>
+    </row>
+    <row r="596" ht="12.75">
+      <c r="A596" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C596" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D596" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E596" s="45">
+        <v>0</v>
+      </c>
+      <c r="F596" s="30"/>
+      <c r="G596" s="15"/>
+      <c r="H596" s="1"/>
+      <c r="I596" s="1"/>
+    </row>
+    <row r="597" ht="12.75">
+      <c r="A597" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C597" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D597" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E597" s="33">
+        <v>-375</v>
+      </c>
+      <c r="F597" s="30"/>
+      <c r="G597" s="15"/>
+      <c r="H597" s="1"/>
+      <c r="I597" s="1"/>
+    </row>
+    <row r="598" ht="12.75">
+      <c r="A598" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C598" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D598" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E598" s="33">
+        <v>-8417</v>
+      </c>
+      <c r="F598" s="30"/>
+      <c r="G598" s="15"/>
+      <c r="H598" s="1"/>
+      <c r="I598" s="1"/>
+    </row>
+    <row r="599" ht="12.75">
+      <c r="A599" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C599" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D599" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E599" s="29">
+        <v>-110016</v>
+      </c>
+      <c r="F599" s="30"/>
+      <c r="G599" s="15"/>
+      <c r="H599" s="1"/>
+      <c r="I599" s="1"/>
+    </row>
+    <row r="600" ht="12.75">
+      <c r="A600" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C600" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D600" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E600" s="33">
+        <v>-2624</v>
+      </c>
+      <c r="F600" s="30"/>
+      <c r="G600" s="15"/>
+      <c r="H600" s="1"/>
+      <c r="I600" s="1"/>
+    </row>
+    <row r="601" ht="12.75">
+      <c r="A601" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C601" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D601" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E601" s="33">
+        <v>-15000</v>
+      </c>
+      <c r="F601" s="30"/>
+      <c r="G601" s="15"/>
+      <c r="H601" s="1"/>
+      <c r="I601" s="1"/>
+    </row>
+    <row r="602" ht="12.75">
+      <c r="A602" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C602" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D602" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E602" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F602" s="30"/>
+      <c r="G602" s="15"/>
+      <c r="H602" s="1"/>
+      <c r="I602" s="1"/>
+    </row>
+    <row r="603" ht="12.75">
+      <c r="A603" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C603" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D603" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="E603" s="44">
+        <v>-1000</v>
+      </c>
+      <c r="F603" s="30"/>
+      <c r="G603" s="15"/>
+      <c r="H603" s="1"/>
+      <c r="I603" s="1"/>
+    </row>
+    <row r="604" ht="12.75">
+      <c r="A604" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C604" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D604" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="E604" s="44">
+        <v>-2000</v>
+      </c>
+      <c r="F604" s="30"/>
+      <c r="G604" s="15"/>
+      <c r="H604" s="1"/>
+      <c r="I604" s="1"/>
+    </row>
+    <row r="605" ht="12.75">
+      <c r="A605" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C605" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D605" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E605" s="29">
+        <v>-3500</v>
+      </c>
+      <c r="F605" s="30"/>
+      <c r="G605" s="15"/>
+      <c r="H605" s="1"/>
+      <c r="I605" s="1"/>
+    </row>
+    <row r="606" ht="12.75">
+      <c r="A606" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C606" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D606" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E606" s="29">
+        <v>0</v>
+      </c>
+      <c r="F606" s="30"/>
+      <c r="G606" s="15"/>
+      <c r="H606" s="1"/>
+      <c r="I606" s="1"/>
+    </row>
+    <row r="607" ht="12.75">
+      <c r="A607" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C607" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D607" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E607" s="29">
+        <v>-1000</v>
+      </c>
+      <c r="F607" s="30"/>
+      <c r="G607" s="15"/>
+      <c r="H607" s="1"/>
+      <c r="I607" s="1"/>
+    </row>
+    <row r="608" ht="12.75">
+      <c r="A608" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C608" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D608" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E608" s="29">
+        <v>-13200</v>
+      </c>
+      <c r="F608" s="30"/>
+      <c r="G608" s="15"/>
+      <c r="H608" s="1"/>
+      <c r="I608" s="1"/>
+    </row>
+    <row r="609" ht="12.75">
+      <c r="A609" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C609" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D609" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E609" s="29">
+        <v>-4000</v>
+      </c>
+      <c r="F609" s="30"/>
+      <c r="G609" s="15"/>
+      <c r="H609" s="1"/>
+      <c r="I609" s="1"/>
+    </row>
+    <row r="610" ht="12.75">
+      <c r="A610" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C610" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D610" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E610" s="29">
+        <v>-3000</v>
+      </c>
+      <c r="F610" s="30"/>
+      <c r="G610" s="15"/>
+      <c r="H610" s="1"/>
+      <c r="I610" s="1"/>
+    </row>
+    <row r="611" ht="12.75">
+      <c r="A611" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C611" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D611" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E611" s="29">
+        <v>-1500</v>
+      </c>
+      <c r="F611" s="30"/>
+      <c r="G611" s="15"/>
+      <c r="H611" s="1"/>
+      <c r="I611" s="1"/>
+    </row>
+    <row r="612" ht="12.75">
+      <c r="A612" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C612" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D612" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E612" s="29">
+        <v>-2000</v>
+      </c>
+      <c r="F612" s="30"/>
+      <c r="G612" s="15"/>
+      <c r="H612" s="1"/>
+      <c r="I612" s="1"/>
+    </row>
+    <row r="613" ht="12.75">
+      <c r="A613" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C613" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D613" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E613" s="29">
+        <v>-3000</v>
+      </c>
+      <c r="F613" s="30"/>
+      <c r="G613" s="15"/>
+      <c r="H613" s="1"/>
+      <c r="I613" s="1"/>
+    </row>
+    <row r="614" ht="12.75">
+      <c r="A614" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C614" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D614" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E614" s="29">
+        <v>-2500</v>
+      </c>
+      <c r="F614" s="30"/>
+      <c r="G614" s="15"/>
+      <c r="H614" s="1"/>
+      <c r="I614" s="1"/>
+    </row>
+    <row r="615" ht="12.75">
+      <c r="A615" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C615" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D615" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E615" s="29">
+        <v>-1000</v>
+      </c>
+      <c r="F615" s="30"/>
+      <c r="G615" s="15"/>
+      <c r="H615" s="1"/>
+      <c r="I615" s="1"/>
+    </row>
+    <row r="616" ht="12.75">
+      <c r="A616" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C616" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D616" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E616" s="29">
+        <v>-1000</v>
+      </c>
+      <c r="F616" s="30"/>
+      <c r="G616" s="15"/>
+      <c r="H616" s="1"/>
+      <c r="I616" s="1"/>
+    </row>
+    <row r="617" ht="12.75">
+      <c r="A617" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C617" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D617" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E617" s="29">
+        <v>-5000</v>
+      </c>
+      <c r="F617" s="30"/>
+      <c r="G617" s="15"/>
+      <c r="H617" s="1"/>
+      <c r="I617" s="1"/>
+    </row>
+    <row r="618" ht="12.75">
+      <c r="A618" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C618" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D618" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E618" s="29">
+        <v>-6000</v>
+      </c>
+      <c r="F618" s="30"/>
+      <c r="G618" s="15"/>
+      <c r="H618" s="1"/>
+      <c r="I618" s="1"/>
+    </row>
+    <row r="619" ht="12.75">
+      <c r="A619" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C619" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D619" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E619" s="33">
+        <v>-1500</v>
+      </c>
+      <c r="F619" s="30"/>
+      <c r="G619" s="15"/>
+      <c r="H619" s="1"/>
+      <c r="I619" s="1"/>
+    </row>
+    <row r="620" ht="12.75">
+      <c r="A620" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C620" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D620" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E620" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="F620" s="30"/>
+      <c r="G620" s="15"/>
+      <c r="H620" s="1"/>
+      <c r="I620" s="1"/>
+    </row>
+    <row r="621" ht="12.75">
+      <c r="A621" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C621" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D621" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E621" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="F621" s="30"/>
+      <c r="G621" s="15"/>
+      <c r="H621" s="1"/>
+      <c r="I621" s="1"/>
+    </row>
+    <row r="622" ht="12.75">
+      <c r="A622" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C622" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D622" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E622" s="33">
+        <v>-750</v>
+      </c>
+      <c r="F622" s="30"/>
+      <c r="G622" s="15"/>
+      <c r="H622" s="1"/>
+      <c r="I622" s="1"/>
+    </row>
+    <row r="623" ht="12.75">
+      <c r="A623" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C623" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D623" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E623" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="F623" s="30"/>
+      <c r="G623" s="15"/>
+      <c r="H623" s="1"/>
+      <c r="I623" s="1"/>
+    </row>
+    <row r="624" ht="12.75">
+      <c r="A624" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C624" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D624" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E624" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="F624" s="30"/>
+      <c r="G624" s="15"/>
+      <c r="H624" s="1"/>
+      <c r="I624" s="1"/>
+    </row>
+    <row r="625" ht="12.75">
+      <c r="A625" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C625" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D625" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E625" s="29">
+        <v>-19200</v>
+      </c>
+      <c r="F625" s="30"/>
+      <c r="G625" s="15"/>
+      <c r="H625" s="1"/>
+      <c r="I625" s="1"/>
+    </row>
+    <row r="626" ht="12.75">
+      <c r="A626" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C626" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D626" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E626" s="33">
+        <v>-1296</v>
+      </c>
+      <c r="F626" s="30"/>
+      <c r="G626" s="15"/>
+      <c r="H626" s="1"/>
+      <c r="I626" s="1"/>
+    </row>
+    <row r="627" ht="12.75">
+      <c r="A627" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C627" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D627" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E627" s="33">
+        <v>0</v>
+      </c>
+      <c r="F627" s="30"/>
+      <c r="G627" s="15"/>
+      <c r="H627" s="1"/>
+      <c r="I627" s="1"/>
+    </row>
+    <row r="628" ht="12.75">
+      <c r="A628" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C628" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D628" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E628" s="33">
+        <v>0</v>
+      </c>
+      <c r="F628" s="30"/>
+      <c r="G628" s="15"/>
+      <c r="H628" s="1"/>
+      <c r="I628" s="1"/>
+    </row>
+    <row r="629" ht="12.75">
+      <c r="A629" s="1"/>
+      <c r="B629" s="1"/>
+      <c r="C629" s="7"/>
+      <c r="D629" s="46"/>
+      <c r="E629" s="13"/>
+      <c r="F629" s="15"/>
+      <c r="G629" s="15"/>
+      <c r="H629" s="1"/>
+      <c r="I629" s="1"/>
+    </row>
+    <row r="630" ht="12.75">
+      <c r="A630" s="1"/>
+      <c r="B630" s="1"/>
+      <c r="C630" s="7"/>
+      <c r="D630" s="46"/>
+      <c r="E630" s="13"/>
+      <c r="F630" s="15"/>
+      <c r="G630" s="15"/>
+      <c r="H630" s="1"/>
+      <c r="I630" s="1"/>
+    </row>
+    <row r="631" ht="12.75">
+      <c r="A631" s="1"/>
+      <c r="B631" s="1"/>
+      <c r="C631" s="7"/>
+      <c r="D631" s="12"/>
+      <c r="E631" s="13"/>
+      <c r="F631" s="15"/>
+      <c r="G631" s="15"/>
+      <c r="H631" s="1"/>
+      <c r="I631" s="1"/>
+    </row>
+    <row r="632" ht="12.75">
+      <c r="A632" s="1"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="7"/>
+      <c r="D632" s="46"/>
+      <c r="E632" s="13"/>
+      <c r="F632" s="15"/>
+      <c r="G632" s="15"/>
+      <c r="H632" s="1"/>
+      <c r="I632" s="1"/>
+    </row>
+    <row r="633" ht="12.75">
+      <c r="A633" s="1"/>
+      <c r="B633" s="1"/>
+      <c r="C633" s="7"/>
+      <c r="D633" s="46"/>
+      <c r="E633" s="13"/>
+      <c r="F633" s="15"/>
+      <c r="G633" s="15"/>
+      <c r="H633" s="1"/>
+      <c r="I633" s="1"/>
+    </row>
+    <row r="634" ht="12.75">
+      <c r="A634" s="1"/>
+      <c r="B634" s="1"/>
+      <c r="C634" s="7"/>
+      <c r="D634" s="46"/>
+      <c r="E634" s="13"/>
+      <c r="F634" s="15"/>
+      <c r="G634" s="15"/>
+      <c r="H634" s="1"/>
+      <c r="I634" s="1"/>
+    </row>
+    <row r="635" ht="12.75">
+      <c r="A635" s="1"/>
+      <c r="B635" s="1"/>
+      <c r="C635" s="7"/>
+      <c r="D635" s="46"/>
+      <c r="E635" s="13"/>
+      <c r="F635" s="15"/>
+      <c r="G635" s="15"/>
+      <c r="H635" s="1"/>
+      <c r="I635" s="1"/>
+    </row>
+    <row r="636" ht="12.75">
+      <c r="A636" s="1"/>
+      <c r="B636" s="1"/>
+      <c r="C636" s="7"/>
+      <c r="D636" s="46"/>
+      <c r="E636" s="13"/>
+      <c r="F636" s="15"/>
+      <c r="G636" s="15"/>
+      <c r="H636" s="1"/>
+      <c r="I636" s="1"/>
+    </row>
+    <row r="637" ht="12.75">
+      <c r="A637" s="1"/>
+      <c r="B637" s="1"/>
+      <c r="C637" s="7"/>
+      <c r="D637" s="46"/>
+      <c r="E637" s="13"/>
+      <c r="F637" s="15"/>
+      <c r="G637" s="15"/>
+      <c r="H637" s="1"/>
+      <c r="I637" s="1"/>
+    </row>
+    <row r="638" ht="12.75">
+      <c r="A638" s="1"/>
+      <c r="B638" s="1"/>
+      <c r="C638" s="7"/>
+      <c r="D638" s="46"/>
+      <c r="E638" s="13"/>
+      <c r="F638" s="15"/>
+      <c r="G638" s="15"/>
+      <c r="H638" s="1"/>
+      <c r="I638" s="1"/>
+    </row>
+    <row r="639" ht="12.75">
+      <c r="A639" s="1"/>
+      <c r="B639" s="1"/>
+      <c r="C639" s="7"/>
+      <c r="D639" s="46"/>
+      <c r="E639" s="13"/>
+      <c r="F639" s="15"/>
+      <c r="G639" s="15"/>
+      <c r="H639" s="1"/>
+      <c r="I639" s="1"/>
+    </row>
+    <row r="640" ht="12.75">
+      <c r="A640" s="1"/>
+      <c r="B640" s="1"/>
+      <c r="C640" s="7"/>
+      <c r="D640" s="46"/>
+      <c r="E640" s="13"/>
+      <c r="F640" s="15"/>
+      <c r="G640" s="15"/>
+      <c r="H640" s="1"/>
+      <c r="I640" s="1"/>
+    </row>
+    <row r="641" ht="12.75">
+      <c r="A641" s="1"/>
+      <c r="B641" s="1"/>
+      <c r="C641" s="7"/>
+      <c r="D641" s="47"/>
+      <c r="E641" s="48"/>
+      <c r="F641" s="15"/>
+      <c r="G641" s="15"/>
+      <c r="H641" s="1"/>
+      <c r="I641" s="1"/>
+    </row>
+    <row r="642" ht="12.75">
+      <c r="A642" s="1"/>
+      <c r="B642" s="1"/>
+      <c r="C642" s="7"/>
+      <c r="D642" s="46"/>
+      <c r="E642" s="13"/>
+      <c r="F642" s="15"/>
+      <c r="G642" s="15"/>
+      <c r="H642" s="1"/>
+      <c r="I642" s="1"/>
+    </row>
+    <row r="643" ht="12.75">
+      <c r="A643" s="1"/>
+      <c r="B643" s="1"/>
+      <c r="C643" s="7"/>
+      <c r="D643" s="49"/>
+      <c r="E643" s="16"/>
+      <c r="F643" s="15"/>
+      <c r="G643" s="15"/>
+      <c r="H643" s="1"/>
+      <c r="I643" s="1"/>
+    </row>
+    <row r="644" ht="12.75">
+      <c r="A644" s="1"/>
+      <c r="B644" s="1"/>
+      <c r="C644" s="7"/>
+      <c r="D644" s="46"/>
+      <c r="E644" s="13"/>
+      <c r="F644" s="15"/>
+      <c r="G644" s="15"/>
+      <c r="H644" s="1"/>
+      <c r="I644" s="1"/>
+    </row>
+    <row r="645" ht="12.75">
+      <c r="A645" s="1"/>
+      <c r="B645" s="1"/>
+      <c r="C645" s="7"/>
+      <c r="D645" s="46"/>
+      <c r="E645" s="13"/>
+      <c r="F645" s="15"/>
+      <c r="G645" s="15"/>
+      <c r="H645" s="1"/>
+      <c r="I645" s="1"/>
+    </row>
+    <row r="646" ht="12.75">
+      <c r="A646" s="1"/>
+      <c r="B646" s="1"/>
+      <c r="C646" s="7"/>
+      <c r="D646" s="12"/>
+      <c r="E646" s="13"/>
+      <c r="F646" s="15"/>
+      <c r="G646" s="15"/>
+      <c r="H646" s="1"/>
+      <c r="I646" s="1"/>
+    </row>
+    <row r="647" ht="12.75">
+      <c r="A647" s="1"/>
+      <c r="B647" s="1"/>
+      <c r="C647" s="7"/>
+      <c r="D647" s="46"/>
+      <c r="E647" s="13"/>
+      <c r="F647" s="15"/>
+      <c r="G647" s="15"/>
+      <c r="H647" s="1"/>
+      <c r="I647" s="1"/>
+    </row>
+    <row r="648" ht="12.75">
+      <c r="A648" s="1"/>
+      <c r="B648" s="1"/>
+      <c r="C648" s="7"/>
+      <c r="D648" s="47"/>
+      <c r="E648" s="48"/>
+      <c r="F648" s="15"/>
+      <c r="G648" s="15"/>
+      <c r="H648" s="1"/>
+      <c r="I648" s="1"/>
+    </row>
+    <row r="649" ht="12.75">
+      <c r="A649" s="1"/>
+      <c r="B649" s="1"/>
+      <c r="C649" s="7"/>
+      <c r="D649" s="47"/>
+      <c r="E649" s="48"/>
+      <c r="F649" s="15"/>
+      <c r="G649" s="15"/>
+      <c r="H649" s="1"/>
+      <c r="I649" s="1"/>
+    </row>
+    <row r="650" ht="12.75">
+      <c r="A650" s="1"/>
+      <c r="B650" s="1"/>
+      <c r="C650" s="7"/>
+      <c r="D650" s="47"/>
+      <c r="E650" s="48"/>
+      <c r="F650" s="15"/>
+      <c r="G650" s="15"/>
+      <c r="H650" s="1"/>
+      <c r="I650" s="1"/>
+    </row>
+    <row r="651" ht="12.75">
+      <c r="A651" s="1"/>
+      <c r="B651" s="1"/>
+      <c r="C651" s="7"/>
+      <c r="D651" s="46"/>
+      <c r="E651" s="13"/>
+      <c r="F651" s="15"/>
+      <c r="G651" s="15"/>
+      <c r="H651" s="1"/>
+      <c r="I651" s="1"/>
+    </row>
+    <row r="652" ht="12.75">
+      <c r="A652" s="1"/>
+      <c r="B652" s="1"/>
+      <c r="C652" s="7"/>
+      <c r="D652" s="12"/>
+      <c r="E652" s="13"/>
+      <c r="F652" s="15"/>
+      <c r="G652" s="15"/>
+      <c r="H652" s="1"/>
+      <c r="I652" s="1"/>
+    </row>
+    <row r="653" ht="12.75">
+      <c r="A653" s="1"/>
+      <c r="B653" s="1"/>
+      <c r="C653" s="7"/>
+      <c r="D653" s="46"/>
+      <c r="E653" s="13"/>
+      <c r="F653" s="15"/>
+      <c r="G653" s="15"/>
+      <c r="H653" s="1"/>
+      <c r="I653" s="1"/>
+    </row>
+    <row r="654" ht="12.75">
+      <c r="A654" s="1"/>
+      <c r="B654" s="1"/>
+      <c r="C654" s="7"/>
+      <c r="D654" s="46"/>
+      <c r="E654" s="13"/>
+      <c r="F654" s="15"/>
+      <c r="G654" s="15"/>
+      <c r="H654" s="1"/>
+      <c r="I654" s="1"/>
+    </row>
+    <row r="655" ht="12.75">
+      <c r="A655" s="1"/>
+      <c r="B655" s="1"/>
+      <c r="C655" s="7"/>
+      <c r="D655" s="46"/>
+      <c r="E655" s="13"/>
+      <c r="F655" s="15"/>
+      <c r="G655" s="15"/>
+      <c r="H655" s="1"/>
+      <c r="I655" s="1"/>
+    </row>
+    <row r="656" ht="12.75">
+      <c r="A656" s="1"/>
+      <c r="B656" s="1"/>
+      <c r="C656" s="7"/>
+      <c r="D656" s="46"/>
+      <c r="E656" s="13"/>
+      <c r="F656" s="15"/>
+      <c r="G656" s="15"/>
+      <c r="H656" s="1"/>
+      <c r="I656" s="1"/>
+    </row>
+    <row r="657" ht="12.75">
+      <c r="A657" s="1"/>
+      <c r="B657" s="1"/>
+      <c r="C657" s="7"/>
+      <c r="D657" s="46"/>
+      <c r="E657" s="13"/>
+      <c r="F657" s="15"/>
+      <c r="G657" s="15"/>
+      <c r="H657" s="1"/>
+      <c r="I657" s="1"/>
+    </row>
+    <row r="658" ht="12.75">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="7"/>
+      <c r="D658" s="46"/>
+      <c r="E658" s="13"/>
+      <c r="F658" s="15"/>
+      <c r="G658" s="15"/>
+      <c r="H658" s="1"/>
+      <c r="I658" s="1"/>
+    </row>
+    <row r="659" ht="12.75">
+      <c r="A659" s="1"/>
+      <c r="B659" s="1"/>
+      <c r="C659" s="7"/>
+      <c r="D659" s="12"/>
+      <c r="E659" s="13"/>
+      <c r="F659" s="15"/>
+      <c r="G659" s="15"/>
+      <c r="H659" s="1"/>
+      <c r="I659" s="1"/>
+    </row>
+    <row r="660" ht="12.75">
+      <c r="A660" s="1"/>
+      <c r="B660" s="1"/>
+      <c r="C660" s="7"/>
+      <c r="D660" s="47"/>
+      <c r="E660" s="48"/>
+      <c r="F660" s="15"/>
+      <c r="G660" s="15"/>
+      <c r="H660" s="1"/>
+      <c r="I660" s="1"/>
+    </row>
+    <row r="661" ht="12.75">
+      <c r="A661" s="1"/>
+      <c r="B661" s="1"/>
+      <c r="C661" s="7"/>
+      <c r="D661" s="47"/>
+      <c r="E661" s="48"/>
+      <c r="F661" s="15"/>
+      <c r="G661" s="15"/>
+      <c r="H661" s="1"/>
+      <c r="I661" s="1"/>
+    </row>
+    <row r="662" ht="12.75">
+      <c r="A662" s="1"/>
+      <c r="B662" s="1"/>
+      <c r="C662" s="7"/>
+      <c r="D662" s="1"/>
+      <c r="E662" s="1"/>
+      <c r="F662" s="6"/>
+      <c r="G662" s="1"/>
+      <c r="H662" s="1"/>
+      <c r="I662" s="1"/>
+    </row>
+    <row r="663" ht="12.75">
+      <c r="A663" s="1"/>
+      <c r="B663" s="1"/>
+      <c r="C663" s="7"/>
+      <c r="D663" s="1"/>
+      <c r="E663" s="1"/>
+      <c r="F663" s="6"/>
+      <c r="G663" s="1"/>
+      <c r="H663" s="1"/>
+      <c r="I663" s="1"/>
+    </row>
+    <row r="664" ht="12.75">
+      <c r="A664" s="1"/>
+      <c r="B664" s="1"/>
+      <c r="C664" s="7"/>
+      <c r="D664" s="1"/>
+      <c r="E664" s="1"/>
+      <c r="F664" s="6"/>
+      <c r="G664" s="1"/>
+      <c r="H664" s="1"/>
+      <c r="I664" s="1"/>
+    </row>
+    <row r="665" ht="12.75">
+      <c r="A665" s="1"/>
+      <c r="B665" s="1"/>
+      <c r="C665" s="7"/>
+      <c r="D665" s="1"/>
+      <c r="E665" s="1"/>
+      <c r="F665" s="6"/>
+      <c r="G665" s="1"/>
+      <c r="H665" s="1"/>
+      <c r="I665" s="1"/>
+    </row>
+    <row r="666" ht="12.75">
+      <c r="A666" s="1"/>
+      <c r="B666" s="1"/>
+      <c r="C666" s="7"/>
+      <c r="D666" s="1"/>
+      <c r="E666" s="1"/>
+      <c r="F666" s="6"/>
+      <c r="G666" s="1"/>
+      <c r="H666" s="1"/>
+      <c r="I666" s="1"/>
+    </row>
+    <row r="667" ht="12.75">
+      <c r="A667" s="1"/>
+      <c r="B667" s="1"/>
+      <c r="C667" s="7"/>
+      <c r="D667" s="1"/>
+      <c r="E667" s="1"/>
+      <c r="F667" s="6"/>
+      <c r="G667" s="1"/>
+      <c r="H667" s="1"/>
+      <c r="I667" s="1"/>
+    </row>
+    <row r="668" ht="12.75">
+      <c r="A668" s="1"/>
+      <c r="B668" s="1"/>
+      <c r="C668" s="7"/>
+      <c r="D668" s="1"/>
+      <c r="E668" s="1"/>
+      <c r="F668" s="6"/>
+      <c r="G668" s="1"/>
+      <c r="H668" s="1"/>
+      <c r="I668" s="1"/>
+    </row>
+    <row r="669" ht="12.75">
+      <c r="A669" s="1"/>
+      <c r="B669" s="1"/>
+      <c r="C669" s="7"/>
+      <c r="D669" s="1"/>
+      <c r="E669" s="1"/>
+      <c r="F669" s="6"/>
+      <c r="G669" s="1"/>
+      <c r="H669" s="1"/>
+      <c r="I669" s="1"/>
+    </row>
+    <row r="670" ht="12.75">
+      <c r="A670" s="1"/>
+      <c r="B670" s="1"/>
+      <c r="C670" s="7"/>
+      <c r="D670" s="1"/>
+      <c r="E670" s="1"/>
+      <c r="F670" s="6"/>
+      <c r="G670" s="1"/>
+      <c r="H670" s="1"/>
+      <c r="I670" s="1"/>
+    </row>
+    <row r="671" ht="12.75">
+      <c r="A671" s="1"/>
+      <c r="B671" s="1"/>
+      <c r="C671" s="7"/>
+      <c r="D671" s="1"/>
+      <c r="E671" s="1"/>
+      <c r="F671" s="6"/>
+      <c r="G671" s="1"/>
+      <c r="H671" s="1"/>
+      <c r="I671" s="1"/>
+    </row>
+    <row r="672" ht="12.75">
+      <c r="A672" s="1"/>
+      <c r="B672" s="1"/>
+      <c r="C672" s="7"/>
+      <c r="D672" s="1"/>
+      <c r="E672" s="1"/>
+      <c r="F672" s="6"/>
+      <c r="G672" s="1"/>
+      <c r="H672" s="1"/>
+      <c r="I672" s="1"/>
+    </row>
+    <row r="673" ht="12.75">
+      <c r="A673" s="1"/>
+      <c r="B673" s="1"/>
+      <c r="C673" s="7"/>
+      <c r="D673" s="1"/>
+      <c r="E673" s="1"/>
+      <c r="F673" s="6"/>
+      <c r="G673" s="1"/>
+      <c r="H673" s="1"/>
+      <c r="I673" s="1"/>
+    </row>
+    <row r="674" ht="12.75">
+      <c r="A674" s="1"/>
+      <c r="B674" s="1"/>
+      <c r="C674" s="7"/>
+      <c r="D674" s="1"/>
+      <c r="E674" s="1"/>
+      <c r="F674" s="6"/>
+      <c r="G674" s="1"/>
+      <c r="H674" s="1"/>
+      <c r="I674" s="1"/>
+    </row>
+    <row r="675" ht="12.75">
+      <c r="A675" s="1"/>
+      <c r="B675" s="1"/>
+      <c r="C675" s="7"/>
+      <c r="D675" s="1"/>
+      <c r="E675" s="1"/>
+      <c r="F675" s="6"/>
+      <c r="G675" s="1"/>
+      <c r="H675" s="1"/>
+      <c r="I675" s="1"/>
+    </row>
+    <row r="676" ht="12.75">
+      <c r="A676" s="1"/>
+      <c r="B676" s="1"/>
+      <c r="C676" s="7"/>
+      <c r="D676" s="1"/>
+      <c r="E676" s="1"/>
+      <c r="F676" s="6"/>
+      <c r="G676" s="1"/>
+      <c r="H676" s="1"/>
+      <c r="I676" s="1"/>
+    </row>
+    <row r="677" ht="12.75">
+      <c r="A677" s="1"/>
+      <c r="B677" s="1"/>
+      <c r="C677" s="7"/>
+      <c r="D677" s="1"/>
+      <c r="E677" s="1"/>
+      <c r="F677" s="6"/>
+      <c r="G677" s="1"/>
+      <c r="H677" s="1"/>
+      <c r="I677" s="1"/>
+    </row>
+    <row r="678" ht="12.75">
+      <c r="A678" s="1"/>
+      <c r="B678" s="1"/>
+      <c r="C678" s="7"/>
+      <c r="D678" s="1"/>
+      <c r="E678" s="1"/>
+      <c r="F678" s="6"/>
+      <c r="G678" s="1"/>
+      <c r="H678" s="1"/>
+      <c r="I678" s="1"/>
+    </row>
+    <row r="679" ht="12.75">
+      <c r="A679" s="1"/>
+      <c r="B679" s="1"/>
+      <c r="C679" s="7"/>
+      <c r="D679" s="1"/>
+      <c r="E679" s="1"/>
+      <c r="F679" s="6"/>
+      <c r="G679" s="1"/>
+      <c r="H679" s="1"/>
+      <c r="I679" s="1"/>
+    </row>
+    <row r="680" ht="12.75">
+      <c r="A680" s="1"/>
+      <c r="B680" s="1"/>
+      <c r="C680" s="7"/>
+      <c r="D680" s="1"/>
+      <c r="E680" s="1"/>
+      <c r="F680" s="6"/>
+      <c r="G680" s="1"/>
+      <c r="H680" s="1"/>
+      <c r="I680" s="1"/>
+    </row>
+    <row r="681" ht="12.75">
+      <c r="A681" s="1"/>
+      <c r="B681" s="1"/>
+      <c r="C681" s="7"/>
+      <c r="D681" s="1"/>
+      <c r="E681" s="1"/>
+      <c r="F681" s="6"/>
+      <c r="G681" s="1"/>
+      <c r="H681" s="1"/>
+      <c r="I681" s="1"/>
+    </row>
+    <row r="682" ht="12.75">
+      <c r="A682" s="1"/>
+      <c r="B682" s="1"/>
+      <c r="C682" s="7"/>
+      <c r="D682" s="1"/>
+      <c r="E682" s="1"/>
+      <c r="F682" s="6"/>
+      <c r="G682" s="1"/>
+      <c r="H682" s="1"/>
+      <c r="I682" s="1"/>
+    </row>
+    <row r="683" ht="12.75">
+      <c r="A683" s="1"/>
+      <c r="B683" s="1"/>
+      <c r="C683" s="7"/>
+      <c r="D683" s="1"/>
+      <c r="E683" s="1"/>
+      <c r="F683" s="6"/>
+      <c r="G683" s="1"/>
+      <c r="H683" s="1"/>
+      <c r="I683" s="1"/>
+    </row>
+    <row r="684" ht="12.75">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="7"/>
+      <c r="D684" s="1"/>
+      <c r="E684" s="1"/>
+      <c r="F684" s="6"/>
+      <c r="G684" s="1"/>
+      <c r="H684" s="1"/>
+      <c r="I684" s="1"/>
+    </row>
+    <row r="685" ht="12.75">
+      <c r="A685" s="1"/>
+      <c r="B685" s="1"/>
+      <c r="C685" s="7"/>
+      <c r="D685" s="1"/>
+      <c r="E685" s="1"/>
+      <c r="F685" s="6"/>
+      <c r="G685" s="1"/>
+      <c r="H685" s="1"/>
+      <c r="I685" s="1"/>
+    </row>
+    <row r="686" ht="12.75">
+      <c r="A686" s="1"/>
+      <c r="B686" s="1"/>
+      <c r="C686" s="7"/>
+      <c r="D686" s="1"/>
+      <c r="E686" s="1"/>
+      <c r="F686" s="6"/>
+      <c r="G686" s="1"/>
+      <c r="H686" s="1"/>
+      <c r="I686" s="1"/>
+    </row>
+    <row r="687" ht="12.75">
+      <c r="A687" s="1"/>
+      <c r="B687" s="1"/>
+      <c r="C687" s="7"/>
+      <c r="D687" s="1"/>
+      <c r="E687" s="1"/>
+      <c r="F687" s="6"/>
+      <c r="G687" s="1"/>
+      <c r="H687" s="1"/>
+      <c r="I687" s="1"/>
+    </row>
+    <row r="688" ht="12.75">
+      <c r="A688" s="1"/>
+      <c r="B688" s="1"/>
+      <c r="C688" s="7"/>
+      <c r="D688" s="1"/>
+      <c r="E688" s="1"/>
+      <c r="F688" s="6"/>
+      <c r="G688" s="1"/>
+      <c r="H688" s="1"/>
+      <c r="I688" s="1"/>
+    </row>
+    <row r="689" ht="12.75">
+      <c r="A689" s="1"/>
+      <c r="B689" s="1"/>
+      <c r="C689" s="7"/>
+      <c r="D689" s="1"/>
+      <c r="E689" s="1"/>
+      <c r="F689" s="6"/>
+      <c r="G689" s="1"/>
+      <c r="H689" s="1"/>
+      <c r="I689" s="1"/>
+    </row>
+    <row r="690" ht="12.75">
+      <c r="A690" s="1"/>
+      <c r="B690" s="1"/>
+      <c r="C690" s="7"/>
+      <c r="D690" s="1"/>
+      <c r="E690" s="1"/>
+      <c r="F690" s="6"/>
+      <c r="G690" s="1"/>
+      <c r="H690" s="1"/>
+      <c r="I690" s="1"/>
+    </row>
+    <row r="691" ht="12.75">
+      <c r="A691" s="1"/>
+      <c r="B691" s="1"/>
+      <c r="C691" s="7"/>
+      <c r="D691" s="1"/>
+      <c r="E691" s="1"/>
+      <c r="F691" s="6"/>
+      <c r="G691" s="1"/>
+      <c r="H691" s="1"/>
+      <c r="I691" s="1"/>
+    </row>
+    <row r="692" ht="12.75">
+      <c r="A692" s="1"/>
+      <c r="B692" s="1"/>
+      <c r="C692" s="7"/>
+      <c r="D692" s="1"/>
+      <c r="E692" s="1"/>
+      <c r="F692" s="6"/>
+      <c r="G692" s="1"/>
+      <c r="H692" s="1"/>
+      <c r="I692" s="1"/>
+    </row>
+    <row r="693" ht="12.75">
+      <c r="A693" s="1"/>
+      <c r="B693" s="1"/>
+      <c r="C693" s="7"/>
+      <c r="D693" s="1"/>
+      <c r="E693" s="1"/>
+      <c r="F693" s="6"/>
+      <c r="G693" s="1"/>
+      <c r="H693" s="1"/>
+      <c r="I693" s="1"/>
+    </row>
+    <row r="694" ht="12.75">
+      <c r="A694" s="1"/>
+      <c r="B694" s="1"/>
+      <c r="C694" s="7"/>
+      <c r="D694" s="1"/>
+      <c r="E694" s="1"/>
+      <c r="F694" s="6"/>
+      <c r="G694" s="1"/>
+      <c r="H694" s="1"/>
+      <c r="I694" s="1"/>
+    </row>
+    <row r="695" ht="12.75">
+      <c r="A695" s="1"/>
+      <c r="B695" s="1"/>
+      <c r="C695" s="7"/>
+      <c r="D695" s="1"/>
+      <c r="E695" s="1"/>
+      <c r="F695" s="6"/>
+      <c r="G695" s="1"/>
+      <c r="H695" s="1"/>
+      <c r="I695" s="1"/>
+    </row>
+    <row r="696" ht="12.75">
+      <c r="A696" s="1"/>
+      <c r="B696" s="1"/>
+      <c r="C696" s="7"/>
+      <c r="D696" s="1"/>
+      <c r="E696" s="1"/>
+      <c r="F696" s="6"/>
+      <c r="G696" s="1"/>
+      <c r="H696" s="1"/>
+      <c r="I696" s="1"/>
+    </row>
+    <row r="697" ht="12.75">
+      <c r="A697" s="1"/>
+      <c r="B697" s="1"/>
+      <c r="C697" s="7"/>
+      <c r="D697" s="1"/>
+      <c r="E697" s="1"/>
+      <c r="F697" s="6"/>
+      <c r="G697" s="1"/>
+      <c r="H697" s="1"/>
+      <c r="I697" s="1"/>
+    </row>
+    <row r="698" ht="12.75">
+      <c r="A698" s="1"/>
+      <c r="B698" s="1"/>
+      <c r="C698" s="7"/>
+      <c r="D698" s="1"/>
+      <c r="E698" s="1"/>
+      <c r="F698" s="6"/>
+      <c r="G698" s="1"/>
+      <c r="H698" s="1"/>
+      <c r="I698" s="1"/>
+    </row>
+    <row r="699" ht="12.75">
+      <c r="A699" s="1"/>
+      <c r="B699" s="1"/>
+      <c r="C699" s="7"/>
+      <c r="D699" s="1"/>
+      <c r="E699" s="1"/>
+      <c r="F699" s="6"/>
+      <c r="G699" s="1"/>
+      <c r="H699" s="1"/>
+      <c r="I699" s="1"/>
+    </row>
+    <row r="700" ht="12.75">
+      <c r="A700" s="1"/>
+      <c r="B700" s="1"/>
+      <c r="C700" s="7"/>
+      <c r="D700" s="1"/>
+      <c r="E700" s="1"/>
+      <c r="F700" s="6"/>
+      <c r="G700" s="1"/>
+      <c r="H700" s="1"/>
+      <c r="I700" s="1"/>
+    </row>
+    <row r="701" ht="12.75">
+      <c r="A701" s="1"/>
+      <c r="B701" s="1"/>
+      <c r="C701" s="7"/>
+      <c r="D701" s="1"/>
+      <c r="E701" s="1"/>
+      <c r="F701" s="6"/>
+      <c r="G701" s="1"/>
+      <c r="H701" s="1"/>
+      <c r="I701" s="1"/>
+    </row>
+    <row r="702" ht="12.75">
+      <c r="A702" s="1"/>
+      <c r="B702" s="1"/>
+      <c r="C702" s="7"/>
+      <c r="D702" s="1"/>
+      <c r="E702" s="1"/>
+      <c r="F702" s="6"/>
+      <c r="G702" s="1"/>
+      <c r="H702" s="1"/>
+      <c r="I702" s="1"/>
+    </row>
+    <row r="703" ht="12.75">
+      <c r="A703" s="1"/>
+      <c r="B703" s="1"/>
+      <c r="C703" s="7"/>
+      <c r="D703" s="1"/>
+      <c r="E703" s="1"/>
+      <c r="F703" s="6"/>
+      <c r="G703" s="1"/>
+      <c r="H703" s="1"/>
+      <c r="I703" s="1"/>
+    </row>
+    <row r="704" ht="12.75">
+      <c r="A704" s="1"/>
+      <c r="B704" s="1"/>
+      <c r="C704" s="7"/>
+      <c r="D704" s="1"/>
+      <c r="E704" s="1"/>
+      <c r="F704" s="6"/>
+      <c r="G704" s="1"/>
+      <c r="H704" s="1"/>
+      <c r="I704" s="1"/>
+    </row>
+    <row r="705" ht="12.75">
+      <c r="A705" s="1"/>
+      <c r="B705" s="1"/>
+      <c r="C705" s="7"/>
+      <c r="D705" s="1"/>
+      <c r="E705" s="1"/>
+      <c r="F705" s="6"/>
+      <c r="G705" s="1"/>
+      <c r="H705" s="1"/>
+      <c r="I705" s="1"/>
+    </row>
+    <row r="706" ht="12.75">
+      <c r="A706" s="1"/>
+      <c r="B706" s="1"/>
+      <c r="C706" s="7"/>
+      <c r="D706" s="1"/>
+      <c r="E706" s="1"/>
+      <c r="F706" s="6"/>
+      <c r="G706" s="1"/>
+      <c r="H706" s="1"/>
+      <c r="I706" s="1"/>
+    </row>
+    <row r="707" ht="12.75">
+      <c r="A707" s="1"/>
+      <c r="B707" s="1"/>
+      <c r="C707" s="7"/>
+      <c r="D707" s="1"/>
+      <c r="E707" s="1"/>
+      <c r="F707" s="6"/>
+      <c r="G707" s="1"/>
+      <c r="H707" s="1"/>
+      <c r="I707" s="1"/>
+    </row>
+    <row r="708" ht="12.75">
+      <c r="A708" s="1"/>
+      <c r="B708" s="1"/>
+      <c r="C708" s="7"/>
+      <c r="D708" s="1"/>
+      <c r="E708" s="1"/>
+      <c r="F708" s="6"/>
+      <c r="G708" s="1"/>
+      <c r="H708" s="1"/>
+      <c r="I708" s="1"/>
+    </row>
+    <row r="709" ht="12.75">
+      <c r="A709" s="1"/>
+      <c r="B709" s="1"/>
+      <c r="C709" s="7"/>
+      <c r="D709" s="1"/>
+      <c r="E709" s="1"/>
+      <c r="F709" s="6"/>
+      <c r="G709" s="1"/>
+      <c r="H709" s="1"/>
+      <c r="I709" s="1"/>
+    </row>
+    <row r="710" ht="12.75">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="7"/>
+      <c r="D710" s="1"/>
+      <c r="E710" s="1"/>
+      <c r="F710" s="6"/>
+      <c r="G710" s="1"/>
+      <c r="H710" s="1"/>
+      <c r="I710" s="1"/>
+    </row>
+    <row r="711" ht="12.75">
+      <c r="A711" s="1"/>
+      <c r="B711" s="1"/>
+      <c r="C711" s="7"/>
+      <c r="D711" s="1"/>
+      <c r="E711" s="1"/>
+      <c r="F711" s="6"/>
+      <c r="G711" s="1"/>
+      <c r="H711" s="1"/>
+      <c r="I711" s="1"/>
+    </row>
+    <row r="712" ht="12.75">
+      <c r="A712" s="1"/>
+      <c r="B712" s="1"/>
+      <c r="C712" s="7"/>
+      <c r="D712" s="1"/>
+      <c r="E712" s="1"/>
+      <c r="F712" s="6"/>
+      <c r="G712" s="1"/>
+      <c r="H712" s="1"/>
+      <c r="I712" s="1"/>
+    </row>
+    <row r="713" ht="12.75">
+      <c r="A713" s="1"/>
+      <c r="B713" s="1"/>
+      <c r="C713" s="7"/>
+      <c r="D713" s="1"/>
+      <c r="E713" s="1"/>
+      <c r="F713" s="6"/>
+      <c r="G713" s="1"/>
+      <c r="H713" s="1"/>
+      <c r="I713" s="1"/>
+    </row>
+    <row r="714" ht="12.75">
+      <c r="A714" s="1"/>
+      <c r="B714" s="1"/>
+      <c r="C714" s="7"/>
+      <c r="D714" s="1"/>
+      <c r="E714" s="1"/>
+      <c r="F714" s="6"/>
+      <c r="G714" s="1"/>
+      <c r="H714" s="1"/>
+      <c r="I714" s="1"/>
+    </row>
+    <row r="715" ht="12.75">
+      <c r="A715" s="1"/>
+      <c r="B715" s="1"/>
+      <c r="C715" s="7"/>
+      <c r="D715" s="1"/>
+      <c r="E715" s="1"/>
+      <c r="F715" s="6"/>
+      <c r="G715" s="1"/>
+      <c r="H715" s="1"/>
+      <c r="I715" s="1"/>
+    </row>
+    <row r="716" ht="12.75">
+      <c r="A716" s="1"/>
+      <c r="B716" s="1"/>
+      <c r="C716" s="7"/>
+      <c r="D716" s="1"/>
+      <c r="E716" s="1"/>
+      <c r="F716" s="6"/>
+      <c r="G716" s="1"/>
+      <c r="H716" s="1"/>
+      <c r="I716" s="1"/>
+    </row>
+    <row r="717" ht="12.75">
+      <c r="A717" s="1"/>
+      <c r="B717" s="1"/>
+      <c r="C717" s="7"/>
+      <c r="D717" s="1"/>
+      <c r="E717" s="1"/>
+      <c r="F717" s="6"/>
+      <c r="G717" s="1"/>
+      <c r="H717" s="1"/>
+      <c r="I717" s="1"/>
+    </row>
+    <row r="718" ht="12.75">
+      <c r="A718" s="1"/>
+      <c r="B718" s="1"/>
+      <c r="C718" s="7"/>
+      <c r="D718" s="1"/>
+      <c r="E718" s="1"/>
+      <c r="F718" s="6"/>
+      <c r="G718" s="1"/>
+      <c r="H718" s="1"/>
+      <c r="I718" s="1"/>
+    </row>
+    <row r="719" ht="12.75">
+      <c r="A719" s="1"/>
+      <c r="B719" s="1"/>
+      <c r="C719" s="7"/>
+      <c r="D719" s="1"/>
+      <c r="E719" s="1"/>
+      <c r="F719" s="6"/>
+      <c r="G719" s="1"/>
+      <c r="H719" s="1"/>
+      <c r="I719" s="1"/>
+    </row>
+    <row r="720" ht="12.75">
+      <c r="A720" s="1"/>
+      <c r="B720" s="1"/>
+      <c r="C720" s="7"/>
+      <c r="D720" s="1"/>
+      <c r="E720" s="1"/>
+      <c r="F720" s="6"/>
+      <c r="G720" s="1"/>
+      <c r="H720" s="1"/>
+      <c r="I720" s="1"/>
+    </row>
+    <row r="721" ht="12.75">
+      <c r="A721" s="1"/>
+      <c r="B721" s="1"/>
+      <c r="C721" s="7"/>
+      <c r="D721" s="1"/>
+      <c r="E721" s="1"/>
+      <c r="F721" s="6"/>
+      <c r="G721" s="1"/>
+      <c r="H721" s="1"/>
+      <c r="I721" s="1"/>
+    </row>
+    <row r="722" ht="12.75">
+      <c r="A722" s="1"/>
+      <c r="B722" s="1"/>
+      <c r="C722" s="7"/>
+      <c r="D722" s="1"/>
+      <c r="E722" s="1"/>
+      <c r="F722" s="6"/>
+      <c r="G722" s="1"/>
+      <c r="H722" s="1"/>
+      <c r="I722" s="1"/>
+    </row>
+    <row r="723" ht="12.75">
+      <c r="A723" s="1"/>
+      <c r="B723" s="1"/>
+      <c r="C723" s="7"/>
+      <c r="D723" s="1"/>
+      <c r="E723" s="1"/>
+      <c r="F723" s="6"/>
+      <c r="G723" s="1"/>
+      <c r="H723" s="1"/>
+      <c r="I723" s="1"/>
+    </row>
+    <row r="724" ht="12.75">
+      <c r="A724" s="1"/>
+      <c r="B724" s="1"/>
+      <c r="C724" s="7"/>
+      <c r="D724" s="1"/>
+      <c r="E724" s="1"/>
+      <c r="F724" s="6"/>
+      <c r="G724" s="1"/>
+      <c r="H724" s="1"/>
+      <c r="I724" s="1"/>
+    </row>
+    <row r="725" ht="12.75">
+      <c r="A725" s="1"/>
+      <c r="B725" s="1"/>
+      <c r="C725" s="7"/>
+      <c r="D725" s="1"/>
+      <c r="E725" s="1"/>
+      <c r="F725" s="6"/>
+      <c r="G725" s="1"/>
+      <c r="H725" s="1"/>
+      <c r="I725" s="1"/>
+    </row>
+    <row r="726" ht="12.75">
+      <c r="A726" s="1"/>
+      <c r="B726" s="1"/>
+      <c r="C726" s="7"/>
+      <c r="D726" s="1"/>
+      <c r="E726" s="1"/>
+      <c r="F726" s="6"/>
+      <c r="G726" s="1"/>
+      <c r="H726" s="1"/>
+      <c r="I726" s="1"/>
+    </row>
+    <row r="727" ht="12.75">
+      <c r="A727" s="1"/>
+      <c r="B727" s="1"/>
+      <c r="C727" s="7"/>
+      <c r="D727" s="1"/>
+      <c r="E727" s="1"/>
+      <c r="F727" s="6"/>
+      <c r="G727" s="1"/>
+    </row>
+    <row r="728" ht="12.75">
+      <c r="A728" s="1"/>
+      <c r="B728" s="1"/>
+      <c r="C728" s="7"/>
+      <c r="D728" s="1"/>
+      <c r="E728" s="1"/>
+      <c r="F728" s="6"/>
+      <c r="G728" s="1"/>
+    </row>
+    <row r="729" ht="12.75">
+      <c r="A729" s="1"/>
+      <c r="B729" s="1"/>
+      <c r="C729" s="7"/>
+      <c r="D729" s="1"/>
+      <c r="E729" s="1"/>
+      <c r="F729" s="6"/>
+      <c r="G729" s="1"/>
+    </row>
+    <row r="730" ht="12.75">
+      <c r="A730" s="1"/>
+      <c r="B730" s="1"/>
+      <c r="C730" s="7"/>
+      <c r="D730" s="1"/>
+      <c r="E730" s="1"/>
+      <c r="F730" s="6"/>
+      <c r="G730" s="1"/>
+    </row>
+    <row r="731" ht="12.75">
+      <c r="A731" s="1"/>
+      <c r="B731" s="1"/>
+      <c r="C731" s="7"/>
+      <c r="D731" s="1"/>
+      <c r="E731" s="1"/>
+      <c r="F731" s="6"/>
+      <c r="G731" s="1"/>
+    </row>
+    <row r="732" ht="12.75">
+      <c r="A732" s="1"/>
+      <c r="B732" s="1"/>
+      <c r="C732" s="7"/>
+      <c r="D732" s="1"/>
+      <c r="E732" s="1"/>
+      <c r="F732" s="6"/>
+      <c r="G732" s="1"/>
+    </row>
+    <row r="733" ht="12.75">
+      <c r="A733" s="1"/>
+      <c r="B733" s="1"/>
+      <c r="C733" s="7"/>
+      <c r="D733" s="1"/>
+      <c r="E733" s="1"/>
+      <c r="F733" s="6"/>
+      <c r="G733" s="1"/>
+    </row>
+    <row r="734" ht="12.75">
+      <c r="A734" s="1"/>
+      <c r="B734" s="1"/>
+      <c r="C734" s="7"/>
+      <c r="D734" s="1"/>
+      <c r="E734" s="1"/>
+      <c r="F734" s="6"/>
+      <c r="G734" s="1"/>
+    </row>
+    <row r="735" ht="12.75">
+      <c r="A735" s="1"/>
+      <c r="B735" s="1"/>
+      <c r="C735" s="7"/>
+      <c r="D735" s="1"/>
+      <c r="E735" s="1"/>
+      <c r="F735" s="6"/>
+      <c r="G735" s="1"/>
+    </row>
+    <row r="736" ht="12.75">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="7"/>
+      <c r="D736" s="1"/>
+      <c r="E736" s="1"/>
+      <c r="F736" s="6"/>
+      <c r="G736" s="1"/>
+    </row>
+    <row r="737" ht="12.75">
+      <c r="A737" s="1"/>
+      <c r="B737" s="1"/>
+      <c r="C737" s="7"/>
+      <c r="D737" s="1"/>
+      <c r="E737" s="1"/>
+      <c r="F737" s="6"/>
+      <c r="G737" s="1"/>
+    </row>
+    <row r="738" ht="12.75">
+      <c r="A738" s="1"/>
+      <c r="B738" s="1"/>
+      <c r="C738" s="7"/>
+      <c r="D738" s="1"/>
+      <c r="E738" s="1"/>
+      <c r="F738" s="6"/>
+      <c r="G738" s="1"/>
+    </row>
+    <row r="739" ht="12.75">
+      <c r="A739" s="1"/>
+      <c r="B739" s="1"/>
+      <c r="C739" s="7"/>
+      <c r="D739" s="1"/>
+      <c r="E739" s="1"/>
+      <c r="F739" s="6"/>
+      <c r="G739" s="1"/>
+    </row>
+    <row r="740" ht="12.75">
+      <c r="A740" s="1"/>
+      <c r="B740" s="1"/>
+      <c r="C740" s="7"/>
+      <c r="D740" s="1"/>
+      <c r="E740" s="1"/>
+      <c r="F740" s="6"/>
+      <c r="G740" s="1"/>
+    </row>
+    <row r="741" ht="12.75">
+      <c r="A741" s="1"/>
+      <c r="B741" s="1"/>
+      <c r="C741" s="7"/>
+      <c r="D741" s="1"/>
+      <c r="E741" s="1"/>
+      <c r="F741" s="6"/>
+      <c r="G741" s="1"/>
+    </row>
+    <row r="742" ht="12.75">
+      <c r="A742" s="1"/>
+      <c r="B742" s="1"/>
+      <c r="C742" s="7"/>
+      <c r="D742" s="1"/>
+      <c r="E742" s="1"/>
+      <c r="F742" s="6"/>
+      <c r="G742" s="1"/>
+    </row>
+    <row r="743" ht="12.75">
+      <c r="A743" s="1"/>
+      <c r="B743" s="1"/>
+      <c r="C743" s="7"/>
+      <c r="D743" s="1"/>
+      <c r="E743" s="1"/>
+      <c r="F743" s="6"/>
+      <c r="G743" s="1"/>
+    </row>
+    <row r="744" ht="12.75">
+      <c r="A744" s="1"/>
+      <c r="B744" s="1"/>
+      <c r="C744" s="7"/>
+      <c r="D744" s="1"/>
+      <c r="E744" s="1"/>
+      <c r="F744" s="6"/>
+      <c r="G744" s="1"/>
+    </row>
+    <row r="745" ht="12.75">
+      <c r="A745" s="1"/>
+      <c r="B745" s="1"/>
+      <c r="C745" s="7"/>
+      <c r="D745" s="1"/>
+      <c r="E745" s="1"/>
+      <c r="F745" s="6"/>
+      <c r="G745" s="1"/>
+    </row>
+    <row r="746" ht="12.75">
+      <c r="A746" s="1"/>
+      <c r="B746" s="1"/>
+      <c r="C746" s="7"/>
+      <c r="D746" s="1"/>
+      <c r="E746" s="1"/>
+      <c r="F746" s="6"/>
+      <c r="G746" s="1"/>
+    </row>
+    <row r="747" ht="12.75">
+      <c r="A747" s="1"/>
+      <c r="B747" s="1"/>
+      <c r="C747" s="7"/>
+      <c r="D747" s="1"/>
+      <c r="E747" s="1"/>
+      <c r="F747" s="6"/>
+      <c r="G747" s="1"/>
+    </row>
+    <row r="748" ht="12.75">
+      <c r="A748" s="1"/>
+      <c r="B748" s="1"/>
+      <c r="C748" s="7"/>
+      <c r="D748" s="1"/>
+      <c r="E748" s="1"/>
+      <c r="F748" s="6"/>
+      <c r="G748" s="1"/>
+    </row>
+    <row r="749" ht="12.75">
+      <c r="A749" s="1"/>
+      <c r="B749" s="1"/>
+      <c r="C749" s="7"/>
+      <c r="D749" s="1"/>
+      <c r="E749" s="1"/>
+      <c r="F749" s="6"/>
+      <c r="G749" s="1"/>
+    </row>
+    <row r="750" ht="12.75">
+      <c r="A750" s="1"/>
+      <c r="B750" s="1"/>
+      <c r="C750" s="7"/>
+      <c r="D750" s="1"/>
+      <c r="E750" s="1"/>
+      <c r="F750" s="6"/>
+      <c r="G750" s="1"/>
+    </row>
+    <row r="751" ht="12.75">
+      <c r="A751" s="1"/>
+      <c r="B751" s="1"/>
+      <c r="C751" s="7"/>
+      <c r="D751" s="1"/>
+      <c r="E751" s="1"/>
+      <c r="F751" s="6"/>
+      <c r="G751" s="1"/>
+    </row>
+    <row r="752" ht="12.75">
+      <c r="A752" s="1"/>
+      <c r="B752" s="1"/>
+      <c r="C752" s="7"/>
+      <c r="D752" s="1"/>
+      <c r="E752" s="1"/>
+      <c r="F752" s="6"/>
+      <c r="G752" s="1"/>
+    </row>
+    <row r="753" ht="12.75">
+      <c r="A753" s="1"/>
+      <c r="B753" s="1"/>
+      <c r="C753" s="7"/>
+      <c r="D753" s="1"/>
+      <c r="E753" s="1"/>
+      <c r="F753" s="6"/>
+      <c r="G753" s="1"/>
+    </row>
+    <row r="754" ht="12.75">
+      <c r="A754" s="1"/>
+      <c r="B754" s="1"/>
+      <c r="C754" s="7"/>
+      <c r="D754" s="1"/>
+      <c r="E754" s="1"/>
+      <c r="F754" s="6"/>
+      <c r="G754" s="1"/>
+    </row>
+    <row r="755" ht="12.75">
+      <c r="A755" s="1"/>
+      <c r="B755" s="1"/>
+      <c r="C755" s="7"/>
+      <c r="D755" s="1"/>
+      <c r="E755" s="1"/>
+      <c r="F755" s="6"/>
+      <c r="G755" s="1"/>
+    </row>
+    <row r="756" ht="12.75">
+      <c r="A756" s="1"/>
+      <c r="B756" s="1"/>
+      <c r="C756" s="7"/>
+      <c r="D756" s="1"/>
+      <c r="E756" s="1"/>
+      <c r="F756" s="6"/>
+      <c r="G756" s="1"/>
+    </row>
+    <row r="757" ht="12.75">
+      <c r="A757" s="1"/>
+      <c r="B757" s="1"/>
+      <c r="C757" s="7"/>
+      <c r="D757" s="1"/>
+      <c r="E757" s="1"/>
+      <c r="F757" s="6"/>
+      <c r="G757" s="1"/>
+    </row>
+    <row r="758" ht="12.75">
+      <c r="A758" s="1"/>
+      <c r="B758" s="1"/>
+      <c r="C758" s="7"/>
+      <c r="D758" s="1"/>
+      <c r="E758" s="1"/>
+      <c r="F758" s="6"/>
+      <c r="G758" s="1"/>
+    </row>
+    <row r="759" ht="12.75">
+      <c r="A759" s="1"/>
+      <c r="B759" s="1"/>
+      <c r="C759" s="7"/>
+      <c r="D759" s="1"/>
+      <c r="E759" s="1"/>
+      <c r="F759" s="6"/>
+      <c r="G759" s="1"/>
+    </row>
+    <row r="760" ht="12.75">
+      <c r="A760" s="1"/>
+      <c r="B760" s="1"/>
+      <c r="C760" s="7"/>
+      <c r="D760" s="1"/>
+      <c r="E760" s="1"/>
+      <c r="F760" s="6"/>
+      <c r="G760" s="1"/>
+    </row>
+    <row r="761" ht="12.75">
+      <c r="A761" s="1"/>
+      <c r="B761" s="1"/>
+      <c r="C761" s="7"/>
+      <c r="D761" s="1"/>
+      <c r="E761" s="1"/>
+      <c r="F761" s="6"/>
+      <c r="G761" s="1"/>
+    </row>
+    <row r="762" ht="12.75">
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="7"/>
+      <c r="D762" s="1"/>
+      <c r="E762" s="1"/>
+      <c r="F762" s="6"/>
+      <c r="G762" s="1"/>
+    </row>
+    <row r="763" ht="12.75">
+      <c r="A763" s="1"/>
+      <c r="B763" s="1"/>
+      <c r="C763" s="7"/>
+      <c r="D763" s="1"/>
+      <c r="E763" s="1"/>
+      <c r="F763" s="6"/>
+      <c r="G763" s="1"/>
+    </row>
+    <row r="764" ht="12.75">
+      <c r="A764" s="1"/>
+      <c r="B764" s="1"/>
+      <c r="C764" s="7"/>
+      <c r="D764" s="1"/>
+      <c r="E764" s="1"/>
+      <c r="F764" s="6"/>
+      <c r="G764" s="1"/>
+    </row>
+    <row r="765" ht="12.75">
+      <c r="A765" s="1"/>
+      <c r="B765" s="1"/>
+      <c r="C765" s="7"/>
+      <c r="D765" s="1"/>
+      <c r="E765" s="1"/>
+      <c r="F765" s="6"/>
+      <c r="G765" s="1"/>
+    </row>
+    <row r="766" ht="12.75">
+      <c r="A766" s="1"/>
+      <c r="B766" s="1"/>
+      <c r="C766" s="7"/>
+      <c r="D766" s="1"/>
+      <c r="E766" s="1"/>
+      <c r="F766" s="6"/>
+      <c r="G766" s="1"/>
+    </row>
+    <row r="767" ht="12.75">
+      <c r="A767" s="1"/>
+      <c r="B767" s="1"/>
+      <c r="C767" s="7"/>
+      <c r="D767" s="1"/>
+      <c r="E767" s="1"/>
+      <c r="F767" s="6"/>
+      <c r="G767" s="1"/>
+    </row>
+    <row r="768" ht="12.75">
+      <c r="A768" s="1"/>
+      <c r="B768" s="1"/>
+      <c r="C768" s="7"/>
+      <c r="D768" s="1"/>
+      <c r="E768" s="1"/>
+      <c r="F768" s="6"/>
+      <c r="G768" s="1"/>
+    </row>
+    <row r="769" ht="12.75">
+      <c r="A769" s="1"/>
+      <c r="B769" s="1"/>
+      <c r="C769" s="7"/>
+      <c r="D769" s="1"/>
+      <c r="E769" s="1"/>
+      <c r="F769" s="6"/>
+      <c r="G769" s="1"/>
+    </row>
+    <row r="770" ht="12.75">
+      <c r="A770" s="1"/>
+      <c r="B770" s="1"/>
+      <c r="C770" s="7"/>
+      <c r="D770" s="1"/>
+      <c r="E770" s="1"/>
+      <c r="F770" s="6"/>
+      <c r="G770" s="1"/>
+    </row>
+    <row r="771" ht="12.75">
+      <c r="A771" s="1"/>
+      <c r="B771" s="1"/>
+      <c r="C771" s="7"/>
+      <c r="D771" s="1"/>
+      <c r="E771" s="1"/>
+      <c r="F771" s="6"/>
+      <c r="G771" s="1"/>
+    </row>
+    <row r="772" ht="12.75">
+      <c r="A772" s="1"/>
+      <c r="B772" s="1"/>
+      <c r="C772" s="7"/>
+      <c r="D772" s="1"/>
+      <c r="E772" s="1"/>
+      <c r="F772" s="6"/>
+      <c r="G772" s="1"/>
+    </row>
+    <row r="773" ht="12.75">
+      <c r="A773" s="1"/>
+      <c r="B773" s="1"/>
+      <c r="C773" s="7"/>
+      <c r="D773" s="1"/>
+      <c r="E773" s="1"/>
+      <c r="F773" s="6"/>
+      <c r="G773" s="1"/>
+    </row>
+    <row r="774" ht="12.75">
+      <c r="A774" s="1"/>
+      <c r="B774" s="1"/>
+      <c r="C774" s="7"/>
+      <c r="D774" s="1"/>
+      <c r="E774" s="1"/>
+      <c r="F774" s="6"/>
+      <c r="G774" s="1"/>
+    </row>
+    <row r="775" ht="12.75">
+      <c r="A775" s="1"/>
+      <c r="B775" s="1"/>
+      <c r="C775" s="7"/>
+      <c r="D775" s="1"/>
+      <c r="E775" s="1"/>
+      <c r="F775" s="6"/>
+      <c r="G775" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F414"/>
+  <autoFilter ref="A1:F775"/>
   <printOptions headings="1" gridLines="0"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="42" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
@@ -10288,7 +16628,49 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{006A0000-006E-4D93-ACD7-004F00BD00E3}">
+          <x14:cfRule type="cellIs" priority="45" operator="notEqual" id="{00E30075-00E0-4817-A9F1-0076008C009E}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E496</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="40" operator="notEqual" id="{00C8008D-0031-4487-8B51-007900170017}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E415</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="40" operator="notEqual" id="{009100A1-00BE-40F0-B3FF-00A600EF00FA}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E449:E455 E417:E661</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005D00F7-00EE-47BF-94B6-00750000002C}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -10299,7 +16681,2723 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A2:F9999</xm:sqref>
+          <xm:sqref>A2:F414 A415:B775 D415:D775 F662:F775 A776:F9934</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00640074-006B-464D-B215-00F6006D007A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A415</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001900D1-002B-481E-BAD6-009E00ED0082}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F414</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0063009C-00AC-4736-BAF7-000A0078001B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A461:B461</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007A00C9-0090-4E00-AB9E-0099001200AC}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A489:B489</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00AC00AE-007F-432A-9A61-000B00BF00FD}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A495:B495</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009300A4-0086-4A78-BBED-00B5004C006D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A509:B509</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00070098-003A-4E5B-8B15-009E00AF00FE}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A509:B509</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BF00C6-003C-4EC2-92AC-00730031004C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A509:B509</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BE00D1-00B8-4951-BD25-000A00D100FB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A525:B525</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{000B0010-00EE-490C-A74B-004900860005}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A525:B525</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003500FF-00D8-43E8-A8F6-004000AE009D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A535:B535</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A9008B-0048-4FAE-A101-008100720009}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A535:B535</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00520028-009F-474D-858A-00CE00950019}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A535:B535</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FD003D-00DF-4D60-A5D1-00CF00720025}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A535:B535</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005E00AB-00F4-4455-BDEF-00F5007D008D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A535:B535</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008E00BF-00B5-4474-9BA8-002A002C0067}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005200EA-0021-4A2D-9241-00F8008D004A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{002600F0-00C1-4F99-B4D7-008400B90093}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004000F2-0047-41D9-B289-009C00E5003E}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001B0076-0015-49D1-A1A4-0056001C0074}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00230022-009C-4490-A44F-00B2006F00A2}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A60015-0006-4768-8444-001600A60056}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A548:B548</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006D0005-002C-4DF9-BCC7-003A00B200EB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A554:B554</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00120034-00CC-4670-99F3-0056005B0048}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A554:B554</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D900EE-0004-4E83-88EA-00E200E6003B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A554:B554</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F500B9-00DD-460A-B6A9-00C8000400AA}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A554:B554</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006700F6-00BF-411F-8D24-00BA00F3008F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A561:B561</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0054009C-00B4-4B19-AA2B-0080004C001A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A561:B561</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{002D00F6-000E-4982-B597-0020007E009A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A561:B561</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{002B0013-00F8-4D9C-99E9-003F00BE0013}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A561:B561</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A60071-00AB-468C-ADBB-00B400CD00EB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00400065-00CC-48A5-B573-003000F100F7}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A600FA-0054-4093-867A-005D0085004B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001E00DA-00D7-4432-A025-00C4003A0012}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003100D6-009A-4739-8BE0-0028008E00A4}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001D0071-00A6-4FD2-AEBD-00410006008B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00350065-00E5-4122-8E07-00EB00CE002B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A40070-00BD-4400-9990-00E30029001F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BE00B6-00AA-4E32-B6C2-00D40098004C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A569:B569</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00CA00A0-0060-489E-91E3-00EF00F800B0}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A579:B579</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00900086-00EE-4B71-BEF0-0089008B002E}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A579:B579</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007300BD-0052-4E27-AB61-00E200690018}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A579:B579</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00EC00DB-00AF-473C-90D4-00F8009100EB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A579:B579</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0059000F-0010-482A-AD85-006F00CA00A7}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A579:B579</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009F009D-0030-4887-901F-00AA0098009B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BD0033-0074-44D2-BCD6-00B7007F0099}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0082002E-00B6-4CDB-B306-00DA002C0006}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00490004-00D7-48AE-A307-00C7009E0080}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00770095-00F3-4FDE-8F94-005600AE006F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C70001-006B-4BC1-B79A-0038004D0072}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001200F4-0038-4192-B1E1-000900DC0097}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{000200CD-00C1-4693-8BEF-00BD00BC00D6}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008900C5-008E-4016-89F9-00F90023006F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00000064-00CF-4F68-BC8C-00CD00FD00DB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007C004F-0067-40A6-8AF6-0072006E00AB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A588:B588</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003E00B8-00CD-4BCE-8D45-0000000D0023}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A596:B596</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001B0090-0050-4C40-98AC-008B00B100F1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A596:B596</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D800B6-001D-4A2D-BB1A-00B8005E004D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A596:B596</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B200AD-0064-418F-8A10-00150028008B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A596:B596</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006B007E-0021-4D7A-899B-006800AD0071}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A596:B596</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A7002E-0003-4B5A-8CF3-0073000900D2}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A596:B596</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008E0066-0013-4103-84AE-005D00E60061}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0051007E-006C-47E0-90B1-00BF007B003C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00DA00FF-000F-4A07-BB98-009100E60019}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D7001A-001A-4576-ABD3-00EC00720019}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C70093-00CC-4C8B-A335-006600780001}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D80079-0011-4FBF-8EC2-009300520048}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003300D9-006C-441A-B21B-006C000B00F7}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00E1002C-00C1-41E0-BD7F-00A600C500DE}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A6008C-0078-425E-9EC9-00E500920039}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00270062-0048-4930-9954-00CE001F00CB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001900A1-00FF-443B-A1E8-002600CF0053}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00410086-009A-4408-90D5-006E004700C5}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00AF0031-0092-49E4-82BD-0006006B002C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A609:B609</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009A0008-009B-4F47-B696-003900FF00B1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F300BF-00A9-432E-8813-0008002F006A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F3003A-001E-4DC7-83E6-0098002D00F0}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0083001D-00AE-46D2-9CCB-007D0040008A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005C0090-006D-44F1-B105-0064005600AE}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003100BE-00C0-4F41-8CB5-00010098009C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FF00A7-0065-4175-9E8F-002A005600ED}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008100FB-008A-4ED3-8AFF-006D002500A5}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0069002D-0007-4ACD-B0F1-0077006000E0}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00DD0011-00F1-4BEF-A726-0033002F009F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004600BC-0039-46A1-9208-0091003C0048}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009300B3-00BA-40B3-8426-00BE0029005E}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D00050-0092-4031-A728-0064002A001A}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BD008D-00C1-4675-A91C-00B0008300C1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B600E5-0036-4858-AF34-007A001F00FD}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A616:B616</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007700A5-009A-465D-8CD7-00E700A3005F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005C00C5-00AE-479B-B6EE-005E000900C4}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00340064-009A-4F37-AE08-000D00750032}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007300C7-00B8-4714-8561-00D300DE00B9}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{000E0030-002A-4249-9896-008500AF005B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006F002B-00C9-4C3D-970F-0003008F0033}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008C00AA-007A-42D3-AF9B-00160038003E}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009000DF-0065-4835-A876-009E007D0058}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C2006C-007A-418E-B9DF-004900640014}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007700B6-00BC-4538-8A72-0091006F0009}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009F0054-0096-4A47-B92D-00EC00CC00F5}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006C00D9-00EB-4F58-8E47-000C00F20013}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A500A0-0036-429C-8EDA-00CA00220050}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00E30055-00A2-4BEE-A068-00EC003100A6}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00EC0055-00FF-41D8-B842-00AB0042006E}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009C00B6-000D-474C-A625-0034006100F2}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005D0072-001B-43B7-BE91-007B00810030}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A624:B624</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006E001E-0091-4600-96C5-003C005E004D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A655:B655</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BA0098-0079-42C8-AF77-002400C900D3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A655:B655</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{000A00C3-00BB-46DA-832A-000400CC00DA}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A655:B655</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A60051-0048-4059-B286-00D6003E003C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A655:B655</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F20015-00FF-491E-81E3-00E1008D00A6}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008C004B-0036-4FB2-8B91-009E003900C8}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004700E6-0075-400B-8A52-00B200500002}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00AC00B3-008B-4005-A138-003A00BD00B3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005D0029-0067-4B94-B105-005200950018}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FF00DE-0039-41FD-B9AC-00EE00C700A0}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BA00DB-00C2-4206-9934-00DC00910089}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00BA0031-007A-41A1-9475-00C70016007F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008B0001-001A-4BEB-9302-00F10083000F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B200DD-00BC-4828-85EE-00DE00EF00E1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A665:B665</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FB000E-0022-447C-B015-004600B9004D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005F0093-00B1-4D4F-B6BF-008000D50038}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007F00AB-0004-4E9E-8AF7-000300840035}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009300CD-003B-4346-88D1-005D008900F3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006E006C-00F5-4636-B0C4-00E7001400F4}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D30079-00DB-459E-9D07-004700EC00CA}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0073007D-009E-4780-BF12-00F3007C005F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{000A0001-005C-4C16-96A3-008E00DB0028}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A90014-00E7-42DE-87D3-007B00E90070}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00960044-003C-4C36-9EDF-00C3005B00D3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A678:B678</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FE00AB-0011-48D6-BBBD-0094003700B8}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0005000D-006D-4495-8B25-006C003900EC}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004200DE-00BF-496F-84CD-00AB00880056}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009500E7-00F8-43DD-BA53-00B400A1001B}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00790004-0078-498D-81D7-00CD007B0030}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0034004C-0089-43DD-9F02-007C007000B1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D200C2-0047-40B7-960C-006900F80011}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{009F005A-000B-426F-A7D3-0024007600E8}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0050008D-00A9-479F-BEA3-00A500270087}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A3002A-00E4-4392-BC36-009700090019}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C20066-00E6-40DA-B20D-0023009300DC}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{001C006A-00E1-4495-8DF5-0087008A005C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A685:B685</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D100F8-00BE-49B8-B2EB-0030000F0008}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004F00FD-00F2-4F73-83C6-00C8008F00C7}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00630023-0049-4D07-B70A-00E300210086}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00940085-0099-478C-9E86-002F00AA00D3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003B0033-0034-4E73-B0EA-003C00B500A9}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00730086-0092-49ED-8375-009500FB00C3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0085001E-00F7-4EB2-86A4-00D4006900B3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008F00C2-0073-49E6-B267-00EE004D00A1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F500D7-0024-4132-8C08-00F100FE0028}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B20080-00B3-49FE-9835-002C006C001F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00EC0054-008A-424B-A3FC-006C0054001C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00DE004D-00DC-4FB5-B56B-001A004200D7}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A639:B639</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00810001-0051-4162-AF4C-007A003E00DA}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FD006D-000E-4AE1-A420-008E002E00BD}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003C0099-0021-4364-9ED8-00CC00DA0062}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006900F7-0047-458F-B76B-00FA00B30063}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007F006A-0077-42C2-9EE8-007500710086}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00680083-00A8-4406-A840-003A00F800A5}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D40022-00AE-4371-BA82-001500500082}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00EA005B-00E4-4264-AE9A-00ED001C0062}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00EC0096-003C-4447-BB85-00D200D00055}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00FB00A2-00F6-4C79-9725-007200D10034}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C8008B-0004-4B66-9A0B-00E100B70046}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B3006E-0014-415D-9C3F-00B900790020}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B20019-0061-457D-8C76-00CA004100E5}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C700A6-008F-4881-885D-00EC008B0032}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00AC0074-000A-4F8B-AD07-007E00870046}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00270093-009F-4442-9361-0030002E0083}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F1000F-006D-43BF-B057-0054005E00E0}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00D10041-0042-438B-9834-009C00FC00F8}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004D0001-00F2-4DCA-882E-007E00C000C9}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B0008A-00C1-47D0-92F2-002D00310020}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{004400CF-001D-464B-8755-000E00DE001F}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00760076-00FF-4FAD-A280-00BE006B0019}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{000700D6-00CC-4FE6-B2AD-00CB00F400BF}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00E4007F-00F4-41C5-8351-006A000400FE}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C40062-0091-4EAA-872D-00C2008D00D3}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A649:B649</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00DF001F-00DE-4220-BDBF-0068002000FC}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00B500C0-003F-43B7-800C-006900EB00D2}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F100EC-0003-411E-A159-0084002A0043}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{003B00FE-0072-4E3F-803F-001000AE0090}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00180092-0004-4945-BCB4-00E400670093}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007E005C-0091-4C3B-B07A-00D100FB00EF}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{007300CB-0073-40E3-9106-008700E000BB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00E0009D-00AC-484D-A1A6-00AD00DB0022}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00740070-0026-4C85-9D4B-009300810013}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008D00DB-0077-4CD2-8FC2-001B00410021}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F700AD-0032-4FD5-A80B-006700620057}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0019003B-00F6-4706-8672-0059005A000D}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00160071-00E2-42F4-8A88-007200CE0077}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A658:B658</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{005A0084-004D-4B03-9AF5-0072008C0024}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A415:B415</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{002A007C-0041-441D-BA49-009400EB00AF}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A415</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/input/budget.xlsx
+++ b/input/budget.xlsx
@@ -12,11 +12,11 @@
     <externalReference r:id="rId1"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$776</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$779</definedName>
     <definedName name="Print_Titles" localSheetId="0">Sheet1!$1:$1</definedName>
     <definedName name="_xlcn.WorksheetConnection_budget_2024.xlsxTable2" hidden="1">'[1]budget 11-01-23'!$A$1:$M$198</definedName>
     <definedName name="_xlcn.WorksheetConnection_budget_2024.xlsxTable3" hidden="1">Table1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$776</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$779</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="318">
   <si>
     <t>Year</t>
   </si>
@@ -928,7 +928,16 @@
     <t xml:space="preserve">1234 Designated Fund Income</t>
   </si>
   <si>
-    <t xml:space="preserve">Consistory added $450*11 for art night on 1/14/25 and $1k for classis meeting in 3/2025</t>
+    <t xml:space="preserve">Using this to offset 7121?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/2024 approved budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consistory added $450*11 for art night on 1/14/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consistory added $1k for classis meeting in 3/2025</t>
   </si>
   <si>
     <t xml:space="preserve">5020 Pastoral Search Expense</t>
@@ -996,6 +1005,12 @@
   </si>
   <si>
     <t xml:space="preserve">Ammended 1/14/25 by Consistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6707 temp number for Classis meeting expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ammended 3/2025 by Consistory</t>
   </si>
   <si>
     <t xml:space="preserve">13 Creation Care</t>
@@ -1154,7 +1169,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1216,6 +1231,9 @@
     <xf fontId="3" fillId="6" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf fontId="4" fillId="3" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1810,7 +1828,8 @@
     <col bestFit="1" customWidth="1" min="2" max="2" style="1" width="17.28515625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" style="1" width="29.140625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="46.7109375"/>
-    <col customWidth="1" min="5" max="6" style="2" width="24"/>
+    <col customWidth="1" min="5" max="5" style="2" width="24"/>
+    <col customWidth="1" min="6" max="6" style="2" width="24.8515625"/>
     <col bestFit="1" min="7" max="7" style="1" width="9.42578125"/>
     <col min="8" max="16384" style="1" width="9.140625"/>
   </cols>
@@ -11250,7 +11269,9 @@
       <c r="E429" s="20">
         <v>40000</v>
       </c>
-      <c r="F429" s="20"/>
+      <c r="F429" s="20" t="s">
+        <v>291</v>
+      </c>
       <c r="G429" s="6">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -11380,12 +11401,11 @@
       <c r="D435" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E435" s="23">
-        <f>25100+11*450+1000</f>
-        <v>31050</v>
-      </c>
-      <c r="F435" s="23" t="s">
-        <v>291</v>
+      <c r="E435" s="20">
+        <v>25100</v>
+      </c>
+      <c r="F435" s="20" t="s">
+        <v>292</v>
       </c>
       <c r="G435" s="6">
         <f t="shared" si="6"/>
@@ -11399,110 +11419,115 @@
       <c r="B436" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C436" t="s">
+      <c r="C436" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="D436" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E436" s="20">
+        <f>11*450</f>
+        <v>4950</v>
+      </c>
+      <c r="F436" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="G436" s="6">
+        <f>IF(C436=C435,G435,G435+1)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="437" ht="14.25">
+      <c r="A437" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C437" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="D437" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E437" s="20">
+        <v>1000</v>
+      </c>
+      <c r="F437" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="G437" s="6">
+        <f>IF(C437=C436,G436,G436+1)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="438" ht="14.25">
+      <c r="A438" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C438" t="s">
         <v>247</v>
       </c>
-      <c r="D436" s="11" t="s">
+      <c r="D438" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E436" s="14">
+      <c r="E438" s="14">
         <v>70000</v>
       </c>
-      <c r="F436" s="14"/>
-      <c r="G436" s="6">
+      <c r="F438" s="14"/>
+      <c r="G438" s="6">
+        <f>IF(C438=C435,G435,G435+1)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="439" ht="14.25">
+      <c r="A439" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C439" t="s">
+        <v>247</v>
+      </c>
+      <c r="D439" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E439" s="14">
+        <f>246500-E440-E438</f>
+        <v>76500</v>
+      </c>
+      <c r="F439" s="14"/>
+      <c r="G439" s="6">
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
-    <row r="437" ht="14.25">
-      <c r="A437" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B437" s="1" t="s">
+    <row r="440" ht="14.25">
+      <c r="A440" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B440" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C437" t="s">
+      <c r="C440" t="s">
         <v>247</v>
       </c>
-      <c r="D437" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E437" s="14">
-        <f>246500-E438-E436</f>
-        <v>76500</v>
-      </c>
-      <c r="F437" s="14"/>
-      <c r="G437" s="6">
+      <c r="D440" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E440" s="14">
+        <v>100000</v>
+      </c>
+      <c r="F440" s="14"/>
+      <c r="G440" s="6">
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
-    <row r="438" ht="14.25">
-      <c r="A438" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B438" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C438" t="s">
-        <v>247</v>
-      </c>
-      <c r="D438" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E438" s="14">
-        <v>100000</v>
-      </c>
-      <c r="F438" s="14"/>
-      <c r="G438" s="6">
-        <f t="shared" si="6"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="439" ht="14.25">
-      <c r="A439" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B439" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C439" t="s">
-        <v>248</v>
-      </c>
-      <c r="D439" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E439" s="13">
-        <v>10000</v>
-      </c>
-      <c r="F439" s="13"/>
-      <c r="G439" s="6">
-        <f t="shared" si="6"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="440" ht="14.25">
-      <c r="A440" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B440" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C440" t="s">
-        <v>248</v>
-      </c>
-      <c r="D440" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E440" s="13">
-        <v>3000</v>
-      </c>
-      <c r="F440" s="13"/>
-      <c r="G440" s="6">
-        <f t="shared" si="6"/>
-        <v>52</v>
-      </c>
-    </row>
     <row r="441" ht="14.25">
       <c r="A441" s="1">
         <v>2025</v>
@@ -11514,10 +11539,10 @@
         <v>248</v>
       </c>
       <c r="D441" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E441" s="13">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="F441" s="13"/>
       <c r="G441" s="6">
@@ -11536,10 +11561,10 @@
         <v>248</v>
       </c>
       <c r="D442" s="11" t="s">
-        <v>249</v>
+        <v>31</v>
       </c>
       <c r="E442" s="13">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="F442" s="13"/>
       <c r="G442" s="6">
@@ -11558,10 +11583,10 @@
         <v>248</v>
       </c>
       <c r="D443" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E443" s="13">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="F443" s="13"/>
       <c r="G443" s="6">
@@ -11580,10 +11605,10 @@
         <v>248</v>
       </c>
       <c r="D444" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E444" s="13">
-        <v>5000</v>
+        <v>1100</v>
       </c>
       <c r="F444" s="13"/>
       <c r="G444" s="6">
@@ -11596,21 +11621,21 @@
         <v>2025</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C445" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D445" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E445" s="24">
-        <v>-2200</v>
-      </c>
-      <c r="F445" s="24"/>
+        <v>34</v>
+      </c>
+      <c r="E445" s="13">
+        <v>1000</v>
+      </c>
+      <c r="F445" s="13"/>
       <c r="G445" s="6">
         <f t="shared" si="6"/>
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="446" ht="14.25">
@@ -11618,21 +11643,21 @@
         <v>2025</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C446" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D446" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="E446" s="25">
-        <v>-57500</v>
-      </c>
-      <c r="F446" s="25"/>
+        <v>250</v>
+      </c>
+      <c r="E446" s="13">
+        <v>5000</v>
+      </c>
+      <c r="F446" s="13"/>
       <c r="G446" s="6">
         <f t="shared" si="6"/>
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="447" ht="14.25">
@@ -11646,10 +11671,10 @@
         <v>251</v>
       </c>
       <c r="D447" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E447" s="25">
-        <v>-10000</v>
+        <v>-2200</v>
       </c>
       <c r="F447" s="25"/>
       <c r="G447" s="6">
@@ -11668,12 +11693,12 @@
         <v>251</v>
       </c>
       <c r="D448" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="E448" s="25">
-        <v>-13300</v>
-      </c>
-      <c r="F448" s="25"/>
+        <v>210</v>
+      </c>
+      <c r="E448" s="26">
+        <v>-57500</v>
+      </c>
+      <c r="F448" s="26"/>
       <c r="G448" s="6">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -11690,12 +11715,12 @@
         <v>251</v>
       </c>
       <c r="D449" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E449" s="25">
-        <v>-7268</v>
-      </c>
-      <c r="F449" s="25"/>
+        <v>211</v>
+      </c>
+      <c r="E449" s="26">
+        <v>-10000</v>
+      </c>
+      <c r="F449" s="26"/>
       <c r="G449" s="6">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -11712,12 +11737,12 @@
         <v>251</v>
       </c>
       <c r="D450" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E450" s="25">
-        <v>-5000</v>
-      </c>
-      <c r="F450" s="25"/>
+        <v>212</v>
+      </c>
+      <c r="E450" s="26">
+        <v>-13300</v>
+      </c>
+      <c r="F450" s="26"/>
       <c r="G450" s="6">
         <f t="shared" ref="G450:G513" si="7">IF(C450=C449,G449,G449+1)</f>
         <v>53</v>
@@ -11734,12 +11759,12 @@
         <v>251</v>
       </c>
       <c r="D451" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E451" s="25">
-        <v>-37500</v>
-      </c>
-      <c r="F451" s="25"/>
+        <v>213</v>
+      </c>
+      <c r="E451" s="26">
+        <v>-7268</v>
+      </c>
+      <c r="F451" s="26"/>
       <c r="G451" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11756,12 +11781,12 @@
         <v>251</v>
       </c>
       <c r="D452" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="E452" s="25">
-        <v>-1425</v>
-      </c>
-      <c r="F452" s="25"/>
+        <v>214</v>
+      </c>
+      <c r="E452" s="26">
+        <v>-5000</v>
+      </c>
+      <c r="F452" s="26"/>
       <c r="G452" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11778,10 +11803,10 @@
         <v>251</v>
       </c>
       <c r="D453" s="11" t="s">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="E453" s="26">
-        <v>-10000</v>
+        <v>-37500</v>
       </c>
       <c r="F453" s="26"/>
       <c r="G453" s="6">
@@ -11800,12 +11825,12 @@
         <v>251</v>
       </c>
       <c r="D454" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="E454" s="24">
-        <v>-1524</v>
-      </c>
-      <c r="F454" s="24"/>
+        <v>216</v>
+      </c>
+      <c r="E454" s="26">
+        <v>-1425</v>
+      </c>
+      <c r="F454" s="26"/>
       <c r="G454" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11822,12 +11847,12 @@
         <v>251</v>
       </c>
       <c r="D455" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="E455" s="24">
-        <v>-44623</v>
-      </c>
-      <c r="F455" s="24"/>
+        <v>295</v>
+      </c>
+      <c r="E455" s="27">
+        <v>-10000</v>
+      </c>
+      <c r="F455" s="27"/>
       <c r="G455" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11844,12 +11869,12 @@
         <v>251</v>
       </c>
       <c r="D456" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E456" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F456" s="27"/>
+        <v>205</v>
+      </c>
+      <c r="E456" s="25">
+        <v>-1524</v>
+      </c>
+      <c r="F456" s="25"/>
       <c r="G456" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11865,13 +11890,13 @@
       <c r="C457" t="s">
         <v>251</v>
       </c>
-      <c r="D457" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="E457" s="24">
-        <v>-18000</v>
-      </c>
-      <c r="F457" s="24"/>
+      <c r="D457" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E457" s="25">
+        <v>-44623</v>
+      </c>
+      <c r="F457" s="25"/>
       <c r="G457" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11888,12 +11913,12 @@
         <v>251</v>
       </c>
       <c r="D458" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E458" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F458" s="27"/>
+        <v>207</v>
+      </c>
+      <c r="E458" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F458" s="28"/>
       <c r="G458" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11909,13 +11934,13 @@
       <c r="C459" t="s">
         <v>251</v>
       </c>
-      <c r="D459" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="E459" s="27">
-        <v>-700</v>
-      </c>
-      <c r="F459" s="27"/>
+      <c r="D459" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="E459" s="25">
+        <v>-18000</v>
+      </c>
+      <c r="F459" s="25"/>
       <c r="G459" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11932,12 +11957,12 @@
         <v>251</v>
       </c>
       <c r="D460" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E460" s="27">
-        <v>-12950</v>
-      </c>
-      <c r="F460" s="27"/>
+        <v>180</v>
+      </c>
+      <c r="E460" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F460" s="28"/>
       <c r="G460" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11954,12 +11979,12 @@
         <v>251</v>
       </c>
       <c r="D461" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E461" s="27">
-        <v>-1200</v>
-      </c>
-      <c r="F461" s="27"/>
+        <v>181</v>
+      </c>
+      <c r="E461" s="28">
+        <v>-700</v>
+      </c>
+      <c r="F461" s="28"/>
       <c r="G461" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11976,12 +12001,12 @@
         <v>251</v>
       </c>
       <c r="D462" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E462" s="27">
-        <v>-250</v>
-      </c>
-      <c r="F462" s="27"/>
+        <v>182</v>
+      </c>
+      <c r="E462" s="28">
+        <v>-12950</v>
+      </c>
+      <c r="F462" s="28"/>
       <c r="G462" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -11998,12 +12023,12 @@
         <v>251</v>
       </c>
       <c r="D463" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E463" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F463" s="27"/>
+        <v>183</v>
+      </c>
+      <c r="E463" s="28">
+        <v>-1200</v>
+      </c>
+      <c r="F463" s="28"/>
       <c r="G463" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12020,12 +12045,12 @@
         <v>251</v>
       </c>
       <c r="D464" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E464" s="27">
-        <v>-1200</v>
-      </c>
-      <c r="F464" s="27"/>
+        <v>184</v>
+      </c>
+      <c r="E464" s="28">
+        <v>-250</v>
+      </c>
+      <c r="F464" s="28"/>
       <c r="G464" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12042,12 +12067,12 @@
         <v>251</v>
       </c>
       <c r="D465" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E465" s="27">
+        <v>185</v>
+      </c>
+      <c r="E465" s="28">
         <v>-200</v>
       </c>
-      <c r="F465" s="27"/>
+      <c r="F465" s="28"/>
       <c r="G465" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12064,12 +12089,12 @@
         <v>251</v>
       </c>
       <c r="D466" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E466" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F466" s="27"/>
+        <v>186</v>
+      </c>
+      <c r="E466" s="28">
+        <v>-1200</v>
+      </c>
+      <c r="F466" s="28"/>
       <c r="G466" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12085,11 +12110,11 @@
       <c r="C467" t="s">
         <v>251</v>
       </c>
-      <c r="D467" s="16" t="s">
-        <v>189</v>
+      <c r="D467" s="11" t="s">
+        <v>187</v>
       </c>
       <c r="E467" s="28">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F467" s="28"/>
       <c r="G467" s="6">
@@ -12108,12 +12133,12 @@
         <v>251</v>
       </c>
       <c r="D468" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E468" s="27">
-        <v>-3200</v>
-      </c>
-      <c r="F468" s="27"/>
+        <v>188</v>
+      </c>
+      <c r="E468" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F468" s="28"/>
       <c r="G468" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12129,13 +12154,13 @@
       <c r="C469" t="s">
         <v>251</v>
       </c>
-      <c r="D469" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="E469" s="27">
+      <c r="D469" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E469" s="29">
         <v>0</v>
       </c>
-      <c r="F469" s="27"/>
+      <c r="F469" s="29"/>
       <c r="G469" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12152,12 +12177,12 @@
         <v>251</v>
       </c>
       <c r="D470" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E470" s="27">
-        <v>0</v>
-      </c>
-      <c r="F470" s="27"/>
+        <v>190</v>
+      </c>
+      <c r="E470" s="28">
+        <v>-3200</v>
+      </c>
+      <c r="F470" s="28"/>
       <c r="G470" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12174,12 +12199,12 @@
         <v>251</v>
       </c>
       <c r="D471" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="E471" s="27">
-        <v>-100</v>
-      </c>
-      <c r="F471" s="27"/>
+        <v>191</v>
+      </c>
+      <c r="E471" s="28">
+        <v>0</v>
+      </c>
+      <c r="F471" s="28"/>
       <c r="G471" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12196,12 +12221,12 @@
         <v>251</v>
       </c>
       <c r="D472" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E472" s="27">
-        <v>-12000</v>
-      </c>
-      <c r="F472" s="27"/>
+        <v>192</v>
+      </c>
+      <c r="E472" s="28">
+        <v>0</v>
+      </c>
+      <c r="F472" s="28"/>
       <c r="G472" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12217,13 +12242,13 @@
       <c r="C473" t="s">
         <v>251</v>
       </c>
-      <c r="D473" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="E473" s="24">
-        <v>-2000</v>
-      </c>
-      <c r="F473" s="24"/>
+      <c r="D473" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E473" s="28">
+        <v>-100</v>
+      </c>
+      <c r="F473" s="28"/>
       <c r="G473" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12239,13 +12264,13 @@
       <c r="C474" t="s">
         <v>251</v>
       </c>
-      <c r="D474" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="E474" s="29">
-        <v>0</v>
-      </c>
-      <c r="F474" s="29"/>
+      <c r="D474" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E474" s="28">
+        <v>-12000</v>
+      </c>
+      <c r="F474" s="28"/>
       <c r="G474" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12262,12 +12287,12 @@
         <v>251</v>
       </c>
       <c r="D475" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="E475" s="29">
-        <v>-1000</v>
-      </c>
-      <c r="F475" s="29"/>
+        <v>253</v>
+      </c>
+      <c r="E475" s="25">
+        <v>-2000</v>
+      </c>
+      <c r="F475" s="25"/>
       <c r="G475" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12283,13 +12308,13 @@
       <c r="C476" t="s">
         <v>251</v>
       </c>
-      <c r="D476" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="E476" s="29">
+      <c r="D476" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E476" s="30">
         <v>0</v>
       </c>
-      <c r="F476" s="29"/>
+      <c r="F476" s="30"/>
       <c r="G476" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12305,13 +12330,13 @@
       <c r="C477" t="s">
         <v>251</v>
       </c>
-      <c r="D477" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E477" s="31">
-        <v>0</v>
-      </c>
-      <c r="F477" s="31"/>
+      <c r="D477" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E477" s="30">
+        <v>-1000</v>
+      </c>
+      <c r="F477" s="30"/>
       <c r="G477" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12327,13 +12352,13 @@
       <c r="C478" t="s">
         <v>251</v>
       </c>
-      <c r="D478" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="E478" s="31">
-        <v>-400</v>
-      </c>
-      <c r="F478" s="31"/>
+      <c r="D478" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="E478" s="30">
+        <v>0</v>
+      </c>
+      <c r="F478" s="30"/>
       <c r="G478" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12350,12 +12375,12 @@
         <v>251</v>
       </c>
       <c r="D479" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="E479" s="31">
-        <v>-1300</v>
-      </c>
-      <c r="F479" s="31"/>
+        <v>255</v>
+      </c>
+      <c r="E479" s="32">
+        <v>0</v>
+      </c>
+      <c r="F479" s="32"/>
       <c r="G479" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12371,13 +12396,13 @@
       <c r="C480" t="s">
         <v>251</v>
       </c>
-      <c r="D480" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="E480" s="31">
-        <v>-1000</v>
-      </c>
-      <c r="F480" s="31"/>
+      <c r="D480" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E480" s="32">
+        <v>-400</v>
+      </c>
+      <c r="F480" s="32"/>
       <c r="G480" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12393,13 +12418,13 @@
       <c r="C481" t="s">
         <v>251</v>
       </c>
-      <c r="D481" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="E481" s="31">
-        <v>-1000</v>
-      </c>
-      <c r="F481" s="31"/>
+      <c r="D481" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="E481" s="32">
+        <v>-1300</v>
+      </c>
+      <c r="F481" s="32"/>
       <c r="G481" s="6">
         <f t="shared" si="7"/>
         <v>53</v>
@@ -12413,18 +12438,18 @@
         <v>36</v>
       </c>
       <c r="C482" t="s">
-        <v>295</v>
-      </c>
-      <c r="D482" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E482" s="24">
-        <v>-10000</v>
-      </c>
-      <c r="F482" s="24"/>
+        <v>251</v>
+      </c>
+      <c r="D482" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="E482" s="32">
+        <v>-1000</v>
+      </c>
+      <c r="F482" s="32"/>
       <c r="G482" s="6">
         <f t="shared" si="7"/>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="483" ht="14.25">
@@ -12435,18 +12460,18 @@
         <v>36</v>
       </c>
       <c r="C483" t="s">
-        <v>295</v>
-      </c>
-      <c r="D483" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E483" s="24">
-        <v>-14400</v>
-      </c>
-      <c r="F483" s="24"/>
+        <v>251</v>
+      </c>
+      <c r="D483" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="E483" s="32">
+        <v>-1000</v>
+      </c>
+      <c r="F483" s="32"/>
       <c r="G483" s="6">
         <f t="shared" si="7"/>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="484" ht="14.25">
@@ -12457,15 +12482,15 @@
         <v>36</v>
       </c>
       <c r="C484" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D484" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="E484" s="33">
-        <v>-2000</v>
-      </c>
-      <c r="F484" s="33"/>
+        <v>120</v>
+      </c>
+      <c r="E484" s="25">
+        <v>-10000</v>
+      </c>
+      <c r="F484" s="25"/>
       <c r="G484" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12479,15 +12504,15 @@
         <v>36</v>
       </c>
       <c r="C485" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D485" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E485" s="24">
-        <v>-42800</v>
-      </c>
-      <c r="F485" s="24"/>
+        <v>121</v>
+      </c>
+      <c r="E485" s="25">
+        <v>-14400</v>
+      </c>
+      <c r="F485" s="25"/>
       <c r="G485" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12501,15 +12526,15 @@
         <v>36</v>
       </c>
       <c r="C486" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D486" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E486" s="24">
-        <v>-20000</v>
-      </c>
-      <c r="F486" s="24"/>
+        <v>299</v>
+      </c>
+      <c r="E486" s="34">
+        <v>-2000</v>
+      </c>
+      <c r="F486" s="34"/>
       <c r="G486" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12523,15 +12548,15 @@
         <v>36</v>
       </c>
       <c r="C487" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D487" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E487" s="24">
-        <v>-1600</v>
-      </c>
-      <c r="F487" s="24"/>
+        <v>122</v>
+      </c>
+      <c r="E487" s="25">
+        <v>-42800</v>
+      </c>
+      <c r="F487" s="25"/>
       <c r="G487" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12545,15 +12570,15 @@
         <v>36</v>
       </c>
       <c r="C488" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D488" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E488" s="26">
-        <v>0</v>
-      </c>
-      <c r="F488" s="26"/>
+        <v>123</v>
+      </c>
+      <c r="E488" s="25">
+        <v>-20000</v>
+      </c>
+      <c r="F488" s="25"/>
       <c r="G488" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12567,15 +12592,15 @@
         <v>36</v>
       </c>
       <c r="C489" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D489" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E489" s="24">
-        <v>-7200</v>
-      </c>
-      <c r="F489" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="E489" s="25">
+        <v>-1600</v>
+      </c>
+      <c r="F489" s="25"/>
       <c r="G489" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12589,15 +12614,15 @@
         <v>36</v>
       </c>
       <c r="C490" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D490" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E490" s="24">
-        <v>-7200</v>
-      </c>
-      <c r="F490" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="E490" s="27">
+        <v>0</v>
+      </c>
+      <c r="F490" s="27"/>
       <c r="G490" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12611,15 +12636,15 @@
         <v>36</v>
       </c>
       <c r="C491" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D491" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E491" s="24">
-        <v>-10000</v>
-      </c>
-      <c r="F491" s="24"/>
+        <v>126</v>
+      </c>
+      <c r="E491" s="25">
+        <v>-7200</v>
+      </c>
+      <c r="F491" s="25"/>
       <c r="G491" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12633,15 +12658,15 @@
         <v>36</v>
       </c>
       <c r="C492" t="s">
-        <v>295</v>
-      </c>
-      <c r="D492" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E492" s="34">
-        <v>-36900</v>
-      </c>
-      <c r="F492" s="34"/>
+        <v>298</v>
+      </c>
+      <c r="D492" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E492" s="25">
+        <v>-7200</v>
+      </c>
+      <c r="F492" s="25"/>
       <c r="G492" s="6">
         <f t="shared" si="7"/>
         <v>54</v>
@@ -12655,18 +12680,18 @@
         <v>36</v>
       </c>
       <c r="C493" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="D493" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E493" s="24">
-        <v>-1591</v>
-      </c>
-      <c r="F493" s="24"/>
+        <v>128</v>
+      </c>
+      <c r="E493" s="25">
+        <v>-10000</v>
+      </c>
+      <c r="F493" s="25"/>
       <c r="G493" s="6">
         <f t="shared" si="7"/>
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="494" ht="14.25">
@@ -12677,18 +12702,18 @@
         <v>36</v>
       </c>
       <c r="C494" t="s">
-        <v>259</v>
-      </c>
-      <c r="D494" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="E494" s="24">
-        <v>-20800</v>
-      </c>
-      <c r="F494" s="24"/>
+        <v>298</v>
+      </c>
+      <c r="D494" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E494" s="35">
+        <v>-36900</v>
+      </c>
+      <c r="F494" s="35"/>
       <c r="G494" s="6">
         <f t="shared" si="7"/>
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="495" ht="14.25">
@@ -12702,12 +12727,12 @@
         <v>259</v>
       </c>
       <c r="D495" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="E495" s="27">
-        <v>0</v>
-      </c>
-      <c r="F495" s="27"/>
+        <v>234</v>
+      </c>
+      <c r="E495" s="25">
+        <v>-1591</v>
+      </c>
+      <c r="F495" s="25"/>
       <c r="G495" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12724,12 +12749,12 @@
         <v>259</v>
       </c>
       <c r="D496" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="E496" s="24">
-        <v>0</v>
-      </c>
-      <c r="F496" s="24"/>
+        <v>235</v>
+      </c>
+      <c r="E496" s="25">
+        <v>-20800</v>
+      </c>
+      <c r="F496" s="25"/>
       <c r="G496" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12746,12 +12771,12 @@
         <v>259</v>
       </c>
       <c r="D497" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="E497" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F497" s="27"/>
+        <v>262</v>
+      </c>
+      <c r="E497" s="28">
+        <v>0</v>
+      </c>
+      <c r="F497" s="28"/>
       <c r="G497" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12768,12 +12793,12 @@
         <v>259</v>
       </c>
       <c r="D498" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E498" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F498" s="27"/>
+        <v>263</v>
+      </c>
+      <c r="E498" s="25">
+        <v>0</v>
+      </c>
+      <c r="F498" s="25"/>
       <c r="G498" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12790,12 +12815,12 @@
         <v>259</v>
       </c>
       <c r="D499" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E499" s="27">
-        <v>-250</v>
-      </c>
-      <c r="F499" s="27"/>
+        <v>237</v>
+      </c>
+      <c r="E499" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F499" s="28"/>
       <c r="G499" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12812,12 +12837,12 @@
         <v>259</v>
       </c>
       <c r="D500" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="E500" s="27">
-        <v>-1500</v>
-      </c>
-      <c r="F500" s="27"/>
+        <v>219</v>
+      </c>
+      <c r="E500" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F500" s="28"/>
       <c r="G500" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12834,10 +12859,10 @@
         <v>259</v>
       </c>
       <c r="D501" s="11" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="E501" s="28">
-        <v>-3000</v>
+        <v>-250</v>
       </c>
       <c r="F501" s="28"/>
       <c r="G501" s="6">
@@ -12856,12 +12881,12 @@
         <v>259</v>
       </c>
       <c r="D502" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E502" s="27">
-        <v>-1400</v>
-      </c>
-      <c r="F502" s="27"/>
+        <v>222</v>
+      </c>
+      <c r="E502" s="28">
+        <v>-1500</v>
+      </c>
+      <c r="F502" s="28"/>
       <c r="G502" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12878,12 +12903,12 @@
         <v>259</v>
       </c>
       <c r="D503" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E503" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F503" s="27"/>
+        <v>260</v>
+      </c>
+      <c r="E503" s="29">
+        <v>-3000</v>
+      </c>
+      <c r="F503" s="29"/>
       <c r="G503" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12900,12 +12925,12 @@
         <v>259</v>
       </c>
       <c r="D504" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E504" s="27">
-        <v>-300</v>
-      </c>
-      <c r="F504" s="27"/>
+        <v>224</v>
+      </c>
+      <c r="E504" s="28">
+        <v>-1400</v>
+      </c>
+      <c r="F504" s="28"/>
       <c r="G504" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12922,12 +12947,12 @@
         <v>259</v>
       </c>
       <c r="D505" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E505" s="27">
-        <v>-20000</v>
-      </c>
-      <c r="F505" s="27"/>
+        <v>225</v>
+      </c>
+      <c r="E505" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F505" s="28"/>
       <c r="G505" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12944,12 +12969,12 @@
         <v>259</v>
       </c>
       <c r="D506" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E506" s="27">
-        <v>-150</v>
-      </c>
-      <c r="F506" s="27"/>
+        <v>226</v>
+      </c>
+      <c r="E506" s="28">
+        <v>-300</v>
+      </c>
+      <c r="F506" s="28"/>
       <c r="G506" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12966,12 +12991,12 @@
         <v>259</v>
       </c>
       <c r="D507" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E507" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F507" s="27"/>
+        <v>261</v>
+      </c>
+      <c r="E507" s="28">
+        <v>-20000</v>
+      </c>
+      <c r="F507" s="28"/>
       <c r="G507" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -12988,12 +13013,12 @@
         <v>259</v>
       </c>
       <c r="D508" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E508" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F508" s="27"/>
+        <v>228</v>
+      </c>
+      <c r="E508" s="28">
+        <v>-150</v>
+      </c>
+      <c r="F508" s="28"/>
       <c r="G508" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -13010,12 +13035,12 @@
         <v>259</v>
       </c>
       <c r="D509" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="E509" s="27">
+        <v>229</v>
+      </c>
+      <c r="E509" s="28">
         <v>-200</v>
       </c>
-      <c r="F509" s="27"/>
+      <c r="F509" s="28"/>
       <c r="G509" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -13032,12 +13057,12 @@
         <v>259</v>
       </c>
       <c r="D510" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E510" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F510" s="27"/>
+        <v>230</v>
+      </c>
+      <c r="E510" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F510" s="28"/>
       <c r="G510" s="6">
         <f t="shared" si="7"/>
         <v>55</v>
@@ -13051,18 +13076,18 @@
         <v>36</v>
       </c>
       <c r="C511" t="s">
-        <v>297</v>
-      </c>
-      <c r="D511" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E511" s="26">
-        <v>-13337</v>
-      </c>
-      <c r="F511" s="26"/>
+        <v>259</v>
+      </c>
+      <c r="D511" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E511" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F511" s="28"/>
       <c r="G511" s="6">
         <f t="shared" si="7"/>
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="512" ht="14.25">
@@ -13073,18 +13098,18 @@
         <v>36</v>
       </c>
       <c r="C512" t="s">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="D512" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E512" s="24">
-        <v>-200</v>
-      </c>
-      <c r="F512" s="24"/>
+        <v>232</v>
+      </c>
+      <c r="E512" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F512" s="28"/>
       <c r="G512" s="6">
         <f t="shared" si="7"/>
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="513" ht="14.25">
@@ -13095,15 +13120,15 @@
         <v>36</v>
       </c>
       <c r="C513" t="s">
-        <v>297</v>
-      </c>
-      <c r="D513" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E513" s="24">
-        <v>-10500</v>
-      </c>
-      <c r="F513" s="24"/>
+        <v>300</v>
+      </c>
+      <c r="D513" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E513" s="27">
+        <v>-13337</v>
+      </c>
+      <c r="F513" s="27"/>
       <c r="G513" s="6">
         <f t="shared" si="7"/>
         <v>56</v>
@@ -13117,17 +13142,17 @@
         <v>36</v>
       </c>
       <c r="C514" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D514" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E514" s="24">
+        <v>98</v>
+      </c>
+      <c r="E514" s="25">
         <v>-200</v>
       </c>
-      <c r="F514" s="24"/>
+      <c r="F514" s="25"/>
       <c r="G514" s="6">
-        <f t="shared" ref="G514:G549" si="8">IF(C514=C513,G513,G513+1)</f>
+        <f t="shared" ref="G514:G551" si="8">IF(C514=C513,G513,G513+1)</f>
         <v>56</v>
       </c>
     </row>
@@ -13139,15 +13164,15 @@
         <v>36</v>
       </c>
       <c r="C515" t="s">
-        <v>297</v>
-      </c>
-      <c r="D515" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="E515" s="24">
-        <v>-2000</v>
-      </c>
-      <c r="F515" s="24"/>
+        <v>300</v>
+      </c>
+      <c r="D515" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E515" s="25">
+        <v>-10500</v>
+      </c>
+      <c r="F515" s="25"/>
       <c r="G515" s="6">
         <f t="shared" si="8"/>
         <v>56</v>
@@ -13161,15 +13186,15 @@
         <v>36</v>
       </c>
       <c r="C516" t="s">
-        <v>297</v>
-      </c>
-      <c r="D516" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="E516" s="24">
-        <v>-1000</v>
-      </c>
-      <c r="F516" s="24"/>
+        <v>300</v>
+      </c>
+      <c r="D516" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E516" s="25">
+        <v>-200</v>
+      </c>
+      <c r="F516" s="25"/>
       <c r="G516" s="6">
         <f t="shared" si="8"/>
         <v>56</v>
@@ -13183,15 +13208,15 @@
         <v>36</v>
       </c>
       <c r="C517" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D517" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E517" s="27">
-        <v>-6000</v>
-      </c>
-      <c r="F517" s="27"/>
+        <v>268</v>
+      </c>
+      <c r="E517" s="25">
+        <v>-2000</v>
+      </c>
+      <c r="F517" s="25"/>
       <c r="G517" s="6">
         <f t="shared" si="8"/>
         <v>56</v>
@@ -13205,15 +13230,15 @@
         <v>36</v>
       </c>
       <c r="C518" t="s">
-        <v>297</v>
-      </c>
-      <c r="D518" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E518" s="27">
-        <v>0</v>
-      </c>
-      <c r="F518" s="27"/>
+        <v>300</v>
+      </c>
+      <c r="D518" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="E518" s="25">
+        <v>-1000</v>
+      </c>
+      <c r="F518" s="25"/>
       <c r="G518" s="6">
         <f t="shared" si="8"/>
         <v>56</v>
@@ -13227,21 +13252,21 @@
         <v>36</v>
       </c>
       <c r="C519" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D519" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="E519" s="24">
-        <v>0</v>
-      </c>
-      <c r="F519" s="24"/>
+        <v>142</v>
+      </c>
+      <c r="E519" s="28">
+        <v>-6000</v>
+      </c>
+      <c r="F519" s="28"/>
       <c r="G519" s="6">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
     </row>
-    <row r="520" ht="15">
+    <row r="520" ht="14.25">
       <c r="A520" s="1">
         <v>2025</v>
       </c>
@@ -13249,15 +13274,15 @@
         <v>36</v>
       </c>
       <c r="C520" t="s">
-        <v>297</v>
-      </c>
-      <c r="D520" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="E520" s="36">
+        <v>300</v>
+      </c>
+      <c r="D520" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E520" s="28">
         <v>0</v>
       </c>
-      <c r="F520" s="36"/>
+      <c r="F520" s="28"/>
       <c r="G520" s="6">
         <f t="shared" si="8"/>
         <v>56</v>
@@ -13271,21 +13296,21 @@
         <v>36</v>
       </c>
       <c r="C521" t="s">
-        <v>299</v>
-      </c>
-      <c r="D521" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E521" s="27">
+        <v>300</v>
+      </c>
+      <c r="D521" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E521" s="25">
         <v>0</v>
       </c>
-      <c r="F521" s="27"/>
+      <c r="F521" s="25"/>
       <c r="G521" s="6">
         <f t="shared" si="8"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="522" ht="14.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="522" ht="15">
       <c r="A522" s="1">
         <v>2025</v>
       </c>
@@ -13293,18 +13318,18 @@
         <v>36</v>
       </c>
       <c r="C522" t="s">
-        <v>299</v>
-      </c>
-      <c r="D522" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E522" s="27">
-        <v>-500</v>
-      </c>
-      <c r="F522" s="27"/>
+        <v>300</v>
+      </c>
+      <c r="D522" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="E522" s="37">
+        <v>0</v>
+      </c>
+      <c r="F522" s="37"/>
       <c r="G522" s="6">
         <f t="shared" si="8"/>
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="523" ht="14.25">
@@ -13315,15 +13340,15 @@
         <v>36</v>
       </c>
       <c r="C523" t="s">
-        <v>299</v>
-      </c>
-      <c r="D523" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="E523" s="38">
-        <v>-5000</v>
-      </c>
-      <c r="F523" s="38"/>
+        <v>302</v>
+      </c>
+      <c r="D523" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E523" s="28">
+        <v>0</v>
+      </c>
+      <c r="F523" s="28"/>
       <c r="G523" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13337,15 +13362,15 @@
         <v>36</v>
       </c>
       <c r="C524" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D524" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E524" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F524" s="27"/>
+        <v>116</v>
+      </c>
+      <c r="E524" s="28">
+        <v>-500</v>
+      </c>
+      <c r="F524" s="28"/>
       <c r="G524" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13359,15 +13384,15 @@
         <v>36</v>
       </c>
       <c r="C525" t="s">
-        <v>299</v>
-      </c>
-      <c r="D525" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E525" s="27">
-        <v>-150</v>
-      </c>
-      <c r="F525" s="27"/>
+        <v>302</v>
+      </c>
+      <c r="D525" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="E525" s="39">
+        <v>-5000</v>
+      </c>
+      <c r="F525" s="39"/>
       <c r="G525" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13381,15 +13406,15 @@
         <v>36</v>
       </c>
       <c r="C526" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D526" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E526" s="27">
-        <v>-450</v>
-      </c>
-      <c r="F526" s="27"/>
+        <v>58</v>
+      </c>
+      <c r="E526" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F526" s="28"/>
       <c r="G526" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13403,15 +13428,15 @@
         <v>36</v>
       </c>
       <c r="C527" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D527" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E527" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F527" s="27"/>
+        <v>59</v>
+      </c>
+      <c r="E527" s="28">
+        <v>-150</v>
+      </c>
+      <c r="F527" s="28"/>
       <c r="G527" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13425,15 +13450,15 @@
         <v>36</v>
       </c>
       <c r="C528" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D528" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E528" s="27">
-        <v>-150</v>
-      </c>
-      <c r="F528" s="27"/>
+        <v>60</v>
+      </c>
+      <c r="E528" s="28">
+        <v>-450</v>
+      </c>
+      <c r="F528" s="28"/>
       <c r="G528" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13447,15 +13472,15 @@
         <v>36</v>
       </c>
       <c r="C529" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D529" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E529" s="27">
-        <v>-800</v>
-      </c>
-      <c r="F529" s="27"/>
+        <v>117</v>
+      </c>
+      <c r="E529" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F529" s="28"/>
       <c r="G529" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13469,15 +13494,15 @@
         <v>36</v>
       </c>
       <c r="C530" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D530" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E530" s="27">
+        <v>61</v>
+      </c>
+      <c r="E530" s="28">
         <v>-150</v>
       </c>
-      <c r="F530" s="27"/>
+      <c r="F530" s="28"/>
       <c r="G530" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13491,15 +13516,15 @@
         <v>36</v>
       </c>
       <c r="C531" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D531" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E531" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F531" s="27"/>
+        <v>62</v>
+      </c>
+      <c r="E531" s="28">
+        <v>-800</v>
+      </c>
+      <c r="F531" s="28"/>
       <c r="G531" s="6">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -13513,18 +13538,18 @@
         <v>36</v>
       </c>
       <c r="C532" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D532" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E532" s="25">
-        <v>0</v>
-      </c>
-      <c r="F532" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="E532" s="28">
+        <v>-150</v>
+      </c>
+      <c r="F532" s="28"/>
       <c r="G532" s="6">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="533" ht="14.25">
@@ -13535,18 +13560,18 @@
         <v>36</v>
       </c>
       <c r="C533" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D533" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E533" s="25">
-        <v>0</v>
-      </c>
-      <c r="F533" s="25"/>
+        <v>118</v>
+      </c>
+      <c r="E533" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F533" s="28"/>
       <c r="G533" s="6">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="534" ht="14.25">
@@ -13557,15 +13582,15 @@
         <v>36</v>
       </c>
       <c r="C534" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D534" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E534" s="25">
+        <v>75</v>
+      </c>
+      <c r="E534" s="26">
         <v>0</v>
       </c>
-      <c r="F534" s="25"/>
+      <c r="F534" s="26"/>
       <c r="G534" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13579,15 +13604,15 @@
         <v>36</v>
       </c>
       <c r="C535" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D535" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E535" s="25">
+        <v>76</v>
+      </c>
+      <c r="E535" s="26">
         <v>0</v>
       </c>
-      <c r="F535" s="25"/>
+      <c r="F535" s="26"/>
       <c r="G535" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13601,15 +13626,15 @@
         <v>36</v>
       </c>
       <c r="C536" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D536" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E536" s="25">
+        <v>77</v>
+      </c>
+      <c r="E536" s="26">
         <v>0</v>
       </c>
-      <c r="F536" s="25"/>
+      <c r="F536" s="26"/>
       <c r="G536" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13623,15 +13648,15 @@
         <v>36</v>
       </c>
       <c r="C537" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D537" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E537" s="25">
+        <v>78</v>
+      </c>
+      <c r="E537" s="26">
         <v>0</v>
       </c>
-      <c r="F537" s="25"/>
+      <c r="F537" s="26"/>
       <c r="G537" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13645,15 +13670,15 @@
         <v>36</v>
       </c>
       <c r="C538" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D538" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E538" s="25">
+        <v>79</v>
+      </c>
+      <c r="E538" s="26">
         <v>0</v>
       </c>
-      <c r="F538" s="25"/>
+      <c r="F538" s="26"/>
       <c r="G538" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13667,15 +13692,15 @@
         <v>36</v>
       </c>
       <c r="C539" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D539" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E539" s="25">
+        <v>80</v>
+      </c>
+      <c r="E539" s="26">
         <v>0</v>
       </c>
-      <c r="F539" s="25"/>
+      <c r="F539" s="26"/>
       <c r="G539" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13689,15 +13714,15 @@
         <v>36</v>
       </c>
       <c r="C540" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D540" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E540" s="27">
-        <v>-300</v>
-      </c>
-      <c r="F540" s="27"/>
+        <v>81</v>
+      </c>
+      <c r="E540" s="26">
+        <v>0</v>
+      </c>
+      <c r="F540" s="26"/>
       <c r="G540" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13711,15 +13736,15 @@
         <v>36</v>
       </c>
       <c r="C541" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D541" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E541" s="27">
-        <v>-200</v>
-      </c>
-      <c r="F541" s="27"/>
+        <v>82</v>
+      </c>
+      <c r="E541" s="26">
+        <v>0</v>
+      </c>
+      <c r="F541" s="26"/>
       <c r="G541" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13733,15 +13758,15 @@
         <v>36</v>
       </c>
       <c r="C542" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D542" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E542" s="27">
-        <v>-500</v>
-      </c>
-      <c r="F542" s="27"/>
+        <v>69</v>
+      </c>
+      <c r="E542" s="28">
+        <v>-300</v>
+      </c>
+      <c r="F542" s="28"/>
       <c r="G542" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13755,15 +13780,15 @@
         <v>36</v>
       </c>
       <c r="C543" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D543" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E543" s="27">
-        <v>-100</v>
-      </c>
-      <c r="F543" s="27"/>
+        <v>70</v>
+      </c>
+      <c r="E543" s="28">
+        <v>-200</v>
+      </c>
+      <c r="F543" s="28"/>
       <c r="G543" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13777,15 +13802,15 @@
         <v>36</v>
       </c>
       <c r="C544" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D544" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E544" s="27">
-        <v>-300</v>
-      </c>
-      <c r="F544" s="27"/>
+        <v>71</v>
+      </c>
+      <c r="E544" s="28">
+        <v>-500</v>
+      </c>
+      <c r="F544" s="28"/>
       <c r="G544" s="6">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -13799,18 +13824,18 @@
         <v>36</v>
       </c>
       <c r="C545" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D545" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E545" s="27">
-        <v>-1500</v>
-      </c>
-      <c r="F545" s="27"/>
+        <v>72</v>
+      </c>
+      <c r="E545" s="28">
+        <v>-100</v>
+      </c>
+      <c r="F545" s="28"/>
       <c r="G545" s="6">
         <f t="shared" si="8"/>
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="546" ht="14.25">
@@ -13821,18 +13846,18 @@
         <v>36</v>
       </c>
       <c r="C546" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D546" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E546" s="27">
-        <v>-500</v>
-      </c>
-      <c r="F546" s="27"/>
+        <v>73</v>
+      </c>
+      <c r="E546" s="28">
+        <v>-300</v>
+      </c>
+      <c r="F546" s="28"/>
       <c r="G546" s="6">
         <f t="shared" si="8"/>
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="547" ht="14.25">
@@ -13843,15 +13868,15 @@
         <v>36</v>
       </c>
       <c r="C547" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D547" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="E547" s="27">
-        <v>-300</v>
-      </c>
-      <c r="F547" s="27"/>
+        <v>132</v>
+      </c>
+      <c r="E547" s="28">
+        <v>-1500</v>
+      </c>
+      <c r="F547" s="28"/>
       <c r="G547" s="6">
         <f t="shared" si="8"/>
         <v>59</v>
@@ -13865,15 +13890,15 @@
         <v>36</v>
       </c>
       <c r="C548" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D548" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E548" s="27">
-        <v>-300</v>
-      </c>
-      <c r="F548" s="27"/>
+        <v>133</v>
+      </c>
+      <c r="E548" s="28">
+        <v>-500</v>
+      </c>
+      <c r="F548" s="28"/>
       <c r="G548" s="6">
         <f t="shared" si="8"/>
         <v>59</v>
@@ -13887,18 +13912,15 @@
         <v>36</v>
       </c>
       <c r="C549" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D549" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="E549" s="27">
-        <f>11*-450</f>
-        <v>-4950</v>
-      </c>
-      <c r="F549" s="27" t="s">
-        <v>303</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E549" s="28">
+        <v>-300</v>
+      </c>
+      <c r="F549" s="28"/>
       <c r="G549" s="6">
         <f t="shared" si="8"/>
         <v>59</v>
@@ -13915,15 +13937,15 @@
         <v>304</v>
       </c>
       <c r="D550" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E550" s="27">
-        <v>-500</v>
-      </c>
-      <c r="F550" s="27"/>
+        <v>135</v>
+      </c>
+      <c r="E550" s="28">
+        <v>-300</v>
+      </c>
+      <c r="F550" s="28"/>
       <c r="G550" s="6">
-        <f>IF(C550=C548,G548,G548+1)</f>
-        <v>60</v>
+        <f t="shared" si="8"/>
+        <v>59</v>
       </c>
     </row>
     <row r="551" ht="14.25">
@@ -13937,15 +13959,18 @@
         <v>304</v>
       </c>
       <c r="D551" s="11" t="s">
-        <v>101</v>
+        <v>305</v>
       </c>
       <c r="E551" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F551" s="27"/>
+        <f>11*-450</f>
+        <v>-4950</v>
+      </c>
+      <c r="F551" s="27" t="s">
+        <v>306</v>
+      </c>
       <c r="G551" s="6">
-        <f t="shared" ref="G551:G614" si="9">IF(C551=C550,G550,G550+1)</f>
-        <v>60</v>
+        <f t="shared" si="8"/>
+        <v>59</v>
       </c>
     </row>
     <row r="552" ht="14.25">
@@ -13955,109 +13980,111 @@
       <c r="B552" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C552" t="s">
+      <c r="C552" s="24" t="s">
         <v>304</v>
       </c>
       <c r="D552" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="E552" s="27">
+        <v>-1000</v>
+      </c>
+      <c r="F552" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="G552" s="6">
+        <f>IF(C552=C551,G551,G551+1)</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="553" ht="14.25">
+      <c r="A553" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C553" t="s">
+        <v>309</v>
+      </c>
+      <c r="D553" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E553" s="28">
+        <v>-500</v>
+      </c>
+      <c r="F553" s="28"/>
+      <c r="G553" s="6">
+        <f>IF(C553=C550,G550,G550+1)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="554" ht="14.25">
+      <c r="A554" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C554" t="s">
+        <v>309</v>
+      </c>
+      <c r="D554" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E554" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F554" s="28"/>
+      <c r="G554" s="6">
+        <f t="shared" ref="G554:G617" si="9">IF(C554=C553,G553,G553+1)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="555" ht="14.25">
+      <c r="A555" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C555" t="s">
+        <v>309</v>
+      </c>
+      <c r="D555" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E552" s="24">
+      <c r="E555" s="25">
         <v>0</v>
       </c>
-      <c r="F552" s="24"/>
-      <c r="G552" s="6">
+      <c r="F555" s="25"/>
+      <c r="G555" s="6">
         <f t="shared" si="9"/>
         <v>60</v>
       </c>
     </row>
-    <row r="553" ht="14.25">
-      <c r="A553" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B553" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C553" t="s">
-        <v>304</v>
-      </c>
-      <c r="D553" s="11" t="s">
+    <row r="556" ht="14.25">
+      <c r="A556" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C556" t="s">
+        <v>309</v>
+      </c>
+      <c r="D556" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E553" s="27">
+      <c r="E556" s="28">
         <v>-1000</v>
       </c>
-      <c r="F553" s="27"/>
-      <c r="G553" s="6">
+      <c r="F556" s="28"/>
+      <c r="G556" s="6">
         <f t="shared" si="9"/>
         <v>60</v>
       </c>
     </row>
-    <row r="554" ht="14.25">
-      <c r="A554" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B554" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C554" t="s">
-        <v>305</v>
-      </c>
-      <c r="D554" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E554" s="27">
-        <v>-7571</v>
-      </c>
-      <c r="F554" s="27"/>
-      <c r="G554" s="6">
-        <f t="shared" si="9"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="555" ht="14.25">
-      <c r="A555" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B555" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C555" t="s">
-        <v>305</v>
-      </c>
-      <c r="D555" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="E555" s="24">
-        <v>-98959</v>
-      </c>
-      <c r="F555" s="24"/>
-      <c r="G555" s="6">
-        <f t="shared" si="9"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="556" ht="14.25">
-      <c r="A556" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B556" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C556" t="s">
-        <v>305</v>
-      </c>
-      <c r="D556" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E556" s="27">
-        <v>-15000</v>
-      </c>
-      <c r="F556" s="27"/>
-      <c r="G556" s="6">
-        <f t="shared" si="9"/>
-        <v>61</v>
-      </c>
-    </row>
     <row r="557" ht="14.25">
       <c r="A557" s="1">
         <v>2025</v>
@@ -14066,15 +14093,15 @@
         <v>36</v>
       </c>
       <c r="C557" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D557" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="E557" s="27">
-        <v>-2699</v>
-      </c>
-      <c r="F557" s="27"/>
+        <v>174</v>
+      </c>
+      <c r="E557" s="28">
+        <v>-7571</v>
+      </c>
+      <c r="F557" s="28"/>
       <c r="G557" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14088,15 +14115,15 @@
         <v>36</v>
       </c>
       <c r="C558" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D558" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E558" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F558" s="27"/>
+        <v>175</v>
+      </c>
+      <c r="E558" s="25">
+        <v>-98959</v>
+      </c>
+      <c r="F558" s="25"/>
       <c r="G558" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14110,15 +14137,15 @@
         <v>36</v>
       </c>
       <c r="C559" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D559" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="E559" s="27">
-        <v>-3000</v>
-      </c>
-      <c r="F559" s="27"/>
+        <v>176</v>
+      </c>
+      <c r="E559" s="28">
+        <v>-15000</v>
+      </c>
+      <c r="F559" s="28"/>
       <c r="G559" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14132,15 +14159,15 @@
         <v>36</v>
       </c>
       <c r="C560" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D560" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E560" s="27">
-        <v>-750</v>
-      </c>
-      <c r="F560" s="27"/>
+        <v>177</v>
+      </c>
+      <c r="E560" s="28">
+        <v>-2699</v>
+      </c>
+      <c r="F560" s="28"/>
       <c r="G560" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14154,15 +14181,15 @@
         <v>36</v>
       </c>
       <c r="C561" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D561" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E561" s="27">
-        <v>-8850</v>
-      </c>
-      <c r="F561" s="27"/>
+        <v>178</v>
+      </c>
+      <c r="E561" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F561" s="28"/>
       <c r="G561" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14176,15 +14203,15 @@
         <v>36</v>
       </c>
       <c r="C562" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D562" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E562" s="27">
-        <v>-9500</v>
-      </c>
-      <c r="F562" s="27"/>
+        <v>277</v>
+      </c>
+      <c r="E562" s="28">
+        <v>-3000</v>
+      </c>
+      <c r="F562" s="28"/>
       <c r="G562" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14198,15 +14225,15 @@
         <v>36</v>
       </c>
       <c r="C563" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D563" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E563" s="27">
-        <v>-950</v>
-      </c>
-      <c r="F563" s="27"/>
+        <v>146</v>
+      </c>
+      <c r="E563" s="28">
+        <v>-750</v>
+      </c>
+      <c r="F563" s="28"/>
       <c r="G563" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14220,15 +14247,15 @@
         <v>36</v>
       </c>
       <c r="C564" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D564" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E564" s="27">
-        <v>-1500</v>
-      </c>
-      <c r="F564" s="27"/>
+        <v>147</v>
+      </c>
+      <c r="E564" s="28">
+        <v>-8850</v>
+      </c>
+      <c r="F564" s="28"/>
       <c r="G564" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14242,15 +14269,15 @@
         <v>36</v>
       </c>
       <c r="C565" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D565" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E565" s="27">
-        <v>-5000</v>
-      </c>
-      <c r="F565" s="27"/>
+        <v>148</v>
+      </c>
+      <c r="E565" s="28">
+        <v>-9500</v>
+      </c>
+      <c r="F565" s="28"/>
       <c r="G565" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14264,15 +14291,15 @@
         <v>36</v>
       </c>
       <c r="C566" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D566" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E566" s="27">
-        <v>-2300</v>
-      </c>
-      <c r="F566" s="27"/>
+        <v>149</v>
+      </c>
+      <c r="E566" s="28">
+        <v>-950</v>
+      </c>
+      <c r="F566" s="28"/>
       <c r="G566" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14286,15 +14313,15 @@
         <v>36</v>
       </c>
       <c r="C567" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D567" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E567" s="27">
-        <v>-4300</v>
-      </c>
-      <c r="F567" s="27"/>
+        <v>150</v>
+      </c>
+      <c r="E567" s="28">
+        <v>-1500</v>
+      </c>
+      <c r="F567" s="28"/>
       <c r="G567" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14308,15 +14335,15 @@
         <v>36</v>
       </c>
       <c r="C568" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D568" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E568" s="27">
-        <v>-10950</v>
-      </c>
-      <c r="F568" s="27"/>
+        <v>151</v>
+      </c>
+      <c r="E568" s="28">
+        <v>-5000</v>
+      </c>
+      <c r="F568" s="28"/>
       <c r="G568" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14330,15 +14357,15 @@
         <v>36</v>
       </c>
       <c r="C569" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D569" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E569" s="27">
-        <v>0</v>
-      </c>
-      <c r="F569" s="27"/>
+        <v>152</v>
+      </c>
+      <c r="E569" s="28">
+        <v>-2300</v>
+      </c>
+      <c r="F569" s="28"/>
       <c r="G569" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14352,15 +14379,15 @@
         <v>36</v>
       </c>
       <c r="C570" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D570" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E570" s="27">
-        <v>0</v>
-      </c>
-      <c r="F570" s="27"/>
+        <v>153</v>
+      </c>
+      <c r="E570" s="28">
+        <v>-4300</v>
+      </c>
+      <c r="F570" s="28"/>
       <c r="G570" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14374,15 +14401,15 @@
         <v>36</v>
       </c>
       <c r="C571" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D571" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E571" s="27">
-        <v>0</v>
-      </c>
-      <c r="F571" s="27"/>
+        <v>154</v>
+      </c>
+      <c r="E571" s="28">
+        <v>-10950</v>
+      </c>
+      <c r="F571" s="28"/>
       <c r="G571" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14396,15 +14423,15 @@
         <v>36</v>
       </c>
       <c r="C572" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D572" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E572" s="27">
+        <v>155</v>
+      </c>
+      <c r="E572" s="28">
         <v>0</v>
       </c>
-      <c r="F572" s="27"/>
+      <c r="F572" s="28"/>
       <c r="G572" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14418,15 +14445,15 @@
         <v>36</v>
       </c>
       <c r="C573" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D573" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E573" s="27">
-        <v>-1500</v>
-      </c>
-      <c r="F573" s="27"/>
+        <v>156</v>
+      </c>
+      <c r="E573" s="28">
+        <v>0</v>
+      </c>
+      <c r="F573" s="28"/>
       <c r="G573" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14440,15 +14467,15 @@
         <v>36</v>
       </c>
       <c r="C574" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D574" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="E574" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F574" s="27"/>
+        <v>157</v>
+      </c>
+      <c r="E574" s="28">
+        <v>0</v>
+      </c>
+      <c r="F574" s="28"/>
       <c r="G574" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14462,15 +14489,15 @@
         <v>36</v>
       </c>
       <c r="C575" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D575" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E575" s="27">
-        <v>-13500</v>
-      </c>
-      <c r="F575" s="27"/>
+        <v>158</v>
+      </c>
+      <c r="E575" s="28">
+        <v>0</v>
+      </c>
+      <c r="F575" s="28"/>
       <c r="G575" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14484,15 +14511,15 @@
         <v>36</v>
       </c>
       <c r="C576" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D576" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E576" s="27">
-        <v>-5000</v>
-      </c>
-      <c r="F576" s="27"/>
+        <v>159</v>
+      </c>
+      <c r="E576" s="28">
+        <v>-1500</v>
+      </c>
+      <c r="F576" s="28"/>
       <c r="G576" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14506,15 +14533,15 @@
         <v>36</v>
       </c>
       <c r="C577" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D577" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E577" s="27">
-        <v>-14700</v>
-      </c>
-      <c r="F577" s="27"/>
+        <v>160</v>
+      </c>
+      <c r="E577" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F577" s="28"/>
       <c r="G577" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14528,15 +14555,15 @@
         <v>36</v>
       </c>
       <c r="C578" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D578" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E578" s="27">
-        <v>-39900</v>
-      </c>
-      <c r="F578" s="27"/>
+        <v>161</v>
+      </c>
+      <c r="E578" s="28">
+        <v>-13500</v>
+      </c>
+      <c r="F578" s="28"/>
       <c r="G578" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14550,15 +14577,15 @@
         <v>36</v>
       </c>
       <c r="C579" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D579" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E579" s="27">
-        <v>-2200</v>
-      </c>
-      <c r="F579" s="27"/>
+        <v>162</v>
+      </c>
+      <c r="E579" s="28">
+        <v>-5000</v>
+      </c>
+      <c r="F579" s="28"/>
       <c r="G579" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14572,15 +14599,15 @@
         <v>36</v>
       </c>
       <c r="C580" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D580" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E580" s="27">
-        <v>-4000</v>
-      </c>
-      <c r="F580" s="27"/>
+        <v>163</v>
+      </c>
+      <c r="E580" s="28">
+        <v>-14700</v>
+      </c>
+      <c r="F580" s="28"/>
       <c r="G580" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14594,15 +14621,15 @@
         <v>36</v>
       </c>
       <c r="C581" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D581" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E581" s="27">
-        <v>-3000</v>
-      </c>
-      <c r="F581" s="27"/>
+        <v>164</v>
+      </c>
+      <c r="E581" s="28">
+        <v>-39900</v>
+      </c>
+      <c r="F581" s="28"/>
       <c r="G581" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14616,15 +14643,15 @@
         <v>36</v>
       </c>
       <c r="C582" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D582" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E582" s="27">
-        <v>-3000</v>
-      </c>
-      <c r="F582" s="27"/>
+        <v>165</v>
+      </c>
+      <c r="E582" s="28">
+        <v>-2200</v>
+      </c>
+      <c r="F582" s="28"/>
       <c r="G582" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14638,15 +14665,15 @@
         <v>36</v>
       </c>
       <c r="C583" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D583" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E583" s="27">
+        <v>166</v>
+      </c>
+      <c r="E583" s="28">
         <v>-4000</v>
       </c>
-      <c r="F583" s="27"/>
+      <c r="F583" s="28"/>
       <c r="G583" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14660,15 +14687,15 @@
         <v>36</v>
       </c>
       <c r="C584" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D584" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E584" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F584" s="27"/>
+        <v>167</v>
+      </c>
+      <c r="E584" s="28">
+        <v>-3000</v>
+      </c>
+      <c r="F584" s="28"/>
       <c r="G584" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14682,15 +14709,15 @@
         <v>36</v>
       </c>
       <c r="C585" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D585" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E585" s="26">
-        <v>-60000</v>
-      </c>
-      <c r="F585" s="26"/>
+        <v>168</v>
+      </c>
+      <c r="E585" s="28">
+        <v>-3000</v>
+      </c>
+      <c r="F585" s="28"/>
       <c r="G585" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14704,15 +14731,15 @@
         <v>36</v>
       </c>
       <c r="C586" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D586" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="E586" s="27">
-        <v>-500</v>
-      </c>
-      <c r="F586" s="27"/>
+        <v>169</v>
+      </c>
+      <c r="E586" s="28">
+        <v>-4000</v>
+      </c>
+      <c r="F586" s="28"/>
       <c r="G586" s="6">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -14726,18 +14753,18 @@
         <v>36</v>
       </c>
       <c r="C587" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D587" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E587" s="24">
-        <v>0</v>
-      </c>
-      <c r="F587" s="24"/>
+        <v>170</v>
+      </c>
+      <c r="E587" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F587" s="28"/>
       <c r="G587" s="6">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="588" ht="14.25">
@@ -14748,18 +14775,18 @@
         <v>36</v>
       </c>
       <c r="C588" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D588" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E588" s="24">
-        <v>-40000</v>
-      </c>
-      <c r="F588" s="24"/>
+        <v>171</v>
+      </c>
+      <c r="E588" s="27">
+        <v>-60000</v>
+      </c>
+      <c r="F588" s="27"/>
       <c r="G588" s="6">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="589" ht="14.25">
@@ -14770,18 +14797,18 @@
         <v>36</v>
       </c>
       <c r="C589" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D589" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E589" s="24">
-        <v>-37000</v>
-      </c>
-      <c r="F589" s="24"/>
+        <v>278</v>
+      </c>
+      <c r="E589" s="28">
+        <v>-500</v>
+      </c>
+      <c r="F589" s="28"/>
       <c r="G589" s="6">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="590" ht="14.25">
@@ -14792,15 +14819,15 @@
         <v>36</v>
       </c>
       <c r="C590" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D590" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E590" s="24">
-        <v>-2000</v>
-      </c>
-      <c r="F590" s="24"/>
+        <v>105</v>
+      </c>
+      <c r="E590" s="25">
+        <v>0</v>
+      </c>
+      <c r="F590" s="25"/>
       <c r="G590" s="6">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -14814,15 +14841,15 @@
         <v>36</v>
       </c>
       <c r="C591" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D591" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E591" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F591" s="27"/>
+        <v>106</v>
+      </c>
+      <c r="E591" s="25">
+        <v>-40000</v>
+      </c>
+      <c r="F591" s="25"/>
       <c r="G591" s="6">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -14836,15 +14863,15 @@
         <v>36</v>
       </c>
       <c r="C592" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D592" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E592" s="27">
-        <v>-6000</v>
-      </c>
-      <c r="F592" s="27"/>
+        <v>107</v>
+      </c>
+      <c r="E592" s="25">
+        <v>-37000</v>
+      </c>
+      <c r="F592" s="25"/>
       <c r="G592" s="6">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -14858,15 +14885,15 @@
         <v>36</v>
       </c>
       <c r="C593" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D593" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E593" s="27">
-        <v>-250</v>
-      </c>
-      <c r="F593" s="27"/>
+        <v>281</v>
+      </c>
+      <c r="E593" s="25">
+        <v>-2000</v>
+      </c>
+      <c r="F593" s="25"/>
       <c r="G593" s="6">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -14880,15 +14907,15 @@
         <v>36</v>
       </c>
       <c r="C594" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D594" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E594" s="27">
-        <v>-5000</v>
-      </c>
-      <c r="F594" s="27"/>
+        <v>109</v>
+      </c>
+      <c r="E594" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F594" s="28"/>
       <c r="G594" s="6">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -14902,15 +14929,15 @@
         <v>36</v>
       </c>
       <c r="C595" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D595" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E595" s="27">
-        <v>-500</v>
-      </c>
-      <c r="F595" s="27"/>
+        <v>110</v>
+      </c>
+      <c r="E595" s="28">
+        <v>-6000</v>
+      </c>
+      <c r="F595" s="28"/>
       <c r="G595" s="6">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -14924,18 +14951,18 @@
         <v>36</v>
       </c>
       <c r="C596" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D596" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E596" s="24">
-        <v>-3525</v>
-      </c>
-      <c r="F596" s="24"/>
+        <v>111</v>
+      </c>
+      <c r="E596" s="28">
+        <v>-250</v>
+      </c>
+      <c r="F596" s="28"/>
       <c r="G596" s="6">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="597" ht="14.25">
@@ -14946,18 +14973,18 @@
         <v>36</v>
       </c>
       <c r="C597" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D597" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E597" s="39">
-        <v>0</v>
-      </c>
-      <c r="F597" s="39"/>
+        <v>112</v>
+      </c>
+      <c r="E597" s="28">
+        <v>-5000</v>
+      </c>
+      <c r="F597" s="28"/>
       <c r="G597" s="6">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="598" ht="14.25">
@@ -14968,18 +14995,18 @@
         <v>36</v>
       </c>
       <c r="C598" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D598" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E598" s="27">
-        <v>-375</v>
-      </c>
-      <c r="F598" s="27"/>
+        <v>113</v>
+      </c>
+      <c r="E598" s="28">
+        <v>-500</v>
+      </c>
+      <c r="F598" s="28"/>
       <c r="G598" s="6">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="599" ht="14.25">
@@ -14990,18 +15017,18 @@
         <v>36</v>
       </c>
       <c r="C599" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D599" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E599" s="27">
-        <v>-8417</v>
-      </c>
-      <c r="F599" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="E599" s="25">
+        <v>-3525</v>
+      </c>
+      <c r="F599" s="25"/>
       <c r="G599" s="6">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="600" ht="14.25">
@@ -15012,18 +15039,18 @@
         <v>36</v>
       </c>
       <c r="C600" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D600" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E600" s="24">
-        <v>-110016</v>
-      </c>
-      <c r="F600" s="24"/>
+        <v>66</v>
+      </c>
+      <c r="E600" s="40">
+        <v>0</v>
+      </c>
+      <c r="F600" s="40"/>
       <c r="G600" s="6">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="601" ht="14.25">
@@ -15034,18 +15061,18 @@
         <v>36</v>
       </c>
       <c r="C601" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D601" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E601" s="27">
-        <v>-2624</v>
-      </c>
-      <c r="F601" s="27"/>
+        <v>67</v>
+      </c>
+      <c r="E601" s="28">
+        <v>-375</v>
+      </c>
+      <c r="F601" s="28"/>
       <c r="G601" s="6">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="602" ht="14.25">
@@ -15056,15 +15083,15 @@
         <v>36</v>
       </c>
       <c r="C602" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D602" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E602" s="27">
-        <v>-15000</v>
-      </c>
-      <c r="F602" s="27"/>
+        <v>52</v>
+      </c>
+      <c r="E602" s="28">
+        <v>-8417</v>
+      </c>
+      <c r="F602" s="28"/>
       <c r="G602" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15078,15 +15105,15 @@
         <v>36</v>
       </c>
       <c r="C603" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D603" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E603" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F603" s="27"/>
+        <v>53</v>
+      </c>
+      <c r="E603" s="25">
+        <v>-110016</v>
+      </c>
+      <c r="F603" s="25"/>
       <c r="G603" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15100,15 +15127,15 @@
         <v>36</v>
       </c>
       <c r="C604" t="s">
-        <v>308</v>
-      </c>
-      <c r="D604" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="E604" s="38">
-        <v>-1000</v>
-      </c>
-      <c r="F604" s="38"/>
+        <v>313</v>
+      </c>
+      <c r="D604" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E604" s="28">
+        <v>-2624</v>
+      </c>
+      <c r="F604" s="28"/>
       <c r="G604" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15122,15 +15149,15 @@
         <v>36</v>
       </c>
       <c r="C605" t="s">
-        <v>308</v>
-      </c>
-      <c r="D605" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="E605" s="38">
-        <v>-2000</v>
-      </c>
-      <c r="F605" s="38"/>
+        <v>313</v>
+      </c>
+      <c r="D605" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E605" s="28">
+        <v>-15000</v>
+      </c>
+      <c r="F605" s="28"/>
       <c r="G605" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15144,15 +15171,15 @@
         <v>36</v>
       </c>
       <c r="C606" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D606" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E606" s="24">
-        <v>-3500</v>
-      </c>
-      <c r="F606" s="24"/>
+        <v>56</v>
+      </c>
+      <c r="E606" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F606" s="28"/>
       <c r="G606" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15166,15 +15193,15 @@
         <v>36</v>
       </c>
       <c r="C607" t="s">
-        <v>308</v>
-      </c>
-      <c r="D607" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E607" s="24">
-        <v>0</v>
-      </c>
-      <c r="F607" s="24"/>
+        <v>313</v>
+      </c>
+      <c r="D607" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="E607" s="39">
+        <v>-1000</v>
+      </c>
+      <c r="F607" s="39"/>
       <c r="G607" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15188,15 +15215,15 @@
         <v>36</v>
       </c>
       <c r="C608" t="s">
-        <v>308</v>
-      </c>
-      <c r="D608" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E608" s="24">
-        <v>-1000</v>
-      </c>
-      <c r="F608" s="24"/>
+        <v>313</v>
+      </c>
+      <c r="D608" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="E608" s="39">
+        <v>-2000</v>
+      </c>
+      <c r="F608" s="39"/>
       <c r="G608" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15210,15 +15237,15 @@
         <v>36</v>
       </c>
       <c r="C609" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D609" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E609" s="24">
-        <v>-13200</v>
-      </c>
-      <c r="F609" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="E609" s="25">
+        <v>-3500</v>
+      </c>
+      <c r="F609" s="25"/>
       <c r="G609" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15232,15 +15259,15 @@
         <v>36</v>
       </c>
       <c r="C610" t="s">
-        <v>308</v>
-      </c>
-      <c r="D610" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E610" s="24">
-        <v>-4000</v>
-      </c>
-      <c r="F610" s="24"/>
+        <v>313</v>
+      </c>
+      <c r="D610" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E610" s="25">
+        <v>0</v>
+      </c>
+      <c r="F610" s="25"/>
       <c r="G610" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15254,15 +15281,15 @@
         <v>36</v>
       </c>
       <c r="C611" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D611" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E611" s="24">
-        <v>-3000</v>
-      </c>
-      <c r="F611" s="24"/>
+        <v>40</v>
+      </c>
+      <c r="E611" s="25">
+        <v>-1000</v>
+      </c>
+      <c r="F611" s="25"/>
       <c r="G611" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15276,15 +15303,15 @@
         <v>36</v>
       </c>
       <c r="C612" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D612" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E612" s="24">
-        <v>-1500</v>
-      </c>
-      <c r="F612" s="24"/>
+        <v>41</v>
+      </c>
+      <c r="E612" s="25">
+        <v>-13200</v>
+      </c>
+      <c r="F612" s="25"/>
       <c r="G612" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15298,15 +15325,15 @@
         <v>36</v>
       </c>
       <c r="C613" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D613" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E613" s="24">
-        <v>-2000</v>
-      </c>
-      <c r="F613" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="E613" s="25">
+        <v>-4000</v>
+      </c>
+      <c r="F613" s="25"/>
       <c r="G613" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15320,15 +15347,15 @@
         <v>36</v>
       </c>
       <c r="C614" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D614" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E614" s="24">
+        <v>43</v>
+      </c>
+      <c r="E614" s="25">
         <v>-3000</v>
       </c>
-      <c r="F614" s="24"/>
+      <c r="F614" s="25"/>
       <c r="G614" s="6">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -15342,17 +15369,17 @@
         <v>36</v>
       </c>
       <c r="C615" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D615" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E615" s="24">
-        <v>-2500</v>
-      </c>
-      <c r="F615" s="24"/>
+        <v>44</v>
+      </c>
+      <c r="E615" s="25">
+        <v>-1500</v>
+      </c>
+      <c r="F615" s="25"/>
       <c r="G615" s="6">
-        <f t="shared" ref="G615:G629" si="10">IF(C615=C614,G614,G614+1)</f>
+        <f t="shared" si="9"/>
         <v>64</v>
       </c>
     </row>
@@ -15364,17 +15391,17 @@
         <v>36</v>
       </c>
       <c r="C616" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D616" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="E616" s="24">
-        <v>-1000</v>
-      </c>
-      <c r="F616" s="24"/>
+        <v>45</v>
+      </c>
+      <c r="E616" s="25">
+        <v>-2000</v>
+      </c>
+      <c r="F616" s="25"/>
       <c r="G616" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>64</v>
       </c>
     </row>
@@ -15386,17 +15413,17 @@
         <v>36</v>
       </c>
       <c r="C617" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D617" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E617" s="24">
-        <v>-1000</v>
-      </c>
-      <c r="F617" s="24"/>
+        <v>46</v>
+      </c>
+      <c r="E617" s="25">
+        <v>-3000</v>
+      </c>
+      <c r="F617" s="25"/>
       <c r="G617" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>64</v>
       </c>
     </row>
@@ -15408,17 +15435,17 @@
         <v>36</v>
       </c>
       <c r="C618" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D618" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E618" s="24">
-        <v>-5000</v>
-      </c>
-      <c r="F618" s="24"/>
+        <v>47</v>
+      </c>
+      <c r="E618" s="25">
+        <v>-2500</v>
+      </c>
+      <c r="F618" s="25"/>
       <c r="G618" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="G618:G632" si="10">IF(C618=C617,G617,G617+1)</f>
         <v>64</v>
       </c>
     </row>
@@ -15430,15 +15457,15 @@
         <v>36</v>
       </c>
       <c r="C619" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D619" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E619" s="24">
-        <v>-6000</v>
-      </c>
-      <c r="F619" s="24"/>
+        <v>284</v>
+      </c>
+      <c r="E619" s="25">
+        <v>-1000</v>
+      </c>
+      <c r="F619" s="25"/>
       <c r="G619" s="6">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -15452,18 +15479,18 @@
         <v>36</v>
       </c>
       <c r="C620" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D620" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="E620" s="27">
-        <v>-1500</v>
-      </c>
-      <c r="F620" s="27"/>
+        <v>48</v>
+      </c>
+      <c r="E620" s="25">
+        <v>-1000</v>
+      </c>
+      <c r="F620" s="25"/>
       <c r="G620" s="6">
         <f t="shared" si="10"/>
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="621" ht="14.25">
@@ -15474,18 +15501,18 @@
         <v>36</v>
       </c>
       <c r="C621" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D621" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E621" s="27">
-        <v>-1000</v>
-      </c>
-      <c r="F621" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="E621" s="25">
+        <v>-5000</v>
+      </c>
+      <c r="F621" s="25"/>
       <c r="G621" s="6">
         <f t="shared" si="10"/>
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="622" ht="14.25">
@@ -15496,18 +15523,18 @@
         <v>36</v>
       </c>
       <c r="C622" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D622" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E622" s="27">
-        <v>-2000</v>
-      </c>
-      <c r="F622" s="27"/>
+        <v>50</v>
+      </c>
+      <c r="E622" s="25">
+        <v>-6000</v>
+      </c>
+      <c r="F622" s="25"/>
       <c r="G622" s="6">
         <f t="shared" si="10"/>
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="623" ht="14.25">
@@ -15518,15 +15545,15 @@
         <v>36</v>
       </c>
       <c r="C623" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D623" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E623" s="27">
-        <v>-750</v>
-      </c>
-      <c r="F623" s="27"/>
+        <v>286</v>
+      </c>
+      <c r="E623" s="28">
+        <v>-1500</v>
+      </c>
+      <c r="F623" s="28"/>
       <c r="G623" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -15540,15 +15567,15 @@
         <v>36</v>
       </c>
       <c r="C624" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D624" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E624" s="27">
-        <v>-2000</v>
-      </c>
-      <c r="F624" s="27"/>
+        <v>85</v>
+      </c>
+      <c r="E624" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="F624" s="28"/>
       <c r="G624" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -15562,15 +15589,15 @@
         <v>36</v>
       </c>
       <c r="C625" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D625" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="E625" s="27">
+        <v>86</v>
+      </c>
+      <c r="E625" s="28">
         <v>-2000</v>
       </c>
-      <c r="F625" s="27"/>
+      <c r="F625" s="28"/>
       <c r="G625" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -15584,15 +15611,15 @@
         <v>36</v>
       </c>
       <c r="C626" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D626" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E626" s="24">
-        <v>-19200</v>
-      </c>
-      <c r="F626" s="24"/>
+        <v>87</v>
+      </c>
+      <c r="E626" s="28">
+        <v>-750</v>
+      </c>
+      <c r="F626" s="28"/>
       <c r="G626" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -15606,15 +15633,15 @@
         <v>36</v>
       </c>
       <c r="C627" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D627" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E627" s="27">
-        <v>-1296</v>
-      </c>
-      <c r="F627" s="27"/>
+        <v>88</v>
+      </c>
+      <c r="E627" s="28">
+        <v>-2000</v>
+      </c>
+      <c r="F627" s="28"/>
       <c r="G627" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -15628,15 +15655,15 @@
         <v>36</v>
       </c>
       <c r="C628" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D628" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E628" s="27">
-        <v>0</v>
-      </c>
-      <c r="F628" s="27"/>
+        <v>317</v>
+      </c>
+      <c r="E628" s="28">
+        <v>-2000</v>
+      </c>
+      <c r="F628" s="28"/>
       <c r="G628" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -15650,235 +15677,283 @@
         <v>36</v>
       </c>
       <c r="C629" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D629" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E629" s="27">
-        <v>0</v>
-      </c>
-      <c r="F629" s="27"/>
+        <v>91</v>
+      </c>
+      <c r="E629" s="25">
+        <v>-19200</v>
+      </c>
+      <c r="F629" s="25"/>
       <c r="G629" s="6">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
     </row>
     <row r="630" ht="14.25">
-      <c r="C630"/>
-      <c r="D630" s="40"/>
-      <c r="E630" s="12"/>
-      <c r="F630" s="12"/>
+      <c r="A630" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C630" t="s">
+        <v>316</v>
+      </c>
+      <c r="D630" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E630" s="28">
+        <v>-1296</v>
+      </c>
+      <c r="F630" s="28"/>
+      <c r="G630" s="6">
+        <f t="shared" si="10"/>
+        <v>65</v>
+      </c>
     </row>
     <row r="631" ht="14.25">
-      <c r="C631"/>
-      <c r="D631" s="40"/>
-      <c r="E631" s="12"/>
-      <c r="F631" s="12"/>
+      <c r="A631" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C631" t="s">
+        <v>316</v>
+      </c>
+      <c r="D631" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E631" s="28">
+        <v>0</v>
+      </c>
+      <c r="F631" s="28"/>
+      <c r="G631" s="6">
+        <f t="shared" si="10"/>
+        <v>65</v>
+      </c>
     </row>
     <row r="632" ht="14.25">
-      <c r="C632"/>
-      <c r="D632" s="11"/>
-      <c r="E632" s="12"/>
-      <c r="F632" s="12"/>
+      <c r="A632" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C632" t="s">
+        <v>316</v>
+      </c>
+      <c r="D632" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E632" s="28">
+        <v>0</v>
+      </c>
+      <c r="F632" s="28"/>
+      <c r="G632" s="6">
+        <f t="shared" si="10"/>
+        <v>65</v>
+      </c>
     </row>
     <row r="633" ht="14.25">
       <c r="C633"/>
-      <c r="D633" s="40"/>
+      <c r="D633" s="41"/>
       <c r="E633" s="12"/>
       <c r="F633" s="12"/>
     </row>
     <row r="634" ht="14.25">
       <c r="C634"/>
-      <c r="D634" s="40"/>
+      <c r="D634" s="41"/>
       <c r="E634" s="12"/>
       <c r="F634" s="12"/>
     </row>
     <row r="635" ht="14.25">
       <c r="C635"/>
-      <c r="D635" s="40"/>
+      <c r="D635" s="11"/>
       <c r="E635" s="12"/>
       <c r="F635" s="12"/>
     </row>
     <row r="636" ht="14.25">
       <c r="C636"/>
-      <c r="D636" s="40"/>
+      <c r="D636" s="41"/>
       <c r="E636" s="12"/>
       <c r="F636" s="12"/>
     </row>
     <row r="637" ht="14.25">
       <c r="C637"/>
-      <c r="D637" s="40"/>
+      <c r="D637" s="41"/>
       <c r="E637" s="12"/>
       <c r="F637" s="12"/>
     </row>
     <row r="638" ht="14.25">
       <c r="C638"/>
-      <c r="D638" s="40"/>
+      <c r="D638" s="41"/>
       <c r="E638" s="12"/>
       <c r="F638" s="12"/>
     </row>
     <row r="639" ht="14.25">
       <c r="C639"/>
-      <c r="D639" s="40"/>
+      <c r="D639" s="41"/>
       <c r="E639" s="12"/>
       <c r="F639" s="12"/>
     </row>
     <row r="640" ht="14.25">
       <c r="C640"/>
-      <c r="D640" s="40"/>
+      <c r="D640" s="41"/>
       <c r="E640" s="12"/>
       <c r="F640" s="12"/>
     </row>
     <row r="641" ht="14.25">
       <c r="C641"/>
-      <c r="D641" s="40"/>
+      <c r="D641" s="41"/>
       <c r="E641" s="12"/>
       <c r="F641" s="12"/>
     </row>
-    <row r="642" ht="15">
+    <row r="642" ht="14.25">
       <c r="C642"/>
       <c r="D642" s="41"/>
-      <c r="E642" s="42"/>
-      <c r="F642" s="42"/>
+      <c r="E642" s="12"/>
+      <c r="F642" s="12"/>
     </row>
     <row r="643" ht="14.25">
       <c r="C643"/>
-      <c r="D643" s="40"/>
+      <c r="D643" s="41"/>
       <c r="E643" s="12"/>
       <c r="F643" s="12"/>
     </row>
     <row r="644" ht="14.25">
       <c r="C644"/>
-      <c r="D644" s="43"/>
-      <c r="E644" s="14"/>
-      <c r="F644" s="14"/>
-    </row>
-    <row r="645" ht="14.25">
+      <c r="D644" s="41"/>
+      <c r="E644" s="12"/>
+      <c r="F644" s="12"/>
+    </row>
+    <row r="645" ht="15">
       <c r="C645"/>
-      <c r="D645" s="40"/>
-      <c r="E645" s="12"/>
-      <c r="F645" s="12"/>
+      <c r="D645" s="42"/>
+      <c r="E645" s="43"/>
+      <c r="F645" s="43"/>
     </row>
     <row r="646" ht="14.25">
       <c r="C646"/>
-      <c r="D646" s="40"/>
+      <c r="D646" s="41"/>
       <c r="E646" s="12"/>
       <c r="F646" s="12"/>
     </row>
     <row r="647" ht="14.25">
       <c r="C647"/>
-      <c r="D647" s="11"/>
-      <c r="E647" s="12"/>
-      <c r="F647" s="12"/>
+      <c r="D647" s="44"/>
+      <c r="E647" s="14"/>
+      <c r="F647" s="14"/>
     </row>
     <row r="648" ht="14.25">
       <c r="C648"/>
-      <c r="D648" s="40"/>
+      <c r="D648" s="41"/>
       <c r="E648" s="12"/>
       <c r="F648" s="12"/>
     </row>
-    <row r="649" ht="15">
+    <row r="649" ht="14.25">
       <c r="C649"/>
       <c r="D649" s="41"/>
-      <c r="E649" s="42"/>
-      <c r="F649" s="42"/>
-    </row>
-    <row r="650" ht="15">
+      <c r="E649" s="12"/>
+      <c r="F649" s="12"/>
+    </row>
+    <row r="650" ht="14.25">
       <c r="C650"/>
-      <c r="D650" s="41"/>
-      <c r="E650" s="42"/>
-      <c r="F650" s="42"/>
-    </row>
-    <row r="651" ht="15">
+      <c r="D650" s="11"/>
+      <c r="E650" s="12"/>
+      <c r="F650" s="12"/>
+    </row>
+    <row r="651" ht="14.25">
       <c r="C651"/>
       <c r="D651" s="41"/>
-      <c r="E651" s="42"/>
-      <c r="F651" s="42"/>
-    </row>
-    <row r="652" ht="14.25">
+      <c r="E651" s="12"/>
+      <c r="F651" s="12"/>
+    </row>
+    <row r="652" ht="15">
       <c r="C652"/>
-      <c r="D652" s="40"/>
-      <c r="E652" s="12"/>
-      <c r="F652" s="12"/>
-    </row>
-    <row r="653" ht="14.25">
+      <c r="D652" s="42"/>
+      <c r="E652" s="43"/>
+      <c r="F652" s="43"/>
+    </row>
+    <row r="653" ht="15">
       <c r="C653"/>
-      <c r="D653" s="11"/>
-      <c r="E653" s="12"/>
-      <c r="F653" s="12"/>
-    </row>
-    <row r="654" ht="14.25">
+      <c r="D653" s="42"/>
+      <c r="E653" s="43"/>
+      <c r="F653" s="43"/>
+    </row>
+    <row r="654" ht="15">
       <c r="C654"/>
-      <c r="D654" s="40"/>
-      <c r="E654" s="12"/>
-      <c r="F654" s="12"/>
+      <c r="D654" s="42"/>
+      <c r="E654" s="43"/>
+      <c r="F654" s="43"/>
     </row>
     <row r="655" ht="14.25">
       <c r="C655"/>
-      <c r="D655" s="40"/>
+      <c r="D655" s="41"/>
       <c r="E655" s="12"/>
       <c r="F655" s="12"/>
     </row>
     <row r="656" ht="14.25">
       <c r="C656"/>
-      <c r="D656" s="40"/>
+      <c r="D656" s="11"/>
       <c r="E656" s="12"/>
       <c r="F656" s="12"/>
     </row>
     <row r="657" ht="14.25">
       <c r="C657"/>
-      <c r="D657" s="40"/>
+      <c r="D657" s="41"/>
       <c r="E657" s="12"/>
       <c r="F657" s="12"/>
     </row>
     <row r="658" ht="14.25">
       <c r="C658"/>
-      <c r="D658" s="40"/>
+      <c r="D658" s="41"/>
       <c r="E658" s="12"/>
       <c r="F658" s="12"/>
     </row>
     <row r="659" ht="14.25">
       <c r="C659"/>
-      <c r="D659" s="40"/>
+      <c r="D659" s="41"/>
       <c r="E659" s="12"/>
       <c r="F659" s="12"/>
     </row>
     <row r="660" ht="14.25">
       <c r="C660"/>
-      <c r="D660" s="11"/>
+      <c r="D660" s="41"/>
       <c r="E660" s="12"/>
       <c r="F660" s="12"/>
     </row>
-    <row r="661" ht="15">
+    <row r="661" ht="14.25">
       <c r="C661"/>
       <c r="D661" s="41"/>
-      <c r="E661" s="42"/>
-      <c r="F661" s="42"/>
-    </row>
-    <row r="662" ht="15">
+      <c r="E661" s="12"/>
+      <c r="F661" s="12"/>
+    </row>
+    <row r="662" ht="14.25">
       <c r="C662"/>
       <c r="D662" s="41"/>
-      <c r="E662" s="42"/>
-      <c r="F662" s="42"/>
-    </row>
-    <row r="663">
+      <c r="E662" s="12"/>
+      <c r="F662" s="12"/>
+    </row>
+    <row r="663" ht="14.25">
       <c r="C663"/>
-      <c r="E663" s="1"/>
-      <c r="F663" s="1"/>
-      <c r="G663" s="6"/>
-    </row>
-    <row r="664">
+      <c r="D663" s="11"/>
+      <c r="E663" s="12"/>
+      <c r="F663" s="12"/>
+    </row>
+    <row r="664" ht="15">
       <c r="C664"/>
-      <c r="E664" s="1"/>
-      <c r="F664" s="1"/>
-      <c r="G664" s="6"/>
-    </row>
-    <row r="665">
+      <c r="D664" s="42"/>
+      <c r="E664" s="43"/>
+      <c r="F664" s="43"/>
+    </row>
+    <row r="665" ht="15">
       <c r="C665"/>
-      <c r="E665" s="1"/>
-      <c r="F665" s="1"/>
-      <c r="G665" s="6"/>
+      <c r="D665" s="42"/>
+      <c r="E665" s="43"/>
+      <c r="F665" s="43"/>
     </row>
     <row r="666">
       <c r="C666"/>
@@ -16546,8 +16621,26 @@
       <c r="F776" s="1"/>
       <c r="G776" s="6"/>
     </row>
+    <row r="777">
+      <c r="C777"/>
+      <c r="E777" s="1"/>
+      <c r="F777" s="1"/>
+      <c r="G777" s="6"/>
+    </row>
+    <row r="778">
+      <c r="C778"/>
+      <c r="E778" s="1"/>
+      <c r="F778" s="1"/>
+      <c r="G778" s="6"/>
+    </row>
+    <row r="779">
+      <c r="C779"/>
+      <c r="E779" s="1"/>
+      <c r="F779" s="1"/>
+      <c r="G779" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G776"/>
+  <autoFilter ref="A1:G779"/>
   <printOptions headings="1" gridLines="0"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="42" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
@@ -16556,7 +16649,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="250" id="{005B0028-000F-4462-A939-0018006A00BB}">
+          <x14:cfRule type="expression" priority="250" id="{00530096-008F-4D97-AA55-002E00F8002F}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16567,10 +16660,24 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A549:B549 D549</xm:sqref>
+          <xm:sqref>A551:B551 D551</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="249" operator="notEqual" id="{0049001A-0020-4A25-A548-007200B40099}">
+          <x14:cfRule type="expression" priority="250" id="{002100B8-00DF-4784-8615-00E500250031}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A552:B552 D552</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="249" operator="notEqual" id="{00580026-008D-438C-94BA-004100D50003}">
             <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
@@ -16581,10 +16688,24 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E549</xm:sqref>
+          <xm:sqref>E551</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="245" id="{00A000AB-0061-479C-94B1-007500B100D1}">
+          <x14:cfRule type="cellIs" priority="249" operator="notEqual" id="{00A4000F-00C8-4A75-9155-009800A40000}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E552</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="245" id="{00FE00AA-00DD-44CC-B3CA-0046003D00C0}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16598,7 +16719,7 @@
           <xm:sqref>G417</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="243" id="{00F2001D-00D5-4C37-A6C8-00C300FB00D8}">
+          <x14:cfRule type="expression" priority="243" id="{007200A7-006A-416F-A06A-00B2008F0002}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16612,7 +16733,7 @@
           <xm:sqref>G416</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="241" id="{00DD00FD-0099-4444-A0E2-00710035003F}">
+          <x14:cfRule type="expression" priority="241" id="{00750024-002C-4175-943E-000600E8003F}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16626,7 +16747,91 @@
           <xm:sqref>G415</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="226" id="{006000BC-00CA-498F-BF38-00B0006F004E}">
+          <x14:cfRule type="expression" priority="226" id="{004400EA-0030-4C84-A6F8-002100BC00D1}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A662:B662</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="201" id="{00100038-0046-440E-9BCD-009C0031006E}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A653:B653</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="189" id="{009500B7-003D-4455-9361-009600EB00D6}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A643:B643</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="177" id="{00BB0010-0085-4CEA-82A6-006100BD0025}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A689:B689</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="167" id="{00D00009-00EB-4462-81A9-000100310041}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A682:B682</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="157" id="{00C2003A-0043-49EC-922A-000A00A5001C}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A669:B669</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="153" id="{00320018-00BE-420D-943D-000700D0002E}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16640,7 +16845,7 @@
           <xm:sqref>A659:B659</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="201" id="{006B00B7-0059-4093-85F4-00AD0031007B}">
+          <x14:cfRule type="expression" priority="136" id="{003F0021-00DD-41FE-8282-00CD0079007C}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16651,10 +16856,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A650:B650</xm:sqref>
+          <xm:sqref>A628:B628</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="189" id="{0090007D-0004-4F50-B9DB-00E7007B0054}">
+          <x14:cfRule type="expression" priority="121" id="{002A0040-000E-470D-9522-00040022000E}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16665,10 +16870,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A640:B640</xm:sqref>
+          <xm:sqref>A620:B620</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="177" id="{00D6005B-002F-4288-8B35-003200EF0039}">
+          <x14:cfRule type="expression" priority="108" id="{00BC0061-008F-468E-8B3B-0054004B00B3}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16679,10 +16884,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A686:B686</xm:sqref>
+          <xm:sqref>A613:B613</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="167" id="{0051008D-0006-4BD5-AA19-0049000B009E}">
+          <x14:cfRule type="expression" priority="102" id="{00A3009F-0058-4C27-8A14-003F0068005F}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16693,10 +16898,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A679:B679</xm:sqref>
+          <xm:sqref>A600:B600</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="157" id="{00E80035-0020-4594-9A82-0068003B0037}">
+          <x14:cfRule type="expression" priority="91" id="{0058000F-002A-4E49-B5A2-0009006C00D1}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16707,10 +16912,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A666:B666</xm:sqref>
+          <xm:sqref>A592:B592</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="153" id="{005B007B-00F1-4621-8C93-0074001D009B}">
+          <x14:cfRule type="expression" priority="86" id="{00D50083-0009-4C22-A5B3-00C80014004C}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16721,10 +16926,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A656:B656</xm:sqref>
+          <xm:sqref>A583:B583</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="136" id="{007A003F-0033-42DC-BBBB-00D800AD00E0}">
+          <x14:cfRule type="expression" priority="77" id="{00C6009E-00D6-4267-AD72-007500D80054}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16735,10 +16940,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A625:B625</xm:sqref>
+          <xm:sqref>A573:B573</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="121" id="{00C60065-0035-458F-9112-00A70089003E}">
+          <x14:cfRule type="expression" priority="73" id="{00070009-00D3-4A35-847A-003300DD003F}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16749,10 +16954,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A617:B617</xm:sqref>
+          <xm:sqref>A565:B565</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="108" id="{008800EC-00C6-4CED-9DE8-009100CD0070}">
+          <x14:cfRule type="expression" priority="69" id="{008800E1-00E6-4C3C-9597-00D70012003F}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16763,10 +16968,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A610:B610</xm:sqref>
+          <xm:sqref>A558:B558</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="102" id="{00320060-00EF-4752-ACDD-0074006000E3}">
+          <x14:cfRule type="expression" priority="62" id="{000600F2-0065-44B2-A05B-00E100A900FA}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16777,10 +16982,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A597:B597</xm:sqref>
+          <xm:sqref>A550:B550</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="91" id="{00AA00F4-00DB-456C-B8C7-009B0038009D}">
+          <x14:cfRule type="expression" priority="57" id="{007C006A-0086-4B3D-B7FA-00E80067003D}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16791,10 +16996,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A589:B589</xm:sqref>
+          <xm:sqref>A537:B537</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="86" id="{004000B9-0023-46D0-B01F-00BE009B0064}">
+          <x14:cfRule type="expression" priority="55" id="{00B000A0-00EB-4371-AD15-00E2009E0064}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16805,10 +17010,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A580:B580</xm:sqref>
+          <xm:sqref>A527:B527</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="77" id="{00F40067-0031-4711-9954-0044004A00F1}">
+          <x14:cfRule type="expression" priority="52" id="{005800C1-001A-435E-ACF6-0039007700FD}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16819,10 +17024,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A570:B570</xm:sqref>
+          <xm:sqref>A511:B511</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="73" id="{00670016-0059-40CA-83D0-00F900DB0091}">
+          <x14:cfRule type="expression" priority="51" id="{0045007D-0067-4308-8ACE-007500A300C4}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16833,10 +17038,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A562:B562</xm:sqref>
+          <xm:sqref>A497:B497</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="69" id="{00F000A8-00D5-4C8C-855B-00E100B10092}">
+          <x14:cfRule type="expression" priority="50" id="{00500088-0053-49EC-BE0B-00E9006500CE}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16847,10 +17052,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A555:B555</xm:sqref>
+          <xm:sqref>A491:B491</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="62" id="{007B0081-009D-438A-AF61-00E300670070}">
+          <x14:cfRule type="expression" priority="49" id="{00530013-008A-4356-9128-00E9006A00F1}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16861,94 +17066,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A548:B548</xm:sqref>
+          <xm:sqref>A463:B463</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="57" id="{008800ED-00C1-4FF7-B0B5-005A00C600E7}">
-            <xm:f>MOD($F2,2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor theme="0" tint="-0.14996795556505021"/>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A535:B535</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="55" id="{00D200CE-0082-4640-BBDE-006C00E6009C}">
-            <xm:f>MOD($F2,2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor theme="0" tint="-0.14996795556505021"/>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A525:B525</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="52" id="{00F400B0-0078-4484-86A9-00D000AF0033}">
-            <xm:f>MOD($F2,2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor theme="0" tint="-0.14996795556505021"/>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A509:B509</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="51" id="{001800E5-00B7-4131-A36D-0035009400DF}">
-            <xm:f>MOD($F2,2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor theme="0" tint="-0.14996795556505021"/>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A495:B495</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="50" id="{009C00FC-00FE-4F00-BAE8-0011003F007D}">
-            <xm:f>MOD($F2,2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor theme="0" tint="-0.14996795556505021"/>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A489:B489</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="49" id="{001E00F6-00D1-40EA-95B3-0003006800E4}">
-            <xm:f>MOD($F2,2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor theme="0" tint="-0.14996795556505021"/>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A461:B461</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="48" id="{001E00F8-008E-423F-9A8E-00DE00C60080}">
+          <x14:cfRule type="expression" priority="48" id="{002B00B8-004E-4367-88F2-008D004C0001}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16962,7 +17083,7 @@
           <xm:sqref>G414</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="47" id="{0062006C-006E-4EE5-BDC8-0088002E0022}">
+          <x14:cfRule type="expression" priority="47" id="{0062003E-001E-4494-9EB5-00A1002D00F1}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -16976,7 +17097,7 @@
           <xm:sqref>A415:B415</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="46" operator="notEqual" id="{005F004A-00D2-4F7B-9FA4-00D6007D00AD}">
+          <x14:cfRule type="cellIs" priority="46" operator="notEqual" id="{006C00C0-00F5-4F7B-927D-006D00270084}">
             <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
@@ -16987,10 +17108,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E417:E662</xm:sqref>
+          <xm:sqref>E417:E665</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="45" operator="notEqual" id="{009E0043-007A-471E-87CE-0084004D003B}">
+          <x14:cfRule type="cellIs" priority="46" operator="notEqual" id="{00350009-00E2-4B33-A5FA-00CF00A90060}">
             <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
@@ -17001,10 +17122,52 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E496</xm:sqref>
+          <xm:sqref>E436</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="40" operator="notEqual" id="{00D2009E-009B-46B0-990C-00A200210041}">
+          <x14:cfRule type="cellIs" priority="46" operator="notEqual" id="{00D600C0-004C-43E5-B7C6-00940096002E}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E437</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="46" operator="notEqual" id="{0004006F-000E-4B80-9749-00D000620079}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E552</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="45" operator="notEqual" id="{0032001D-0034-4ED2-A1A4-007400DD0036}">
+            <xm:f>#REF!</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="5"/>
+                  <bgColor indexed="5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E498</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="40" operator="notEqual" id="{00FD0046-00F2-46CE-9CCF-00E800EC00DE}">
             <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
@@ -17018,7 +17181,7 @@
           <xm:sqref>E415</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{00420010-0092-4D95-807D-0026002700C9}">
+          <x14:cfRule type="expression" priority="1" id="{00A10044-0053-4A27-AE42-009200DB0088}">
             <xm:f>MOD($F2,2)=0</xm:f>
             <x14:dxf>
               <fill>
@@ -17029,7 +17192,49 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A2:G414 A415:B776 D415:D776 G663:G776 A777:G9935</xm:sqref>
+          <xm:sqref>A2:G414 A415:B779 D415:D779 G666:G779 A780:G9938</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0058003A-001E-4A22-BA17-00AE001400B5}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A436:B436 D436</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00C10000-0027-4AE3-8C02-000900AE00FB}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A437:B437 D437</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006300DF-0019-48DA-B3D4-00D200E80013}">
+            <xm:f>MOD($F2,2)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor theme="0" tint="-0.14996795556505021"/>
+                  <bgColor theme="0" tint="-0.14996795556505021"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A552:B552 D552</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
